--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624300</v>
+        <v>129624391</v>
       </c>
       <c r="B4" t="n">
-        <v>101852</v>
+        <v>100957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668262</v>
+        <v>668163</v>
       </c>
       <c r="R4" t="n">
-        <v>6703729</v>
+        <v>6703831</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +974,7 @@
         <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624391</v>
+        <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>100945</v>
+        <v>101864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668163</v>
+        <v>668262</v>
       </c>
       <c r="R6" t="n">
-        <v>6703831</v>
+        <v>6703729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624331</v>
+        <v>129624343</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668257</v>
+        <v>668165</v>
       </c>
       <c r="R7" t="n">
-        <v>6703774</v>
+        <v>6703856</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624343</v>
+        <v>129624399</v>
       </c>
       <c r="B8" t="n">
-        <v>98734</v>
+        <v>100957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668165</v>
+        <v>668154</v>
       </c>
       <c r="R8" t="n">
-        <v>6703856</v>
+        <v>6703899</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624395</v>
+        <v>129624370</v>
       </c>
       <c r="B9" t="n">
-        <v>100945</v>
+        <v>105834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668288</v>
+        <v>668108</v>
       </c>
       <c r="R9" t="n">
-        <v>6703696</v>
+        <v>6703888</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624399</v>
+        <v>129624395</v>
       </c>
       <c r="B10" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668154</v>
+        <v>668288</v>
       </c>
       <c r="R10" t="n">
-        <v>6703899</v>
+        <v>6703696</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,45 +1553,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624370</v>
+        <v>129624331</v>
       </c>
       <c r="B11" t="n">
-        <v>105822</v>
+        <v>57732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668108</v>
+        <v>668257</v>
       </c>
       <c r="R11" t="n">
-        <v>6703888</v>
+        <v>6703774</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624374</v>
+        <v>129624308</v>
       </c>
       <c r="B12" t="n">
-        <v>4779</v>
+        <v>97014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668256</v>
+        <v>668162</v>
       </c>
       <c r="R12" t="n">
-        <v>6703754</v>
+        <v>6703712</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1736,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1767,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624394</v>
+        <v>129624313</v>
       </c>
       <c r="B13" t="n">
-        <v>100945</v>
+        <v>97014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668270</v>
+        <v>668179</v>
       </c>
       <c r="R13" t="n">
-        <v>6703699</v>
+        <v>6703790</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1848,6 +1833,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1864,32 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624308</v>
+        <v>129624383</v>
       </c>
       <c r="B14" t="n">
-        <v>97002</v>
+        <v>92237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668162</v>
+        <v>668279</v>
       </c>
       <c r="R14" t="n">
-        <v>6703712</v>
+        <v>6703691</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,6 +1945,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624313</v>
+        <v>129624394</v>
       </c>
       <c r="B15" t="n">
-        <v>97002</v>
+        <v>100957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668179</v>
+        <v>668270</v>
       </c>
       <c r="R15" t="n">
-        <v>6703790</v>
+        <v>6703699</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2042,21 +2057,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624383</v>
+        <v>129624374</v>
       </c>
       <c r="B16" t="n">
-        <v>92231</v>
+        <v>4779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668279</v>
+        <v>668256</v>
       </c>
       <c r="R16" t="n">
-        <v>6703691</v>
+        <v>6703754</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624310</v>
+        <v>129624392</v>
       </c>
       <c r="B17" t="n">
-        <v>97002</v>
+        <v>100957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668108</v>
+        <v>668190</v>
       </c>
       <c r="R17" t="n">
-        <v>6703891</v>
+        <v>6703813</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,21 +2266,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2297,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624392</v>
+        <v>129624390</v>
       </c>
       <c r="B18" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668190</v>
+        <v>668123</v>
       </c>
       <c r="R18" t="n">
-        <v>6703813</v>
+        <v>6703926</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2394,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624390</v>
+        <v>129624310</v>
       </c>
       <c r="B19" t="n">
-        <v>100945</v>
+        <v>97014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668123</v>
+        <v>668108</v>
       </c>
       <c r="R19" t="n">
-        <v>6703926</v>
+        <v>6703891</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2475,6 +2460,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2491,45 +2491,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624297</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>101852</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668176</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703677</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2591,7 +2596,7 @@
         <v>129624396</v>
       </c>
       <c r="B21" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,50 +2690,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624329</v>
+        <v>129624297</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>101864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668230</v>
+        <v>668176</v>
       </c>
       <c r="R22" t="n">
-        <v>6703725</v>
+        <v>6703677</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2790,7 +2790,7 @@
         <v>129624366</v>
       </c>
       <c r="B23" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B24" t="n">
-        <v>98734</v>
+        <v>100957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R24" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2990,45 +2990,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624368</v>
+        <v>129624328</v>
       </c>
       <c r="B25" t="n">
-        <v>105822</v>
+        <v>57732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668181</v>
+        <v>668312</v>
       </c>
       <c r="R25" t="n">
-        <v>6703685</v>
+        <v>6703726</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3087,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624401</v>
+        <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>100945</v>
+        <v>98746</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3098,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3122,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668293</v>
+        <v>668257</v>
       </c>
       <c r="R26" t="n">
-        <v>6703720</v>
+        <v>6703688</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3184,50 +3189,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624328</v>
+        <v>129624368</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>105834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668312</v>
+        <v>668181</v>
       </c>
       <c r="R27" t="n">
-        <v>6703726</v>
+        <v>6703685</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3289,7 +3289,7 @@
         <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B31" t="n">
-        <v>101852</v>
+        <v>87002</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R31" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B32" t="n">
-        <v>86996</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R32" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3785,6 +3790,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3801,10 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624382</v>
+        <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>101864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,39 +3832,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668266</v>
+        <v>668169</v>
       </c>
       <c r="R33" t="n">
-        <v>6703768</v>
+        <v>6703716</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3887,21 +3902,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624311</v>
+        <v>129624320</v>
       </c>
       <c r="B34" t="n">
-        <v>97002</v>
+        <v>104239</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668158</v>
+        <v>668289</v>
       </c>
       <c r="R34" t="n">
-        <v>6703911</v>
+        <v>6703690</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624320</v>
+        <v>129624311</v>
       </c>
       <c r="B35" t="n">
-        <v>104227</v>
+        <v>97014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668289</v>
+        <v>668158</v>
       </c>
       <c r="R35" t="n">
-        <v>6703690</v>
+        <v>6703911</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4115,7 +4115,7 @@
         <v>129624296</v>
       </c>
       <c r="B36" t="n">
-        <v>101852</v>
+        <v>101864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>129624369</v>
       </c>
       <c r="B37" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>129624325</v>
       </c>
       <c r="B39" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624373</v>
+        <v>129624307</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>97014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668112</v>
+        <v>668175</v>
       </c>
       <c r="R40" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,21 +4590,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4621,32 +4606,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624307</v>
+        <v>129624373</v>
       </c>
       <c r="B41" t="n">
-        <v>97002</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4656,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668175</v>
+        <v>668112</v>
       </c>
       <c r="R41" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4702,6 +4687,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,32 +4718,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624318</v>
+        <v>129624322</v>
       </c>
       <c r="B42" t="n">
-        <v>97002</v>
+        <v>104239</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668185</v>
+        <v>668300</v>
       </c>
       <c r="R42" t="n">
-        <v>6703684</v>
+        <v>6703703</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,21 +4799,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4833,7 +4818,7 @@
         <v>129624345</v>
       </c>
       <c r="B43" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4930,7 +4915,7 @@
         <v>129624340</v>
       </c>
       <c r="B44" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5027,7 +5012,7 @@
         <v>129624371</v>
       </c>
       <c r="B45" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5121,32 +5106,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624322</v>
+        <v>129624318</v>
       </c>
       <c r="B46" t="n">
-        <v>104227</v>
+        <v>97014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668300</v>
+        <v>668185</v>
       </c>
       <c r="R46" t="n">
-        <v>6703703</v>
+        <v>6703684</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5202,6 +5187,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101852</v>
+        <v>101864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>129624349</v>
       </c>
       <c r="B48" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>129624327</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>129624397</v>
       </c>
       <c r="B50" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5723,54 +5723,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624367</v>
+        <v>129624339</v>
       </c>
       <c r="B52" t="n">
-        <v>98756</v>
+        <v>98746</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668253</v>
+        <v>668166</v>
       </c>
       <c r="R52" t="n">
-        <v>6703781</v>
+        <v>6703694</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5829,45 +5820,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624339</v>
+        <v>129624367</v>
       </c>
       <c r="B53" t="n">
-        <v>98734</v>
+        <v>98768</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668166</v>
+        <v>668253</v>
       </c>
       <c r="R53" t="n">
-        <v>6703694</v>
+        <v>6703781</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5929,7 +5929,7 @@
         <v>129624393</v>
       </c>
       <c r="B54" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>129624385</v>
       </c>
       <c r="B55" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129624403</v>
       </c>
       <c r="B56" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>129624400</v>
       </c>
       <c r="B57" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624347</v>
+        <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>98734</v>
+        <v>97014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668269</v>
+        <v>668130</v>
       </c>
       <c r="R58" t="n">
-        <v>6703736</v>
+        <v>6703878</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624309</v>
+        <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668130</v>
+        <v>668229</v>
       </c>
       <c r="R59" t="n">
-        <v>6703878</v>
+        <v>6703722</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624317</v>
+        <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>97002</v>
+        <v>98746</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668229</v>
+        <v>668269</v>
       </c>
       <c r="R60" t="n">
-        <v>6703722</v>
+        <v>6703736</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>100945</v>
+        <v>97014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R62" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>97002</v>
+        <v>100957</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R63" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624323</v>
+        <v>129624389</v>
       </c>
       <c r="B64" t="n">
-        <v>110887</v>
+        <v>100957</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668134</v>
+        <v>668107</v>
       </c>
       <c r="R64" t="n">
-        <v>6703832</v>
+        <v>6703910</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6989,18 +6989,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7019,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624301</v>
+        <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>101852</v>
+        <v>110899</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7030,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7054,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668194</v>
+        <v>668134</v>
       </c>
       <c r="R65" t="n">
-        <v>6703673</v>
+        <v>6703832</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7092,12 +7086,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624389</v>
+        <v>129624301</v>
       </c>
       <c r="B66" t="n">
-        <v>100945</v>
+        <v>101864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668107</v>
+        <v>668194</v>
       </c>
       <c r="R66" t="n">
-        <v>6703910</v>
+        <v>6703673</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624391</v>
+        <v>129624346</v>
       </c>
       <c r="B4" t="n">
-        <v>100957</v>
+        <v>98747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668163</v>
+        <v>668302</v>
       </c>
       <c r="R4" t="n">
-        <v>6703831</v>
+        <v>6703689</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624346</v>
+        <v>129624391</v>
       </c>
       <c r="B5" t="n">
-        <v>98746</v>
+        <v>100958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668302</v>
+        <v>668163</v>
       </c>
       <c r="R5" t="n">
-        <v>6703689</v>
+        <v>6703831</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1071,7 @@
         <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624343</v>
+        <v>129624395</v>
       </c>
       <c r="B7" t="n">
-        <v>98746</v>
+        <v>100958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668165</v>
+        <v>668288</v>
       </c>
       <c r="R7" t="n">
-        <v>6703856</v>
+        <v>6703696</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1265,7 +1265,7 @@
         <v>129624399</v>
       </c>
       <c r="B8" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,45 +1359,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624370</v>
+        <v>129624331</v>
       </c>
       <c r="B9" t="n">
-        <v>105834</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668108</v>
+        <v>668257</v>
       </c>
       <c r="R9" t="n">
-        <v>6703888</v>
+        <v>6703774</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624395</v>
+        <v>129624370</v>
       </c>
       <c r="B10" t="n">
-        <v>100957</v>
+        <v>105835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668288</v>
+        <v>668108</v>
       </c>
       <c r="R10" t="n">
-        <v>6703696</v>
+        <v>6703888</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,50 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624331</v>
+        <v>129624343</v>
       </c>
       <c r="B11" t="n">
-        <v>57732</v>
+        <v>98747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668257</v>
+        <v>668165</v>
       </c>
       <c r="R11" t="n">
-        <v>6703774</v>
+        <v>6703856</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624308</v>
+        <v>129624383</v>
       </c>
       <c r="B12" t="n">
-        <v>97014</v>
+        <v>92238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668162</v>
+        <v>668279</v>
       </c>
       <c r="R12" t="n">
-        <v>6703712</v>
+        <v>6703691</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1752,32 +1767,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624313</v>
+        <v>129624374</v>
       </c>
       <c r="B13" t="n">
-        <v>97014</v>
+        <v>4779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668179</v>
+        <v>668256</v>
       </c>
       <c r="R13" t="n">
-        <v>6703790</v>
+        <v>6703754</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1864,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624383</v>
+        <v>129624394</v>
       </c>
       <c r="B14" t="n">
-        <v>92237</v>
+        <v>100958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668279</v>
+        <v>668270</v>
       </c>
       <c r="R14" t="n">
-        <v>6703691</v>
+        <v>6703699</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,21 +1960,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624394</v>
+        <v>129624308</v>
       </c>
       <c r="B15" t="n">
-        <v>100957</v>
+        <v>97015</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668270</v>
+        <v>668162</v>
       </c>
       <c r="R15" t="n">
-        <v>6703699</v>
+        <v>6703712</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2073,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624374</v>
+        <v>129624313</v>
       </c>
       <c r="B16" t="n">
-        <v>4779</v>
+        <v>97015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668256</v>
+        <v>668179</v>
       </c>
       <c r="R16" t="n">
-        <v>6703754</v>
+        <v>6703790</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624392</v>
+        <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>100957</v>
+        <v>97015</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668190</v>
+        <v>668108</v>
       </c>
       <c r="R17" t="n">
-        <v>6703813</v>
+        <v>6703891</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,6 +2266,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2282,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624390</v>
+        <v>129624392</v>
       </c>
       <c r="B18" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668123</v>
+        <v>668190</v>
       </c>
       <c r="R18" t="n">
-        <v>6703926</v>
+        <v>6703813</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2379,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624310</v>
+        <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>97014</v>
+        <v>100958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668108</v>
+        <v>668123</v>
       </c>
       <c r="R19" t="n">
-        <v>6703891</v>
+        <v>6703926</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2460,21 +2475,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2491,50 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>100958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2593,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B21" t="n">
-        <v>100957</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R21" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2693,7 +2693,7 @@
         <v>129624297</v>
       </c>
       <c r="B22" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>129624366</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624401</v>
+        <v>129624368</v>
       </c>
       <c r="B24" t="n">
-        <v>100957</v>
+        <v>105835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668293</v>
+        <v>668181</v>
       </c>
       <c r="R24" t="n">
-        <v>6703720</v>
+        <v>6703685</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2993,7 +2993,7 @@
         <v>129624328</v>
       </c>
       <c r="B25" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B26" t="n">
-        <v>98746</v>
+        <v>100958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R26" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624368</v>
+        <v>129624344</v>
       </c>
       <c r="B27" t="n">
-        <v>105834</v>
+        <v>98747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668181</v>
+        <v>668257</v>
       </c>
       <c r="R27" t="n">
-        <v>6703685</v>
+        <v>6703688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3289,7 +3289,7 @@
         <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B31" t="n">
-        <v>87002</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,34 +3618,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R31" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3688,6 +3693,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3704,10 +3724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624382</v>
+        <v>129624299</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>101865</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,39 +3735,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668266</v>
+        <v>668169</v>
       </c>
       <c r="R32" t="n">
-        <v>6703768</v>
+        <v>6703716</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3790,21 +3805,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3821,10 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B33" t="n">
-        <v>101864</v>
+        <v>87003</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,21 +3832,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R33" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624320</v>
+        <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>104239</v>
+        <v>97015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668289</v>
+        <v>668158</v>
       </c>
       <c r="R34" t="n">
-        <v>6703690</v>
+        <v>6703911</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624311</v>
+        <v>129624320</v>
       </c>
       <c r="B35" t="n">
-        <v>97014</v>
+        <v>104240</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668158</v>
+        <v>668289</v>
       </c>
       <c r="R35" t="n">
-        <v>6703911</v>
+        <v>6703690</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4115,7 +4115,7 @@
         <v>129624296</v>
       </c>
       <c r="B36" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624369</v>
+        <v>129624372</v>
       </c>
       <c r="B37" t="n">
-        <v>105834</v>
+        <v>96211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,34 +4220,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668127</v>
+        <v>668296</v>
       </c>
       <c r="R37" t="n">
-        <v>6703878</v>
+        <v>6703695</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4315,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B38" t="n">
-        <v>96210</v>
+        <v>96115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,43 +4326,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R38" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129624325</v>
+        <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>96114</v>
+        <v>105835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,21 +4423,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668318</v>
+        <v>668127</v>
       </c>
       <c r="R39" t="n">
-        <v>6703714</v>
+        <v>6703878</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624307</v>
+        <v>129624373</v>
       </c>
       <c r="B40" t="n">
-        <v>97014</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668175</v>
+        <v>668112</v>
       </c>
       <c r="R40" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,6 +4590,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4606,10 +4621,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624373</v>
+        <v>129624322</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>104240</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4617,21 +4632,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>222412</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668112</v>
+        <v>668300</v>
       </c>
       <c r="R41" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,21 +4702,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624322</v>
+        <v>129624345</v>
       </c>
       <c r="B42" t="n">
-        <v>104239</v>
+        <v>98747</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668300</v>
+        <v>668302</v>
       </c>
       <c r="R42" t="n">
-        <v>6703703</v>
+        <v>6703713</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624345</v>
+        <v>129624307</v>
       </c>
       <c r="B43" t="n">
-        <v>98746</v>
+        <v>97015</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668302</v>
+        <v>668175</v>
       </c>
       <c r="R43" t="n">
-        <v>6703713</v>
+        <v>6703703</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624340</v>
+        <v>129624318</v>
       </c>
       <c r="B44" t="n">
-        <v>98746</v>
+        <v>97015</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668169</v>
+        <v>668185</v>
       </c>
       <c r="R44" t="n">
-        <v>6703716</v>
+        <v>6703684</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4993,6 +4993,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5009,10 +5024,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624371</v>
+        <v>129624340</v>
       </c>
       <c r="B45" t="n">
-        <v>105834</v>
+        <v>98747</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5020,21 +5035,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5044,10 +5059,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668163</v>
+        <v>668169</v>
       </c>
       <c r="R45" t="n">
-        <v>6703870</v>
+        <v>6703716</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5106,32 +5121,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624318</v>
+        <v>129624371</v>
       </c>
       <c r="B46" t="n">
-        <v>97014</v>
+        <v>105835</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5141,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668185</v>
+        <v>668163</v>
       </c>
       <c r="R46" t="n">
-        <v>6703684</v>
+        <v>6703870</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5187,21 +5202,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5315,45 +5315,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624349</v>
+        <v>129624327</v>
       </c>
       <c r="B48" t="n">
-        <v>92040</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668275</v>
+        <v>668173</v>
       </c>
       <c r="R48" t="n">
-        <v>6703756</v>
+        <v>6703787</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5396,21 +5401,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5427,50 +5417,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624327</v>
+        <v>129624397</v>
       </c>
       <c r="B49" t="n">
-        <v>57732</v>
+        <v>100958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668173</v>
+        <v>668305</v>
       </c>
       <c r="R49" t="n">
-        <v>6703787</v>
+        <v>6703751</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5529,32 +5514,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624397</v>
+        <v>129624349</v>
       </c>
       <c r="B50" t="n">
-        <v>100957</v>
+        <v>92041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5564,10 +5549,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668305</v>
+        <v>668275</v>
       </c>
       <c r="R50" t="n">
-        <v>6703751</v>
+        <v>6703756</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5610,6 +5595,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5629,7 +5629,7 @@
         <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5723,45 +5723,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624339</v>
+        <v>129624367</v>
       </c>
       <c r="B52" t="n">
-        <v>98746</v>
+        <v>98769</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668166</v>
+        <v>668253</v>
       </c>
       <c r="R52" t="n">
-        <v>6703694</v>
+        <v>6703781</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,54 +5829,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624367</v>
+        <v>129624393</v>
       </c>
       <c r="B53" t="n">
-        <v>98768</v>
+        <v>100958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668253</v>
+        <v>668182</v>
       </c>
       <c r="R53" t="n">
-        <v>6703781</v>
+        <v>6703746</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624393</v>
+        <v>129624385</v>
       </c>
       <c r="B54" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668182</v>
+        <v>668149</v>
       </c>
       <c r="R54" t="n">
-        <v>6703746</v>
+        <v>6703811</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624385</v>
+        <v>129624403</v>
       </c>
       <c r="B55" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668149</v>
+        <v>668258</v>
       </c>
       <c r="R55" t="n">
-        <v>6703811</v>
+        <v>6703763</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624403</v>
+        <v>129624400</v>
       </c>
       <c r="B56" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668258</v>
+        <v>668331</v>
       </c>
       <c r="R56" t="n">
-        <v>6703763</v>
+        <v>6703743</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624400</v>
+        <v>129624339</v>
       </c>
       <c r="B57" t="n">
-        <v>100957</v>
+        <v>98747</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668331</v>
+        <v>668166</v>
       </c>
       <c r="R57" t="n">
-        <v>6703743</v>
+        <v>6703694</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6317,7 +6317,7 @@
         <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>129624389</v>
       </c>
       <c r="B64" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>129624301</v>
       </c>
       <c r="B66" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -1165,45 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624395</v>
+        <v>129624331</v>
       </c>
       <c r="B7" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668288</v>
+        <v>668257</v>
       </c>
       <c r="R7" t="n">
-        <v>6703696</v>
+        <v>6703774</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624399</v>
+        <v>129624395</v>
       </c>
       <c r="B8" t="n">
         <v>100958</v>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668154</v>
+        <v>668288</v>
       </c>
       <c r="R8" t="n">
-        <v>6703899</v>
+        <v>6703696</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,50 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624331</v>
+        <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>100958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668257</v>
+        <v>668154</v>
       </c>
       <c r="R9" t="n">
-        <v>6703774</v>
+        <v>6703899</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624370</v>
+        <v>129624343</v>
       </c>
       <c r="B10" t="n">
-        <v>105835</v>
+        <v>98747</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668108</v>
+        <v>668165</v>
       </c>
       <c r="R10" t="n">
-        <v>6703888</v>
+        <v>6703856</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624343</v>
+        <v>129624370</v>
       </c>
       <c r="B11" t="n">
-        <v>98747</v>
+        <v>105835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668165</v>
+        <v>668108</v>
       </c>
       <c r="R11" t="n">
-        <v>6703856</v>
+        <v>6703888</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2491,45 +2491,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2588,50 +2593,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>100958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R21" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B32" t="n">
-        <v>101865</v>
+        <v>87003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R32" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624404</v>
+        <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>87003</v>
+        <v>101865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,21 +3832,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668299</v>
+        <v>668169</v>
       </c>
       <c r="R33" t="n">
-        <v>6703709</v>
+        <v>6703716</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624320</v>
+        <v>129624296</v>
       </c>
       <c r="B35" t="n">
-        <v>104240</v>
+        <v>101865</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668289</v>
+        <v>668152</v>
       </c>
       <c r="R35" t="n">
-        <v>6703690</v>
+        <v>6703756</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624296</v>
+        <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>101865</v>
+        <v>104240</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668152</v>
+        <v>668289</v>
       </c>
       <c r="R36" t="n">
-        <v>6703756</v>
+        <v>6703690</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624373</v>
+        <v>129624322</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>104240</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668112</v>
+        <v>668300</v>
       </c>
       <c r="R40" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,21 +4590,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4621,32 +4606,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624322</v>
+        <v>129624307</v>
       </c>
       <c r="B41" t="n">
-        <v>104240</v>
+        <v>97015</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4656,7 +4641,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668300</v>
+        <v>668175</v>
       </c>
       <c r="R41" t="n">
         <v>6703703</v>
@@ -4718,32 +4703,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624345</v>
+        <v>129624318</v>
       </c>
       <c r="B42" t="n">
-        <v>98747</v>
+        <v>97015</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4738,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668302</v>
+        <v>668185</v>
       </c>
       <c r="R42" t="n">
-        <v>6703713</v>
+        <v>6703684</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,6 +4784,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4815,32 +4815,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624307</v>
+        <v>129624373</v>
       </c>
       <c r="B43" t="n">
-        <v>97015</v>
+        <v>4779</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668175</v>
+        <v>668112</v>
       </c>
       <c r="R43" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4896,6 +4896,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4912,32 +4927,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624318</v>
+        <v>129624345</v>
       </c>
       <c r="B44" t="n">
-        <v>97015</v>
+        <v>98747</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4947,10 +4962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668185</v>
+        <v>668302</v>
       </c>
       <c r="R44" t="n">
-        <v>6703684</v>
+        <v>6703713</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4993,21 +5008,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5315,50 +5315,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>92041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R48" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5401,6 +5396,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5417,45 +5427,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624397</v>
+        <v>129624327</v>
       </c>
       <c r="B49" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668305</v>
+        <v>668173</v>
       </c>
       <c r="R49" t="n">
-        <v>6703751</v>
+        <v>6703787</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5514,32 +5529,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624349</v>
+        <v>129624397</v>
       </c>
       <c r="B50" t="n">
-        <v>92041</v>
+        <v>100958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5549,10 +5564,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668275</v>
+        <v>668305</v>
       </c>
       <c r="R50" t="n">
-        <v>6703756</v>
+        <v>6703751</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5595,21 +5610,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B62" t="n">
-        <v>97015</v>
+        <v>100958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R62" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B63" t="n">
-        <v>100958</v>
+        <v>97015</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R63" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624323</v>
+        <v>129624301</v>
       </c>
       <c r="B65" t="n">
-        <v>110900</v>
+        <v>101865</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668134</v>
+        <v>668194</v>
       </c>
       <c r="R65" t="n">
-        <v>6703832</v>
+        <v>6703673</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7086,18 +7086,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7110,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624301</v>
+        <v>129624323</v>
       </c>
       <c r="B66" t="n">
-        <v>101865</v>
+        <v>110900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7121,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7145,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668194</v>
+        <v>668134</v>
       </c>
       <c r="R66" t="n">
-        <v>6703673</v>
+        <v>6703832</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7189,12 +7183,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624330</v>
+        <v>129624346</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668289</v>
+        <v>668302</v>
       </c>
       <c r="R3" t="n">
-        <v>6703714</v>
+        <v>6703689</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624346</v>
+        <v>129624330</v>
       </c>
       <c r="B4" t="n">
-        <v>98747</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668302</v>
+        <v>668289</v>
       </c>
       <c r="R4" t="n">
-        <v>6703689</v>
+        <v>6703714</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624391</v>
+        <v>129624300</v>
       </c>
       <c r="B5" t="n">
-        <v>100958</v>
+        <v>101870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668163</v>
+        <v>668262</v>
       </c>
       <c r="R5" t="n">
-        <v>6703831</v>
+        <v>6703729</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624300</v>
+        <v>129624391</v>
       </c>
       <c r="B6" t="n">
-        <v>101865</v>
+        <v>100963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668262</v>
+        <v>668163</v>
       </c>
       <c r="R6" t="n">
-        <v>6703729</v>
+        <v>6703831</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624395</v>
+        <v>129624370</v>
       </c>
       <c r="B8" t="n">
-        <v>100958</v>
+        <v>105840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668288</v>
+        <v>668108</v>
       </c>
       <c r="R8" t="n">
-        <v>6703696</v>
+        <v>6703888</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624399</v>
+        <v>129624395</v>
       </c>
       <c r="B9" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668154</v>
+        <v>668288</v>
       </c>
       <c r="R9" t="n">
-        <v>6703899</v>
+        <v>6703696</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624343</v>
+        <v>129624399</v>
       </c>
       <c r="B10" t="n">
-        <v>98747</v>
+        <v>100963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668165</v>
+        <v>668154</v>
       </c>
       <c r="R10" t="n">
-        <v>6703856</v>
+        <v>6703899</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624370</v>
+        <v>129624343</v>
       </c>
       <c r="B11" t="n">
-        <v>105835</v>
+        <v>98752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668108</v>
+        <v>668165</v>
       </c>
       <c r="R11" t="n">
-        <v>6703888</v>
+        <v>6703856</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624383</v>
+        <v>129624308</v>
       </c>
       <c r="B12" t="n">
-        <v>92238</v>
+        <v>97020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668279</v>
+        <v>668162</v>
       </c>
       <c r="R12" t="n">
-        <v>6703691</v>
+        <v>6703712</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1736,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1767,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624374</v>
+        <v>129624313</v>
       </c>
       <c r="B13" t="n">
-        <v>4779</v>
+        <v>97020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668256</v>
+        <v>668179</v>
       </c>
       <c r="R13" t="n">
-        <v>6703754</v>
+        <v>6703790</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1879,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624394</v>
+        <v>129624374</v>
       </c>
       <c r="B14" t="n">
-        <v>100958</v>
+        <v>4779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668270</v>
+        <v>668256</v>
       </c>
       <c r="R14" t="n">
-        <v>6703699</v>
+        <v>6703754</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,6 +1945,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624308</v>
+        <v>129624394</v>
       </c>
       <c r="B15" t="n">
-        <v>97015</v>
+        <v>100963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668162</v>
+        <v>668270</v>
       </c>
       <c r="R15" t="n">
-        <v>6703712</v>
+        <v>6703699</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2073,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624313</v>
+        <v>129624383</v>
       </c>
       <c r="B16" t="n">
-        <v>97015</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668179</v>
+        <v>668279</v>
       </c>
       <c r="R16" t="n">
-        <v>6703790</v>
+        <v>6703691</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2188,7 +2188,7 @@
         <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>129624392</v>
       </c>
       <c r="B18" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,50 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2593,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B21" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R21" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2690,45 +2690,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624297</v>
+        <v>129624366</v>
       </c>
       <c r="B22" t="n">
-        <v>101865</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668176</v>
+        <v>668160</v>
       </c>
       <c r="R22" t="n">
-        <v>6703677</v>
+        <v>6703911</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2787,54 +2796,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624366</v>
+        <v>129624297</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>101870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668160</v>
+        <v>668176</v>
       </c>
       <c r="R23" t="n">
-        <v>6703911</v>
+        <v>6703677</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2893,45 +2893,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624368</v>
+        <v>129624328</v>
       </c>
       <c r="B24" t="n">
-        <v>105835</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668181</v>
+        <v>668312</v>
       </c>
       <c r="R24" t="n">
-        <v>6703685</v>
+        <v>6703726</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2990,50 +2995,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624328</v>
+        <v>129624368</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>105840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668312</v>
+        <v>668181</v>
       </c>
       <c r="R25" t="n">
-        <v>6703726</v>
+        <v>6703685</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3092,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624401</v>
+        <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>100958</v>
+        <v>98752</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668293</v>
+        <v>668257</v>
       </c>
       <c r="R26" t="n">
-        <v>6703720</v>
+        <v>6703688</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B27" t="n">
-        <v>98747</v>
+        <v>100963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R27" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3289,7 +3289,7 @@
         <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624382</v>
+        <v>129624404</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>87008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,39 +3618,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668266</v>
+        <v>668299</v>
       </c>
       <c r="R31" t="n">
-        <v>6703768</v>
+        <v>6703709</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3693,21 +3688,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3724,10 +3704,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B32" t="n">
-        <v>87003</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,34 +3715,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R32" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3805,6 +3790,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3824,7 +3824,7 @@
         <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>101865</v>
+        <v>101870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129624296</v>
       </c>
       <c r="B35" t="n">
-        <v>101865</v>
+        <v>101870</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>104240</v>
+        <v>104245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96211</v>
+        <v>96120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,43 +4220,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R37" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4315,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624325</v>
+        <v>129624369</v>
       </c>
       <c r="B38" t="n">
-        <v>96115</v>
+        <v>105840</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,21 +4317,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4350,10 +4341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668318</v>
+        <v>668127</v>
       </c>
       <c r="R38" t="n">
-        <v>6703714</v>
+        <v>6703878</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4412,10 +4403,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129624369</v>
+        <v>129624372</v>
       </c>
       <c r="B39" t="n">
-        <v>105835</v>
+        <v>96216</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,34 +4414,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668127</v>
+        <v>668296</v>
       </c>
       <c r="R39" t="n">
-        <v>6703878</v>
+        <v>6703695</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624322</v>
+        <v>129624307</v>
       </c>
       <c r="B40" t="n">
-        <v>104240</v>
+        <v>97020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668300</v>
+        <v>668175</v>
       </c>
       <c r="R40" t="n">
         <v>6703703</v>
@@ -4606,32 +4606,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624307</v>
+        <v>129624373</v>
       </c>
       <c r="B41" t="n">
-        <v>97015</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668175</v>
+        <v>668112</v>
       </c>
       <c r="R41" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,6 +4687,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4703,32 +4718,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624318</v>
+        <v>129624371</v>
       </c>
       <c r="B42" t="n">
-        <v>97015</v>
+        <v>105840</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4738,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668185</v>
+        <v>668163</v>
       </c>
       <c r="R42" t="n">
-        <v>6703684</v>
+        <v>6703870</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4784,21 +4799,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4815,10 +4815,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624373</v>
+        <v>129624345</v>
       </c>
       <c r="B43" t="n">
-        <v>4779</v>
+        <v>98752</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668112</v>
+        <v>668302</v>
       </c>
       <c r="R43" t="n">
-        <v>6703887</v>
+        <v>6703713</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4896,21 +4896,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4927,10 +4912,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624345</v>
+        <v>129624340</v>
       </c>
       <c r="B44" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,10 +4947,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668302</v>
+        <v>668169</v>
       </c>
       <c r="R44" t="n">
-        <v>6703713</v>
+        <v>6703716</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5024,10 +5009,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624340</v>
+        <v>129624322</v>
       </c>
       <c r="B45" t="n">
-        <v>98747</v>
+        <v>104245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5035,21 +5020,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5059,10 +5044,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668169</v>
+        <v>668300</v>
       </c>
       <c r="R45" t="n">
-        <v>6703716</v>
+        <v>6703703</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5121,32 +5106,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624371</v>
+        <v>129624318</v>
       </c>
       <c r="B46" t="n">
-        <v>105835</v>
+        <v>97020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668163</v>
+        <v>668185</v>
       </c>
       <c r="R46" t="n">
-        <v>6703870</v>
+        <v>6703684</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5202,6 +5187,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101865</v>
+        <v>101870</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>129624349</v>
       </c>
       <c r="B48" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>129624397</v>
       </c>
       <c r="B50" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5626,10 +5626,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624348</v>
+        <v>129624393</v>
       </c>
       <c r="B51" t="n">
-        <v>91361</v>
+        <v>100963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668185</v>
+        <v>668182</v>
       </c>
       <c r="R51" t="n">
-        <v>6703715</v>
+        <v>6703746</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5723,54 +5723,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624367</v>
+        <v>129624385</v>
       </c>
       <c r="B52" t="n">
-        <v>98769</v>
+        <v>100963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668253</v>
+        <v>668149</v>
       </c>
       <c r="R52" t="n">
-        <v>6703781</v>
+        <v>6703811</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5829,10 +5820,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624393</v>
+        <v>129624403</v>
       </c>
       <c r="B53" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5864,10 +5855,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668182</v>
+        <v>668258</v>
       </c>
       <c r="R53" t="n">
-        <v>6703746</v>
+        <v>6703763</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624385</v>
+        <v>129624400</v>
       </c>
       <c r="B54" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5961,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668149</v>
+        <v>668331</v>
       </c>
       <c r="R54" t="n">
-        <v>6703811</v>
+        <v>6703743</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,10 +6014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624403</v>
+        <v>129624348</v>
       </c>
       <c r="B55" t="n">
-        <v>100958</v>
+        <v>91366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6034,21 +6025,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6058,10 +6049,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668258</v>
+        <v>668185</v>
       </c>
       <c r="R55" t="n">
-        <v>6703763</v>
+        <v>6703715</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,45 +6111,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624400</v>
+        <v>129624367</v>
       </c>
       <c r="B56" t="n">
-        <v>100958</v>
+        <v>98774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668331</v>
+        <v>668253</v>
       </c>
       <c r="R56" t="n">
-        <v>6703743</v>
+        <v>6703781</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6220,7 +6220,7 @@
         <v>129624339</v>
       </c>
       <c r="B57" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>100958</v>
+        <v>97020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R62" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>97015</v>
+        <v>100963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R63" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624389</v>
+        <v>129624301</v>
       </c>
       <c r="B64" t="n">
-        <v>100958</v>
+        <v>101870</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668107</v>
+        <v>668194</v>
       </c>
       <c r="R64" t="n">
-        <v>6703910</v>
+        <v>6703673</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624301</v>
+        <v>129624389</v>
       </c>
       <c r="B65" t="n">
-        <v>101865</v>
+        <v>100963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668194</v>
+        <v>668107</v>
       </c>
       <c r="R65" t="n">
-        <v>6703673</v>
+        <v>6703910</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7113,7 +7113,7 @@
         <v>129624323</v>
       </c>
       <c r="B66" t="n">
-        <v>110900</v>
+        <v>110905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624346</v>
+        <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668302</v>
+        <v>668289</v>
       </c>
       <c r="R3" t="n">
-        <v>6703689</v>
+        <v>6703714</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624330</v>
+        <v>129624391</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668289</v>
+        <v>668163</v>
       </c>
       <c r="R4" t="n">
-        <v>6703714</v>
+        <v>6703831</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624300</v>
+        <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>101870</v>
+        <v>98752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668262</v>
+        <v>668302</v>
       </c>
       <c r="R5" t="n">
-        <v>6703729</v>
+        <v>6703689</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624391</v>
+        <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>101870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668163</v>
+        <v>668262</v>
       </c>
       <c r="R6" t="n">
-        <v>6703831</v>
+        <v>6703729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624331</v>
+        <v>129624395</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668257</v>
+        <v>668288</v>
       </c>
       <c r="R7" t="n">
-        <v>6703774</v>
+        <v>6703696</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624370</v>
+        <v>129624399</v>
       </c>
       <c r="B8" t="n">
-        <v>105840</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668108</v>
+        <v>668154</v>
       </c>
       <c r="R8" t="n">
-        <v>6703888</v>
+        <v>6703899</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624395</v>
+        <v>129624343</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668288</v>
+        <v>668165</v>
       </c>
       <c r="R9" t="n">
-        <v>6703696</v>
+        <v>6703856</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624399</v>
+        <v>129624370</v>
       </c>
       <c r="B10" t="n">
-        <v>100963</v>
+        <v>105840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668154</v>
+        <v>668108</v>
       </c>
       <c r="R10" t="n">
-        <v>6703899</v>
+        <v>6703888</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,45 +1553,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624343</v>
+        <v>129624331</v>
       </c>
       <c r="B11" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668165</v>
+        <v>668257</v>
       </c>
       <c r="R11" t="n">
-        <v>6703856</v>
+        <v>6703774</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624374</v>
+        <v>129624383</v>
       </c>
       <c r="B14" t="n">
-        <v>4779</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668256</v>
+        <v>668279</v>
       </c>
       <c r="R14" t="n">
-        <v>6703754</v>
+        <v>6703691</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624383</v>
+        <v>129624374</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>4779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668279</v>
+        <v>668256</v>
       </c>
       <c r="R16" t="n">
-        <v>6703691</v>
+        <v>6703754</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2491,45 +2491,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2588,50 +2593,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624329</v>
+        <v>129624297</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>101870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668230</v>
+        <v>668176</v>
       </c>
       <c r="R21" t="n">
-        <v>6703725</v>
+        <v>6703677</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624297</v>
+        <v>129624396</v>
       </c>
       <c r="B23" t="n">
-        <v>101870</v>
+        <v>100963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668176</v>
+        <v>668305</v>
       </c>
       <c r="R23" t="n">
-        <v>6703677</v>
+        <v>6703732</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2893,50 +2893,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624328</v>
+        <v>129624401</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668312</v>
+        <v>668293</v>
       </c>
       <c r="R24" t="n">
-        <v>6703726</v>
+        <v>6703720</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2995,45 +2990,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624368</v>
+        <v>129624328</v>
       </c>
       <c r="B25" t="n">
-        <v>105840</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668181</v>
+        <v>668312</v>
       </c>
       <c r="R25" t="n">
-        <v>6703685</v>
+        <v>6703726</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624401</v>
+        <v>129624368</v>
       </c>
       <c r="B27" t="n">
-        <v>100963</v>
+        <v>105840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668293</v>
+        <v>668181</v>
       </c>
       <c r="R27" t="n">
-        <v>6703720</v>
+        <v>6703685</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3286,32 +3286,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624316</v>
+        <v>129624388</v>
       </c>
       <c r="B28" t="n">
-        <v>97020</v>
+        <v>100963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668262</v>
+        <v>668122</v>
       </c>
       <c r="R28" t="n">
-        <v>6703727</v>
+        <v>6703878</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,21 +3367,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3398,32 +3383,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624388</v>
+        <v>129624316</v>
       </c>
       <c r="B29" t="n">
-        <v>100963</v>
+        <v>97020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668122</v>
+        <v>668262</v>
       </c>
       <c r="R29" t="n">
-        <v>6703878</v>
+        <v>6703727</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3479,6 +3464,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3495,32 +3495,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624315</v>
+        <v>129624404</v>
       </c>
       <c r="B30" t="n">
-        <v>97020</v>
+        <v>87008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668277</v>
+        <v>668299</v>
       </c>
       <c r="R30" t="n">
-        <v>6703748</v>
+        <v>6703709</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3576,21 +3576,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3607,10 +3592,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B31" t="n">
-        <v>87008</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,34 +3603,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R31" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3688,6 +3678,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3704,10 +3709,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624382</v>
+        <v>129624299</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>101870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,39 +3720,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668266</v>
+        <v>668169</v>
       </c>
       <c r="R32" t="n">
-        <v>6703768</v>
+        <v>6703716</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3790,21 +3790,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3821,32 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624299</v>
+        <v>129624315</v>
       </c>
       <c r="B33" t="n">
-        <v>101870</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668169</v>
+        <v>668277</v>
       </c>
       <c r="R33" t="n">
-        <v>6703716</v>
+        <v>6703748</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3902,6 +3887,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624296</v>
+        <v>129624320</v>
       </c>
       <c r="B35" t="n">
-        <v>101870</v>
+        <v>104245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668152</v>
+        <v>668289</v>
       </c>
       <c r="R35" t="n">
-        <v>6703756</v>
+        <v>6703690</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624320</v>
+        <v>129624296</v>
       </c>
       <c r="B36" t="n">
-        <v>104245</v>
+        <v>101870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668289</v>
+        <v>668152</v>
       </c>
       <c r="R36" t="n">
-        <v>6703690</v>
+        <v>6703756</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B37" t="n">
-        <v>96120</v>
+        <v>96216</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,34 +4220,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R37" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4315,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624369</v>
+        <v>129624325</v>
       </c>
       <c r="B38" t="n">
-        <v>105840</v>
+        <v>96120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,21 +4326,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4341,10 +4350,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668127</v>
+        <v>668318</v>
       </c>
       <c r="R38" t="n">
-        <v>6703878</v>
+        <v>6703714</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4403,10 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129624372</v>
+        <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>96216</v>
+        <v>105840</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4414,43 +4423,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668296</v>
+        <v>668127</v>
       </c>
       <c r="R39" t="n">
-        <v>6703695</v>
+        <v>6703878</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624307</v>
+        <v>129624322</v>
       </c>
       <c r="B40" t="n">
-        <v>97020</v>
+        <v>104245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668175</v>
+        <v>668300</v>
       </c>
       <c r="R40" t="n">
         <v>6703703</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624373</v>
+        <v>129624345</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>98752</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4617,21 +4617,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668112</v>
+        <v>668302</v>
       </c>
       <c r="R41" t="n">
-        <v>6703887</v>
+        <v>6703713</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,21 +4687,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,10 +4703,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624371</v>
+        <v>129624340</v>
       </c>
       <c r="B42" t="n">
-        <v>105840</v>
+        <v>98752</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4714,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4738,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668163</v>
+        <v>668169</v>
       </c>
       <c r="R42" t="n">
-        <v>6703870</v>
+        <v>6703716</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4815,10 +4800,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624345</v>
+        <v>129624371</v>
       </c>
       <c r="B43" t="n">
-        <v>98752</v>
+        <v>105840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,21 +4811,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4835,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668302</v>
+        <v>668163</v>
       </c>
       <c r="R43" t="n">
-        <v>6703713</v>
+        <v>6703870</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4912,32 +4897,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624340</v>
+        <v>129624307</v>
       </c>
       <c r="B44" t="n">
-        <v>98752</v>
+        <v>97020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4947,10 +4932,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668169</v>
+        <v>668175</v>
       </c>
       <c r="R44" t="n">
-        <v>6703716</v>
+        <v>6703703</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5009,32 +4994,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624322</v>
+        <v>129624318</v>
       </c>
       <c r="B45" t="n">
-        <v>104245</v>
+        <v>97020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5044,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668300</v>
+        <v>668185</v>
       </c>
       <c r="R45" t="n">
-        <v>6703703</v>
+        <v>6703684</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5090,6 +5075,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5106,32 +5106,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624318</v>
+        <v>129624373</v>
       </c>
       <c r="B46" t="n">
-        <v>97020</v>
+        <v>4779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668185</v>
+        <v>668112</v>
       </c>
       <c r="R46" t="n">
-        <v>6703684</v>
+        <v>6703887</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5315,32 +5315,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624349</v>
+        <v>129624397</v>
       </c>
       <c r="B48" t="n">
-        <v>92046</v>
+        <v>100963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668275</v>
+        <v>668305</v>
       </c>
       <c r="R48" t="n">
-        <v>6703756</v>
+        <v>6703751</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5396,21 +5396,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5427,50 +5412,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>92046</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R49" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5513,6 +5493,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5529,45 +5524,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624397</v>
+        <v>129624327</v>
       </c>
       <c r="B50" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668305</v>
+        <v>668173</v>
       </c>
       <c r="R50" t="n">
-        <v>6703751</v>
+        <v>6703787</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5626,10 +5626,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624393</v>
+        <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>100963</v>
+        <v>91366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668182</v>
+        <v>668185</v>
       </c>
       <c r="R51" t="n">
-        <v>6703746</v>
+        <v>6703715</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624385</v>
+        <v>129624339</v>
       </c>
       <c r="B52" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668149</v>
+        <v>668166</v>
       </c>
       <c r="R52" t="n">
-        <v>6703811</v>
+        <v>6703694</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624403</v>
+        <v>129624385</v>
       </c>
       <c r="B53" t="n">
         <v>100963</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668258</v>
+        <v>668149</v>
       </c>
       <c r="R53" t="n">
-        <v>6703763</v>
+        <v>6703811</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5917,45 +5917,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624400</v>
+        <v>129624367</v>
       </c>
       <c r="B54" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668331</v>
+        <v>668253</v>
       </c>
       <c r="R54" t="n">
-        <v>6703743</v>
+        <v>6703781</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6014,10 +6023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624348</v>
+        <v>129624393</v>
       </c>
       <c r="B55" t="n">
-        <v>91366</v>
+        <v>100963</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6025,21 +6034,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6049,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668185</v>
+        <v>668182</v>
       </c>
       <c r="R55" t="n">
-        <v>6703715</v>
+        <v>6703746</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6111,54 +6120,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624367</v>
+        <v>129624403</v>
       </c>
       <c r="B56" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668253</v>
+        <v>668258</v>
       </c>
       <c r="R56" t="n">
-        <v>6703781</v>
+        <v>6703763</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624339</v>
+        <v>129624400</v>
       </c>
       <c r="B57" t="n">
-        <v>98752</v>
+        <v>100963</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668166</v>
+        <v>668331</v>
       </c>
       <c r="R57" t="n">
-        <v>6703694</v>
+        <v>6703743</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B62" t="n">
-        <v>97020</v>
+        <v>100963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R62" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B63" t="n">
-        <v>100963</v>
+        <v>97020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R63" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624301</v>
+        <v>129624389</v>
       </c>
       <c r="B64" t="n">
-        <v>101870</v>
+        <v>100963</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668194</v>
+        <v>668107</v>
       </c>
       <c r="R64" t="n">
-        <v>6703673</v>
+        <v>6703910</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624389</v>
+        <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668107</v>
+        <v>668134</v>
       </c>
       <c r="R65" t="n">
-        <v>6703910</v>
+        <v>6703832</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7086,12 +7086,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7110,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624323</v>
+        <v>129624301</v>
       </c>
       <c r="B66" t="n">
-        <v>110905</v>
+        <v>101870</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7121,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7145,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668134</v>
+        <v>668194</v>
       </c>
       <c r="R66" t="n">
-        <v>6703832</v>
+        <v>6703673</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7183,18 +7189,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624391</v>
+        <v>129624346</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668163</v>
+        <v>668302</v>
       </c>
       <c r="R4" t="n">
-        <v>6703831</v>
+        <v>6703689</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624346</v>
+        <v>129624300</v>
       </c>
       <c r="B5" t="n">
-        <v>98752</v>
+        <v>101870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668302</v>
+        <v>668262</v>
       </c>
       <c r="R5" t="n">
-        <v>6703689</v>
+        <v>6703729</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624300</v>
+        <v>129624391</v>
       </c>
       <c r="B6" t="n">
-        <v>101870</v>
+        <v>100963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668262</v>
+        <v>668163</v>
       </c>
       <c r="R6" t="n">
-        <v>6703729</v>
+        <v>6703831</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624395</v>
+        <v>129624331</v>
       </c>
       <c r="B7" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668288</v>
+        <v>668257</v>
       </c>
       <c r="R7" t="n">
-        <v>6703696</v>
+        <v>6703774</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624399</v>
+        <v>129624343</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668154</v>
+        <v>668165</v>
       </c>
       <c r="R8" t="n">
-        <v>6703899</v>
+        <v>6703856</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624343</v>
+        <v>129624395</v>
       </c>
       <c r="B9" t="n">
-        <v>98752</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668165</v>
+        <v>668288</v>
       </c>
       <c r="R9" t="n">
-        <v>6703856</v>
+        <v>6703696</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624370</v>
+        <v>129624399</v>
       </c>
       <c r="B10" t="n">
-        <v>105840</v>
+        <v>100963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668108</v>
+        <v>668154</v>
       </c>
       <c r="R10" t="n">
-        <v>6703888</v>
+        <v>6703899</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,50 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624331</v>
+        <v>129624370</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>105840</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668257</v>
+        <v>668108</v>
       </c>
       <c r="R11" t="n">
-        <v>6703774</v>
+        <v>6703888</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624308</v>
+        <v>129624383</v>
       </c>
       <c r="B12" t="n">
-        <v>97020</v>
+        <v>92243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668162</v>
+        <v>668279</v>
       </c>
       <c r="R12" t="n">
-        <v>6703712</v>
+        <v>6703691</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1752,7 +1767,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624313</v>
+        <v>129624308</v>
       </c>
       <c r="B13" t="n">
         <v>97020</v>
@@ -1787,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668179</v>
+        <v>668162</v>
       </c>
       <c r="R13" t="n">
-        <v>6703790</v>
+        <v>6703712</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1833,21 +1848,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1864,32 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624383</v>
+        <v>129624313</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>97020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668279</v>
+        <v>668179</v>
       </c>
       <c r="R14" t="n">
-        <v>6703691</v>
+        <v>6703790</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624394</v>
+        <v>129624374</v>
       </c>
       <c r="B15" t="n">
-        <v>100963</v>
+        <v>4779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668270</v>
+        <v>668256</v>
       </c>
       <c r="R15" t="n">
-        <v>6703699</v>
+        <v>6703754</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2057,6 +2057,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2073,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624374</v>
+        <v>129624394</v>
       </c>
       <c r="B16" t="n">
-        <v>4779</v>
+        <v>100963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2099,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668256</v>
+        <v>668270</v>
       </c>
       <c r="R16" t="n">
-        <v>6703754</v>
+        <v>6703699</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2154,21 +2169,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2491,38 +2491,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624366</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2531,10 +2535,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668160</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703911</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2690,54 +2694,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624366</v>
+        <v>129624396</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668160</v>
+        <v>668305</v>
       </c>
       <c r="R22" t="n">
-        <v>6703911</v>
+        <v>6703732</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2796,45 +2791,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B23" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R23" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2990,50 +2990,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624328</v>
+        <v>129624368</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>105840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668312</v>
+        <v>668181</v>
       </c>
       <c r="R25" t="n">
-        <v>6703726</v>
+        <v>6703685</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3092,45 +3087,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624344</v>
+        <v>129624328</v>
       </c>
       <c r="B26" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668257</v>
+        <v>668312</v>
       </c>
       <c r="R26" t="n">
-        <v>6703688</v>
+        <v>6703726</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624368</v>
+        <v>129624344</v>
       </c>
       <c r="B27" t="n">
-        <v>105840</v>
+        <v>98752</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668181</v>
+        <v>668257</v>
       </c>
       <c r="R27" t="n">
-        <v>6703685</v>
+        <v>6703688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B30" t="n">
-        <v>87008</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,34 +3506,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R30" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3576,6 +3581,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3592,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624382</v>
+        <v>129624299</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>101870</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3603,39 +3623,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668266</v>
+        <v>668169</v>
       </c>
       <c r="R31" t="n">
-        <v>6703768</v>
+        <v>6703716</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3678,21 +3693,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3709,10 +3709,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B32" t="n">
-        <v>101870</v>
+        <v>87008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R32" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624311</v>
+        <v>129624320</v>
       </c>
       <c r="B34" t="n">
-        <v>97020</v>
+        <v>104245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668158</v>
+        <v>668289</v>
       </c>
       <c r="R34" t="n">
-        <v>6703911</v>
+        <v>6703690</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624320</v>
+        <v>129624311</v>
       </c>
       <c r="B35" t="n">
-        <v>104245</v>
+        <v>97020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668289</v>
+        <v>668158</v>
       </c>
       <c r="R35" t="n">
-        <v>6703690</v>
+        <v>6703911</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96216</v>
+        <v>96120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,43 +4220,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R37" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4315,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96120</v>
+        <v>96216</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,34 +4317,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R38" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624322</v>
+        <v>129624307</v>
       </c>
       <c r="B40" t="n">
-        <v>104245</v>
+        <v>97020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668300</v>
+        <v>668175</v>
       </c>
       <c r="R40" t="n">
         <v>6703703</v>
@@ -4606,32 +4606,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624345</v>
+        <v>129624318</v>
       </c>
       <c r="B41" t="n">
-        <v>98752</v>
+        <v>97020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668302</v>
+        <v>668185</v>
       </c>
       <c r="R41" t="n">
-        <v>6703713</v>
+        <v>6703684</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,6 +4687,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4703,7 +4718,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624340</v>
+        <v>129624345</v>
       </c>
       <c r="B42" t="n">
         <v>98752</v>
@@ -4738,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668169</v>
+        <v>668302</v>
       </c>
       <c r="R42" t="n">
-        <v>6703716</v>
+        <v>6703713</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4800,10 +4815,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624371</v>
+        <v>129624340</v>
       </c>
       <c r="B43" t="n">
-        <v>105840</v>
+        <v>98752</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,21 +4826,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4835,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668163</v>
+        <v>668169</v>
       </c>
       <c r="R43" t="n">
-        <v>6703870</v>
+        <v>6703716</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4897,32 +4912,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624307</v>
+        <v>129624322</v>
       </c>
       <c r="B44" t="n">
-        <v>97020</v>
+        <v>104245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4932,7 +4947,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668175</v>
+        <v>668300</v>
       </c>
       <c r="R44" t="n">
         <v>6703703</v>
@@ -4994,32 +5009,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624318</v>
+        <v>129624373</v>
       </c>
       <c r="B45" t="n">
-        <v>97020</v>
+        <v>4779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5029,10 +5044,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668185</v>
+        <v>668112</v>
       </c>
       <c r="R45" t="n">
-        <v>6703684</v>
+        <v>6703887</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5078,17 +5093,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5106,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624373</v>
+        <v>129624371</v>
       </c>
       <c r="B46" t="n">
-        <v>4779</v>
+        <v>105840</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5117,21 +5132,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5141,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668112</v>
+        <v>668163</v>
       </c>
       <c r="R46" t="n">
-        <v>6703887</v>
+        <v>6703870</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5187,21 +5202,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5315,32 +5315,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624397</v>
+        <v>129624349</v>
       </c>
       <c r="B48" t="n">
-        <v>100963</v>
+        <v>92046</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668305</v>
+        <v>668275</v>
       </c>
       <c r="R48" t="n">
-        <v>6703751</v>
+        <v>6703756</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5396,6 +5396,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5412,45 +5427,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624349</v>
+        <v>129624327</v>
       </c>
       <c r="B49" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668275</v>
+        <v>668173</v>
       </c>
       <c r="R49" t="n">
-        <v>6703756</v>
+        <v>6703787</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5493,21 +5513,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5524,50 +5529,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624327</v>
+        <v>129624397</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668173</v>
+        <v>668305</v>
       </c>
       <c r="R50" t="n">
-        <v>6703787</v>
+        <v>6703751</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5626,45 +5626,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624348</v>
+        <v>129624367</v>
       </c>
       <c r="B51" t="n">
-        <v>91366</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668185</v>
+        <v>668253</v>
       </c>
       <c r="R51" t="n">
-        <v>6703715</v>
+        <v>6703781</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5723,10 +5732,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624339</v>
+        <v>129624393</v>
       </c>
       <c r="B52" t="n">
-        <v>98752</v>
+        <v>100963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5734,21 +5743,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5758,10 +5767,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668166</v>
+        <v>668182</v>
       </c>
       <c r="R52" t="n">
-        <v>6703694</v>
+        <v>6703746</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5917,54 +5926,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624367</v>
+        <v>129624403</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668253</v>
+        <v>668258</v>
       </c>
       <c r="R54" t="n">
-        <v>6703781</v>
+        <v>6703763</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,7 +6023,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624393</v>
+        <v>129624400</v>
       </c>
       <c r="B55" t="n">
         <v>100963</v>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668182</v>
+        <v>668331</v>
       </c>
       <c r="R55" t="n">
-        <v>6703746</v>
+        <v>6703743</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624403</v>
+        <v>129624348</v>
       </c>
       <c r="B56" t="n">
-        <v>100963</v>
+        <v>91366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6131,21 +6131,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668258</v>
+        <v>668185</v>
       </c>
       <c r="R56" t="n">
-        <v>6703763</v>
+        <v>6703715</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624400</v>
+        <v>129624339</v>
       </c>
       <c r="B57" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668331</v>
+        <v>668166</v>
       </c>
       <c r="R57" t="n">
-        <v>6703743</v>
+        <v>6703694</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624309</v>
+        <v>129624347</v>
       </c>
       <c r="B58" t="n">
-        <v>97020</v>
+        <v>98752</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668130</v>
+        <v>668269</v>
       </c>
       <c r="R58" t="n">
-        <v>6703878</v>
+        <v>6703736</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6411,7 +6411,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624317</v>
+        <v>129624309</v>
       </c>
       <c r="B59" t="n">
         <v>97020</v>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668229</v>
+        <v>668130</v>
       </c>
       <c r="R59" t="n">
-        <v>6703722</v>
+        <v>6703878</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624347</v>
+        <v>129624317</v>
       </c>
       <c r="B60" t="n">
-        <v>98752</v>
+        <v>97020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668269</v>
+        <v>668229</v>
       </c>
       <c r="R60" t="n">
-        <v>6703736</v>
+        <v>6703722</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624389</v>
+        <v>129624323</v>
       </c>
       <c r="B64" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668107</v>
+        <v>668134</v>
       </c>
       <c r="R64" t="n">
-        <v>6703910</v>
+        <v>6703832</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6989,12 +6989,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7013,10 +7019,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624323</v>
+        <v>129624301</v>
       </c>
       <c r="B65" t="n">
-        <v>110905</v>
+        <v>101870</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7030,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7054,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668134</v>
+        <v>668194</v>
       </c>
       <c r="R65" t="n">
-        <v>6703832</v>
+        <v>6703673</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7086,18 +7092,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624301</v>
+        <v>129624389</v>
       </c>
       <c r="B66" t="n">
-        <v>101870</v>
+        <v>100963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668194</v>
+        <v>668107</v>
       </c>
       <c r="R66" t="n">
-        <v>6703673</v>
+        <v>6703910</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624346</v>
+        <v>129624300</v>
       </c>
       <c r="B4" t="n">
-        <v>98752</v>
+        <v>101870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668302</v>
+        <v>668262</v>
       </c>
       <c r="R4" t="n">
-        <v>6703689</v>
+        <v>6703729</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624300</v>
+        <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>101870</v>
+        <v>98752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668262</v>
+        <v>668302</v>
       </c>
       <c r="R5" t="n">
-        <v>6703729</v>
+        <v>6703689</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624383</v>
+        <v>129624308</v>
       </c>
       <c r="B12" t="n">
-        <v>92243</v>
+        <v>97020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668279</v>
+        <v>668162</v>
       </c>
       <c r="R12" t="n">
-        <v>6703691</v>
+        <v>6703712</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1736,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1767,7 +1752,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624308</v>
+        <v>129624313</v>
       </c>
       <c r="B13" t="n">
         <v>97020</v>
@@ -1802,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668162</v>
+        <v>668179</v>
       </c>
       <c r="R13" t="n">
-        <v>6703712</v>
+        <v>6703790</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1848,6 +1833,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1864,32 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624313</v>
+        <v>129624383</v>
       </c>
       <c r="B14" t="n">
-        <v>97020</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668179</v>
+        <v>668279</v>
       </c>
       <c r="R14" t="n">
-        <v>6703790</v>
+        <v>6703691</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2491,42 +2491,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624366</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2535,10 +2531,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668160</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703911</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2694,45 +2690,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624396</v>
+        <v>129624366</v>
       </c>
       <c r="B22" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668305</v>
+        <v>668160</v>
       </c>
       <c r="R22" t="n">
-        <v>6703732</v>
+        <v>6703911</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,50 +2796,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R23" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2893,45 +2893,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624401</v>
+        <v>129624328</v>
       </c>
       <c r="B24" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668293</v>
+        <v>668312</v>
       </c>
       <c r="R24" t="n">
-        <v>6703720</v>
+        <v>6703726</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3087,50 +3092,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624328</v>
+        <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668312</v>
+        <v>668257</v>
       </c>
       <c r="R26" t="n">
-        <v>6703726</v>
+        <v>6703688</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B27" t="n">
-        <v>98752</v>
+        <v>100963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R27" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3495,50 +3495,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624382</v>
+        <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>97020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668266</v>
+        <v>668277</v>
       </c>
       <c r="R30" t="n">
-        <v>6703768</v>
+        <v>6703748</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3584,17 +3579,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3612,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B31" t="n">
-        <v>101870</v>
+        <v>87008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R31" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3709,10 +3704,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B32" t="n">
-        <v>87008</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,34 +3715,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R32" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3790,6 +3790,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3806,32 +3821,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624315</v>
+        <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>101870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668277</v>
+        <v>668169</v>
       </c>
       <c r="R33" t="n">
-        <v>6703748</v>
+        <v>6703716</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3887,21 +3902,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624320</v>
+        <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>104245</v>
+        <v>97020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668289</v>
+        <v>668158</v>
       </c>
       <c r="R34" t="n">
-        <v>6703690</v>
+        <v>6703911</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624311</v>
+        <v>129624296</v>
       </c>
       <c r="B35" t="n">
-        <v>97020</v>
+        <v>101870</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668158</v>
+        <v>668152</v>
       </c>
       <c r="R35" t="n">
-        <v>6703911</v>
+        <v>6703756</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624296</v>
+        <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>101870</v>
+        <v>104245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668152</v>
+        <v>668289</v>
       </c>
       <c r="R36" t="n">
-        <v>6703756</v>
+        <v>6703690</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B37" t="n">
-        <v>96120</v>
+        <v>96216</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,34 +4220,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R37" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4315,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B38" t="n">
-        <v>96216</v>
+        <v>96120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,43 +4326,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R38" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624307</v>
+        <v>129624373</v>
       </c>
       <c r="B40" t="n">
-        <v>97020</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668175</v>
+        <v>668112</v>
       </c>
       <c r="R40" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,6 +4590,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4606,32 +4621,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624318</v>
+        <v>129624345</v>
       </c>
       <c r="B41" t="n">
-        <v>97020</v>
+        <v>98752</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668185</v>
+        <v>668302</v>
       </c>
       <c r="R41" t="n">
-        <v>6703684</v>
+        <v>6703713</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,21 +4702,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,7 +4718,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624345</v>
+        <v>129624340</v>
       </c>
       <c r="B42" t="n">
         <v>98752</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668302</v>
+        <v>668169</v>
       </c>
       <c r="R42" t="n">
-        <v>6703713</v>
+        <v>6703716</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624340</v>
+        <v>129624371</v>
       </c>
       <c r="B43" t="n">
-        <v>98752</v>
+        <v>105840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668169</v>
+        <v>668163</v>
       </c>
       <c r="R43" t="n">
-        <v>6703716</v>
+        <v>6703870</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5009,32 +5009,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624373</v>
+        <v>129624307</v>
       </c>
       <c r="B45" t="n">
-        <v>4779</v>
+        <v>97020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668112</v>
+        <v>668175</v>
       </c>
       <c r="R45" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5090,21 +5090,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5121,32 +5106,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624371</v>
+        <v>129624318</v>
       </c>
       <c r="B46" t="n">
-        <v>105840</v>
+        <v>97020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668163</v>
+        <v>668185</v>
       </c>
       <c r="R46" t="n">
-        <v>6703870</v>
+        <v>6703684</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5202,6 +5187,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5315,45 +5315,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624349</v>
+        <v>129624327</v>
       </c>
       <c r="B48" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668275</v>
+        <v>668173</v>
       </c>
       <c r="R48" t="n">
-        <v>6703756</v>
+        <v>6703787</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5396,21 +5401,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5427,50 +5417,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>92046</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R49" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5513,6 +5498,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5626,54 +5626,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624367</v>
+        <v>129624393</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668253</v>
+        <v>668182</v>
       </c>
       <c r="R51" t="n">
-        <v>6703781</v>
+        <v>6703746</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5732,7 +5723,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624393</v>
+        <v>129624385</v>
       </c>
       <c r="B52" t="n">
         <v>100963</v>
@@ -5767,10 +5758,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668182</v>
+        <v>668149</v>
       </c>
       <c r="R52" t="n">
-        <v>6703746</v>
+        <v>6703811</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5829,7 +5820,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624385</v>
+        <v>129624403</v>
       </c>
       <c r="B53" t="n">
         <v>100963</v>
@@ -5864,10 +5855,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668149</v>
+        <v>668258</v>
       </c>
       <c r="R53" t="n">
-        <v>6703811</v>
+        <v>6703763</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,7 +5917,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624403</v>
+        <v>129624400</v>
       </c>
       <c r="B54" t="n">
         <v>100963</v>
@@ -5961,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668258</v>
+        <v>668331</v>
       </c>
       <c r="R54" t="n">
-        <v>6703763</v>
+        <v>6703743</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,10 +6014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624400</v>
+        <v>129624348</v>
       </c>
       <c r="B55" t="n">
-        <v>100963</v>
+        <v>91366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6034,21 +6025,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6058,10 +6049,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668331</v>
+        <v>668185</v>
       </c>
       <c r="R55" t="n">
-        <v>6703743</v>
+        <v>6703715</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,45 +6111,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624348</v>
+        <v>129624367</v>
       </c>
       <c r="B56" t="n">
-        <v>91366</v>
+        <v>98774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668185</v>
+        <v>668253</v>
       </c>
       <c r="R56" t="n">
-        <v>6703715</v>
+        <v>6703781</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624347</v>
+        <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>98752</v>
+        <v>97020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668269</v>
+        <v>668130</v>
       </c>
       <c r="R58" t="n">
-        <v>6703736</v>
+        <v>6703878</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6411,7 +6411,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624309</v>
+        <v>129624317</v>
       </c>
       <c r="B59" t="n">
         <v>97020</v>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668130</v>
+        <v>668229</v>
       </c>
       <c r="R59" t="n">
-        <v>6703878</v>
+        <v>6703722</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624317</v>
+        <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>97020</v>
+        <v>98752</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668229</v>
+        <v>668269</v>
       </c>
       <c r="R60" t="n">
-        <v>6703722</v>
+        <v>6703736</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624323</v>
+        <v>129624301</v>
       </c>
       <c r="B64" t="n">
-        <v>110905</v>
+        <v>101870</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668134</v>
+        <v>668194</v>
       </c>
       <c r="R64" t="n">
-        <v>6703832</v>
+        <v>6703673</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6989,18 +6989,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7019,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624301</v>
+        <v>129624389</v>
       </c>
       <c r="B65" t="n">
-        <v>101870</v>
+        <v>100963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7030,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7054,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668194</v>
+        <v>668107</v>
       </c>
       <c r="R65" t="n">
-        <v>6703673</v>
+        <v>6703910</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7116,10 +7110,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624389</v>
+        <v>129624323</v>
       </c>
       <c r="B66" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7121,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7145,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668107</v>
+        <v>668134</v>
       </c>
       <c r="R66" t="n">
-        <v>6703910</v>
+        <v>6703832</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7189,12 +7183,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624330</v>
+        <v>129624300</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>101874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668289</v>
+        <v>668262</v>
       </c>
       <c r="R3" t="n">
-        <v>6703714</v>
+        <v>6703729</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624300</v>
+        <v>129624391</v>
       </c>
       <c r="B4" t="n">
-        <v>101870</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668262</v>
+        <v>668163</v>
       </c>
       <c r="R4" t="n">
-        <v>6703729</v>
+        <v>6703831</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624346</v>
+        <v>129624330</v>
       </c>
       <c r="B5" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668302</v>
+        <v>668289</v>
       </c>
       <c r="R5" t="n">
-        <v>6703689</v>
+        <v>6703714</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624391</v>
+        <v>129624346</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668163</v>
+        <v>668302</v>
       </c>
       <c r="R6" t="n">
-        <v>6703831</v>
+        <v>6703689</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624331</v>
+        <v>129624370</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>105844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668257</v>
+        <v>668108</v>
       </c>
       <c r="R7" t="n">
-        <v>6703774</v>
+        <v>6703888</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624343</v>
+        <v>129624395</v>
       </c>
       <c r="B8" t="n">
-        <v>98752</v>
+        <v>100967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668165</v>
+        <v>668288</v>
       </c>
       <c r="R8" t="n">
-        <v>6703856</v>
+        <v>6703696</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624395</v>
+        <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668288</v>
+        <v>668154</v>
       </c>
       <c r="R9" t="n">
-        <v>6703696</v>
+        <v>6703899</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,45 +1456,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624399</v>
+        <v>129624331</v>
       </c>
       <c r="B10" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668154</v>
+        <v>668257</v>
       </c>
       <c r="R10" t="n">
-        <v>6703899</v>
+        <v>6703774</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624370</v>
+        <v>129624343</v>
       </c>
       <c r="B11" t="n">
-        <v>105840</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668108</v>
+        <v>668165</v>
       </c>
       <c r="R11" t="n">
-        <v>6703888</v>
+        <v>6703856</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624308</v>
+        <v>129624374</v>
       </c>
       <c r="B12" t="n">
-        <v>97020</v>
+        <v>4779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668162</v>
+        <v>668256</v>
       </c>
       <c r="R12" t="n">
-        <v>6703712</v>
+        <v>6703754</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1752,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624313</v>
+        <v>129624308</v>
       </c>
       <c r="B13" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668179</v>
+        <v>668162</v>
       </c>
       <c r="R13" t="n">
-        <v>6703790</v>
+        <v>6703712</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1833,21 +1848,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1864,32 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624383</v>
+        <v>129624313</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>97024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668279</v>
+        <v>668179</v>
       </c>
       <c r="R14" t="n">
-        <v>6703691</v>
+        <v>6703790</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624374</v>
+        <v>129624383</v>
       </c>
       <c r="B15" t="n">
-        <v>4779</v>
+        <v>92247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668256</v>
+        <v>668279</v>
       </c>
       <c r="R15" t="n">
-        <v>6703754</v>
+        <v>6703691</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
         <v>129624394</v>
       </c>
       <c r="B16" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>129624392</v>
       </c>
       <c r="B18" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,50 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>100967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2593,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624297</v>
+        <v>129624329</v>
       </c>
       <c r="B21" t="n">
-        <v>101870</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668176</v>
+        <v>668230</v>
       </c>
       <c r="R21" t="n">
-        <v>6703677</v>
+        <v>6703725</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2690,54 +2690,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624366</v>
+        <v>129624297</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>101874</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668160</v>
+        <v>668176</v>
       </c>
       <c r="R22" t="n">
-        <v>6703911</v>
+        <v>6703677</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2796,45 +2787,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624396</v>
+        <v>129624366</v>
       </c>
       <c r="B23" t="n">
-        <v>100963</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668305</v>
+        <v>668160</v>
       </c>
       <c r="R23" t="n">
-        <v>6703732</v>
+        <v>6703911</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2893,50 +2893,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624328</v>
+        <v>129624344</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668312</v>
+        <v>668257</v>
       </c>
       <c r="R24" t="n">
-        <v>6703726</v>
+        <v>6703688</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2998,7 +2993,7 @@
         <v>129624368</v>
       </c>
       <c r="B25" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,45 +3087,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624344</v>
+        <v>129624328</v>
       </c>
       <c r="B26" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668257</v>
+        <v>668312</v>
       </c>
       <c r="R26" t="n">
-        <v>6703688</v>
+        <v>6703726</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3192,7 +3192,7 @@
         <v>129624401</v>
       </c>
       <c r="B27" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,32 +3286,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624388</v>
+        <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>100963</v>
+        <v>97024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668122</v>
+        <v>668262</v>
       </c>
       <c r="R28" t="n">
-        <v>6703878</v>
+        <v>6703727</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,6 +3367,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3383,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624316</v>
+        <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>97020</v>
+        <v>100967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3418,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668262</v>
+        <v>668122</v>
       </c>
       <c r="R29" t="n">
-        <v>6703727</v>
+        <v>6703878</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3464,21 +3479,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3495,32 +3495,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624315</v>
+        <v>129624299</v>
       </c>
       <c r="B30" t="n">
-        <v>97020</v>
+        <v>101874</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668277</v>
+        <v>668169</v>
       </c>
       <c r="R30" t="n">
-        <v>6703748</v>
+        <v>6703716</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3576,21 +3576,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3610,7 +3595,7 @@
         <v>129624404</v>
       </c>
       <c r="B31" t="n">
-        <v>87008</v>
+        <v>87012</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3821,32 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624299</v>
+        <v>129624315</v>
       </c>
       <c r="B33" t="n">
-        <v>101870</v>
+        <v>97024</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668169</v>
+        <v>668277</v>
       </c>
       <c r="R33" t="n">
-        <v>6703716</v>
+        <v>6703748</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3902,6 +3887,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624311</v>
+        <v>129624296</v>
       </c>
       <c r="B34" t="n">
-        <v>97020</v>
+        <v>101874</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668158</v>
+        <v>668152</v>
       </c>
       <c r="R34" t="n">
-        <v>6703911</v>
+        <v>6703756</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624296</v>
+        <v>129624311</v>
       </c>
       <c r="B35" t="n">
-        <v>101870</v>
+        <v>97024</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668152</v>
+        <v>668158</v>
       </c>
       <c r="R35" t="n">
-        <v>6703756</v>
+        <v>6703911</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4115,7 +4115,7 @@
         <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>104245</v>
+        <v>104249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96216</v>
+        <v>96124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,43 +4220,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R37" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4315,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96120</v>
+        <v>96220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,34 +4317,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R38" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4415,7 +4415,7 @@
         <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624373</v>
+        <v>129624318</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>97024</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668112</v>
+        <v>668185</v>
       </c>
       <c r="R40" t="n">
-        <v>6703887</v>
+        <v>6703684</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,17 +4593,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4621,32 +4621,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624345</v>
+        <v>129624307</v>
       </c>
       <c r="B41" t="n">
-        <v>98752</v>
+        <v>97024</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668302</v>
+        <v>668175</v>
       </c>
       <c r="R41" t="n">
-        <v>6703713</v>
+        <v>6703703</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4718,10 +4718,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624340</v>
+        <v>129624373</v>
       </c>
       <c r="B42" t="n">
-        <v>98752</v>
+        <v>4779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668169</v>
+        <v>668112</v>
       </c>
       <c r="R42" t="n">
-        <v>6703716</v>
+        <v>6703887</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,6 +4799,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4815,10 +4830,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624371</v>
+        <v>129624345</v>
       </c>
       <c r="B43" t="n">
-        <v>105840</v>
+        <v>98756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,21 +4841,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4865,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668163</v>
+        <v>668302</v>
       </c>
       <c r="R43" t="n">
-        <v>6703870</v>
+        <v>6703713</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4912,10 +4927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624322</v>
+        <v>129624340</v>
       </c>
       <c r="B44" t="n">
-        <v>104245</v>
+        <v>98756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4923,21 +4938,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4947,10 +4962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668300</v>
+        <v>668169</v>
       </c>
       <c r="R44" t="n">
-        <v>6703703</v>
+        <v>6703716</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5009,32 +5024,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624307</v>
+        <v>129624371</v>
       </c>
       <c r="B45" t="n">
-        <v>97020</v>
+        <v>105844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5044,10 +5059,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668175</v>
+        <v>668163</v>
       </c>
       <c r="R45" t="n">
-        <v>6703703</v>
+        <v>6703870</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5106,32 +5121,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624318</v>
+        <v>129624322</v>
       </c>
       <c r="B46" t="n">
-        <v>97020</v>
+        <v>104249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5141,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668185</v>
+        <v>668300</v>
       </c>
       <c r="R46" t="n">
-        <v>6703684</v>
+        <v>6703703</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5187,21 +5202,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101870</v>
+        <v>101874</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5315,50 +5315,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>92050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R48" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5401,6 +5396,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5417,45 +5427,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624349</v>
+        <v>129624327</v>
       </c>
       <c r="B49" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668275</v>
+        <v>668173</v>
       </c>
       <c r="R49" t="n">
-        <v>6703756</v>
+        <v>6703787</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5498,21 +5513,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5532,7 +5532,7 @@
         <v>129624397</v>
       </c>
       <c r="B50" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5626,10 +5626,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624393</v>
+        <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>100963</v>
+        <v>91370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668182</v>
+        <v>668185</v>
       </c>
       <c r="R51" t="n">
-        <v>6703746</v>
+        <v>6703715</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624385</v>
+        <v>129624339</v>
       </c>
       <c r="B52" t="n">
-        <v>100963</v>
+        <v>98756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668149</v>
+        <v>668166</v>
       </c>
       <c r="R52" t="n">
-        <v>6703811</v>
+        <v>6703694</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,45 +5820,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624403</v>
+        <v>129624367</v>
       </c>
       <c r="B53" t="n">
-        <v>100963</v>
+        <v>98778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668258</v>
+        <v>668253</v>
       </c>
       <c r="R53" t="n">
-        <v>6703763</v>
+        <v>6703781</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5917,10 +5926,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624400</v>
+        <v>129624393</v>
       </c>
       <c r="B54" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5952,10 +5961,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668331</v>
+        <v>668182</v>
       </c>
       <c r="R54" t="n">
-        <v>6703743</v>
+        <v>6703746</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6014,10 +6023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624348</v>
+        <v>129624385</v>
       </c>
       <c r="B55" t="n">
-        <v>91366</v>
+        <v>100967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6025,21 +6034,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6049,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668185</v>
+        <v>668149</v>
       </c>
       <c r="R55" t="n">
-        <v>6703715</v>
+        <v>6703811</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6111,54 +6120,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624367</v>
+        <v>129624403</v>
       </c>
       <c r="B56" t="n">
-        <v>98774</v>
+        <v>100967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668253</v>
+        <v>668258</v>
       </c>
       <c r="R56" t="n">
-        <v>6703781</v>
+        <v>6703763</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624339</v>
+        <v>129624400</v>
       </c>
       <c r="B57" t="n">
-        <v>98752</v>
+        <v>100967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668166</v>
+        <v>668331</v>
       </c>
       <c r="R57" t="n">
-        <v>6703694</v>
+        <v>6703743</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624309</v>
+        <v>129624347</v>
       </c>
       <c r="B58" t="n">
-        <v>97020</v>
+        <v>98756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668130</v>
+        <v>668269</v>
       </c>
       <c r="R58" t="n">
-        <v>6703878</v>
+        <v>6703736</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624317</v>
+        <v>129624309</v>
       </c>
       <c r="B59" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668229</v>
+        <v>668130</v>
       </c>
       <c r="R59" t="n">
-        <v>6703722</v>
+        <v>6703878</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624347</v>
+        <v>129624317</v>
       </c>
       <c r="B60" t="n">
-        <v>98752</v>
+        <v>97024</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668269</v>
+        <v>668229</v>
       </c>
       <c r="R60" t="n">
-        <v>6703736</v>
+        <v>6703722</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>100963</v>
+        <v>97024</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R62" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>97020</v>
+        <v>100967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R63" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6919,7 +6919,7 @@
         <v>129624301</v>
       </c>
       <c r="B64" t="n">
-        <v>101870</v>
+        <v>101874</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624389</v>
+        <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>100963</v>
+        <v>110909</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668107</v>
+        <v>668134</v>
       </c>
       <c r="R65" t="n">
-        <v>6703910</v>
+        <v>6703832</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7086,12 +7086,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7110,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624323</v>
+        <v>129624389</v>
       </c>
       <c r="B66" t="n">
-        <v>110905</v>
+        <v>100967</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7121,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7145,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668134</v>
+        <v>668107</v>
       </c>
       <c r="R66" t="n">
-        <v>6703832</v>
+        <v>6703910</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7183,18 +7189,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624300</v>
+        <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>101874</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668262</v>
+        <v>668289</v>
       </c>
       <c r="R3" t="n">
-        <v>6703729</v>
+        <v>6703714</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +877,7 @@
         <v>129624391</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,50 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624330</v>
+        <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>98758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668289</v>
+        <v>668302</v>
       </c>
       <c r="R5" t="n">
-        <v>6703714</v>
+        <v>6703689</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624346</v>
+        <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>101876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668302</v>
+        <v>668262</v>
       </c>
       <c r="R6" t="n">
-        <v>6703689</v>
+        <v>6703729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624370</v>
+        <v>129624343</v>
       </c>
       <c r="B7" t="n">
-        <v>105844</v>
+        <v>98758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668108</v>
+        <v>668165</v>
       </c>
       <c r="R7" t="n">
-        <v>6703888</v>
+        <v>6703856</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1265,7 +1265,7 @@
         <v>129624395</v>
       </c>
       <c r="B8" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,50 +1456,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624331</v>
+        <v>129624370</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>105846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668257</v>
+        <v>668108</v>
       </c>
       <c r="R10" t="n">
-        <v>6703774</v>
+        <v>6703888</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,45 +1553,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624343</v>
+        <v>129624331</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668165</v>
+        <v>668257</v>
       </c>
       <c r="R11" t="n">
-        <v>6703856</v>
+        <v>6703774</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624374</v>
+        <v>129624308</v>
       </c>
       <c r="B12" t="n">
-        <v>4779</v>
+        <v>97026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668256</v>
+        <v>668162</v>
       </c>
       <c r="R12" t="n">
-        <v>6703754</v>
+        <v>6703712</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1736,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1767,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624308</v>
+        <v>129624313</v>
       </c>
       <c r="B13" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668162</v>
+        <v>668179</v>
       </c>
       <c r="R13" t="n">
-        <v>6703712</v>
+        <v>6703790</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1848,6 +1833,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1864,32 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624313</v>
+        <v>129624383</v>
       </c>
       <c r="B14" t="n">
-        <v>97024</v>
+        <v>92249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668179</v>
+        <v>668279</v>
       </c>
       <c r="R14" t="n">
-        <v>6703790</v>
+        <v>6703691</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624383</v>
+        <v>129624374</v>
       </c>
       <c r="B15" t="n">
-        <v>92247</v>
+        <v>4779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668279</v>
+        <v>668256</v>
       </c>
       <c r="R15" t="n">
-        <v>6703691</v>
+        <v>6703754</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
         <v>129624394</v>
       </c>
       <c r="B16" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>129624392</v>
       </c>
       <c r="B18" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,45 +2491,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>100967</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2588,50 +2593,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>100969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R21" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2693,7 +2693,7 @@
         <v>129624297</v>
       </c>
       <c r="B22" t="n">
-        <v>101874</v>
+        <v>101876</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>129624366</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>100969</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R24" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2990,45 +2990,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624368</v>
+        <v>129624328</v>
       </c>
       <c r="B25" t="n">
-        <v>105844</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668181</v>
+        <v>668312</v>
       </c>
       <c r="R25" t="n">
-        <v>6703685</v>
+        <v>6703726</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3087,50 +3092,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624328</v>
+        <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>98758</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668312</v>
+        <v>668257</v>
       </c>
       <c r="R26" t="n">
-        <v>6703726</v>
+        <v>6703688</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624401</v>
+        <v>129624368</v>
       </c>
       <c r="B27" t="n">
-        <v>100967</v>
+        <v>105846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668293</v>
+        <v>668181</v>
       </c>
       <c r="R27" t="n">
-        <v>6703720</v>
+        <v>6703685</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3286,32 +3286,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624316</v>
+        <v>129624388</v>
       </c>
       <c r="B28" t="n">
-        <v>97024</v>
+        <v>100969</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668262</v>
+        <v>668122</v>
       </c>
       <c r="R28" t="n">
-        <v>6703727</v>
+        <v>6703878</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,21 +3367,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3398,32 +3383,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624388</v>
+        <v>129624316</v>
       </c>
       <c r="B29" t="n">
-        <v>100967</v>
+        <v>97026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668122</v>
+        <v>668262</v>
       </c>
       <c r="R29" t="n">
-        <v>6703878</v>
+        <v>6703727</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3479,6 +3464,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3495,10 +3495,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624299</v>
+        <v>129624382</v>
       </c>
       <c r="B30" t="n">
-        <v>101874</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,34 +3506,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668169</v>
+        <v>668266</v>
       </c>
       <c r="R30" t="n">
-        <v>6703716</v>
+        <v>6703768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3576,6 +3581,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3592,32 +3612,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624404</v>
+        <v>129624315</v>
       </c>
       <c r="B31" t="n">
-        <v>87012</v>
+        <v>97026</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3627,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668299</v>
+        <v>668277</v>
       </c>
       <c r="R31" t="n">
-        <v>6703709</v>
+        <v>6703748</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3673,6 +3693,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3689,10 +3724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624382</v>
+        <v>129624404</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>87014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3700,39 +3735,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668266</v>
+        <v>668299</v>
       </c>
       <c r="R32" t="n">
-        <v>6703768</v>
+        <v>6703709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3775,21 +3805,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3806,32 +3821,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624315</v>
+        <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>97024</v>
+        <v>101876</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668277</v>
+        <v>668169</v>
       </c>
       <c r="R33" t="n">
-        <v>6703748</v>
+        <v>6703716</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3887,21 +3902,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624296</v>
+        <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>101874</v>
+        <v>97026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668152</v>
+        <v>668158</v>
       </c>
       <c r="R34" t="n">
-        <v>6703756</v>
+        <v>6703911</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624311</v>
+        <v>129624320</v>
       </c>
       <c r="B35" t="n">
-        <v>97024</v>
+        <v>104251</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668158</v>
+        <v>668289</v>
       </c>
       <c r="R35" t="n">
-        <v>6703911</v>
+        <v>6703690</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624320</v>
+        <v>129624296</v>
       </c>
       <c r="B36" t="n">
-        <v>104249</v>
+        <v>101876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668289</v>
+        <v>668152</v>
       </c>
       <c r="R36" t="n">
-        <v>6703690</v>
+        <v>6703756</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4212,7 +4212,7 @@
         <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624318</v>
+        <v>129624307</v>
       </c>
       <c r="B40" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668185</v>
+        <v>668175</v>
       </c>
       <c r="R40" t="n">
-        <v>6703684</v>
+        <v>6703703</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,21 +4590,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4621,10 +4606,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624307</v>
+        <v>129624318</v>
       </c>
       <c r="B41" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4656,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668175</v>
+        <v>668185</v>
       </c>
       <c r="R41" t="n">
-        <v>6703703</v>
+        <v>6703684</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4702,6 +4687,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4830,10 +4830,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624345</v>
+        <v>129624371</v>
       </c>
       <c r="B43" t="n">
-        <v>98756</v>
+        <v>105846</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4841,21 +4841,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668302</v>
+        <v>668163</v>
       </c>
       <c r="R43" t="n">
-        <v>6703713</v>
+        <v>6703870</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4927,10 +4927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624340</v>
+        <v>129624345</v>
       </c>
       <c r="B44" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,10 +4962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668169</v>
+        <v>668302</v>
       </c>
       <c r="R44" t="n">
-        <v>6703716</v>
+        <v>6703713</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5024,10 +5024,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624371</v>
+        <v>129624340</v>
       </c>
       <c r="B45" t="n">
-        <v>105844</v>
+        <v>98758</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5035,21 +5035,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668163</v>
+        <v>668169</v>
       </c>
       <c r="R45" t="n">
-        <v>6703870</v>
+        <v>6703716</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5124,7 +5124,7 @@
         <v>129624322</v>
       </c>
       <c r="B46" t="n">
-        <v>104249</v>
+        <v>104251</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101874</v>
+        <v>101876</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5315,32 +5315,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624349</v>
+        <v>129624397</v>
       </c>
       <c r="B48" t="n">
-        <v>92050</v>
+        <v>100969</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668275</v>
+        <v>668305</v>
       </c>
       <c r="R48" t="n">
-        <v>6703756</v>
+        <v>6703751</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5396,21 +5396,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5427,50 +5412,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R49" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5513,6 +5493,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5529,45 +5524,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624397</v>
+        <v>129624327</v>
       </c>
       <c r="B50" t="n">
-        <v>100967</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668305</v>
+        <v>668173</v>
       </c>
       <c r="R50" t="n">
-        <v>6703751</v>
+        <v>6703787</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5629,7 +5629,7 @@
         <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5723,45 +5723,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624339</v>
+        <v>129624367</v>
       </c>
       <c r="B52" t="n">
-        <v>98756</v>
+        <v>98780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668166</v>
+        <v>668253</v>
       </c>
       <c r="R52" t="n">
-        <v>6703694</v>
+        <v>6703781</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,54 +5829,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624367</v>
+        <v>129624339</v>
       </c>
       <c r="B53" t="n">
-        <v>98778</v>
+        <v>98758</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668253</v>
+        <v>668166</v>
       </c>
       <c r="R53" t="n">
-        <v>6703781</v>
+        <v>6703694</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5929,7 +5929,7 @@
         <v>129624393</v>
       </c>
       <c r="B54" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>129624385</v>
       </c>
       <c r="B55" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129624403</v>
       </c>
       <c r="B56" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>129624400</v>
       </c>
       <c r="B57" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624347</v>
+        <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>98756</v>
+        <v>97026</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668269</v>
+        <v>668130</v>
       </c>
       <c r="R58" t="n">
-        <v>6703736</v>
+        <v>6703878</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624309</v>
+        <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668130</v>
+        <v>668229</v>
       </c>
       <c r="R59" t="n">
-        <v>6703878</v>
+        <v>6703722</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624317</v>
+        <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>97024</v>
+        <v>98758</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668229</v>
+        <v>668269</v>
       </c>
       <c r="R60" t="n">
-        <v>6703722</v>
+        <v>6703736</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B62" t="n">
-        <v>97024</v>
+        <v>100969</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R62" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B63" t="n">
-        <v>100967</v>
+        <v>97026</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R63" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6919,7 +6919,7 @@
         <v>129624301</v>
       </c>
       <c r="B64" t="n">
-        <v>101874</v>
+        <v>101876</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>110909</v>
+        <v>110911</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>129624389</v>
       </c>
       <c r="B66" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624330</v>
+        <v>129624346</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>98758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668289</v>
+        <v>668302</v>
       </c>
       <c r="R3" t="n">
-        <v>6703714</v>
+        <v>6703689</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624346</v>
+        <v>129624300</v>
       </c>
       <c r="B5" t="n">
-        <v>98758</v>
+        <v>101876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668302</v>
+        <v>668262</v>
       </c>
       <c r="R5" t="n">
-        <v>6703689</v>
+        <v>6703729</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,45 +1063,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624300</v>
+        <v>129624330</v>
       </c>
       <c r="B6" t="n">
-        <v>101876</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668262</v>
+        <v>668289</v>
       </c>
       <c r="R6" t="n">
-        <v>6703729</v>
+        <v>6703714</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -3495,50 +3495,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624382</v>
+        <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>97026</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668266</v>
+        <v>668277</v>
       </c>
       <c r="R30" t="n">
-        <v>6703768</v>
+        <v>6703748</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3584,17 +3579,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3612,45 +3607,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624315</v>
+        <v>129624382</v>
       </c>
       <c r="B31" t="n">
-        <v>97026</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668277</v>
+        <v>668266</v>
       </c>
       <c r="R31" t="n">
-        <v>6703748</v>
+        <v>6703768</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624325</v>
+        <v>129624369</v>
       </c>
       <c r="B37" t="n">
-        <v>96126</v>
+        <v>105846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,21 +4220,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668318</v>
+        <v>668127</v>
       </c>
       <c r="R37" t="n">
-        <v>6703714</v>
+        <v>6703878</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B38" t="n">
-        <v>96222</v>
+        <v>96126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,43 +4317,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R38" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4412,10 +4403,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129624369</v>
+        <v>129624372</v>
       </c>
       <c r="B39" t="n">
-        <v>105846</v>
+        <v>96222</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,34 +4414,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668127</v>
+        <v>668296</v>
       </c>
       <c r="R39" t="n">
-        <v>6703878</v>
+        <v>6703695</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624307</v>
+        <v>129624371</v>
       </c>
       <c r="B40" t="n">
-        <v>97026</v>
+        <v>105846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668175</v>
+        <v>668163</v>
       </c>
       <c r="R40" t="n">
-        <v>6703703</v>
+        <v>6703870</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4606,32 +4606,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624318</v>
+        <v>129624345</v>
       </c>
       <c r="B41" t="n">
-        <v>97026</v>
+        <v>98758</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668185</v>
+        <v>668302</v>
       </c>
       <c r="R41" t="n">
-        <v>6703684</v>
+        <v>6703713</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,21 +4687,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,10 +4703,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624373</v>
+        <v>129624340</v>
       </c>
       <c r="B42" t="n">
-        <v>4779</v>
+        <v>98758</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4714,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4738,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668112</v>
+        <v>668169</v>
       </c>
       <c r="R42" t="n">
-        <v>6703887</v>
+        <v>6703716</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,21 +4784,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4830,10 +4800,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624371</v>
+        <v>129624322</v>
       </c>
       <c r="B43" t="n">
-        <v>105846</v>
+        <v>104251</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4841,21 +4811,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>222412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4865,10 +4835,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668163</v>
+        <v>668300</v>
       </c>
       <c r="R43" t="n">
-        <v>6703870</v>
+        <v>6703703</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4927,32 +4897,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624345</v>
+        <v>129624307</v>
       </c>
       <c r="B44" t="n">
-        <v>98758</v>
+        <v>97026</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4962,10 +4932,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668302</v>
+        <v>668175</v>
       </c>
       <c r="R44" t="n">
-        <v>6703713</v>
+        <v>6703703</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5024,32 +4994,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624340</v>
+        <v>129624318</v>
       </c>
       <c r="B45" t="n">
-        <v>98758</v>
+        <v>97026</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5059,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668169</v>
+        <v>668185</v>
       </c>
       <c r="R45" t="n">
-        <v>6703716</v>
+        <v>6703684</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5105,6 +5075,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5121,10 +5106,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624322</v>
+        <v>129624373</v>
       </c>
       <c r="B46" t="n">
-        <v>104251</v>
+        <v>4779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,21 +5117,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668300</v>
+        <v>668112</v>
       </c>
       <c r="R46" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5202,6 +5187,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624346</v>
+        <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>98758</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668302</v>
+        <v>668289</v>
       </c>
       <c r="R3" t="n">
-        <v>6703689</v>
+        <v>6703714</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624300</v>
+        <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>101876</v>
+        <v>98758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668262</v>
+        <v>668302</v>
       </c>
       <c r="R5" t="n">
-        <v>6703729</v>
+        <v>6703689</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,50 +1068,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624330</v>
+        <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>101876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668289</v>
+        <v>668262</v>
       </c>
       <c r="R6" t="n">
-        <v>6703714</v>
+        <v>6703729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624343</v>
+        <v>129624331</v>
       </c>
       <c r="B7" t="n">
-        <v>98758</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668165</v>
+        <v>668257</v>
       </c>
       <c r="R7" t="n">
-        <v>6703856</v>
+        <v>6703774</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624395</v>
+        <v>129624343</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>98758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668288</v>
+        <v>668165</v>
       </c>
       <c r="R8" t="n">
-        <v>6703696</v>
+        <v>6703856</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624399</v>
+        <v>129624395</v>
       </c>
       <c r="B9" t="n">
         <v>100969</v>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668154</v>
+        <v>668288</v>
       </c>
       <c r="R9" t="n">
-        <v>6703899</v>
+        <v>6703696</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624370</v>
+        <v>129624399</v>
       </c>
       <c r="B10" t="n">
-        <v>105846</v>
+        <v>100969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668108</v>
+        <v>668154</v>
       </c>
       <c r="R10" t="n">
-        <v>6703888</v>
+        <v>6703899</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,50 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624331</v>
+        <v>129624370</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>105846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668257</v>
+        <v>668108</v>
       </c>
       <c r="R11" t="n">
-        <v>6703774</v>
+        <v>6703888</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624382</v>
+        <v>129624404</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>87014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,39 +3618,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668266</v>
+        <v>668299</v>
       </c>
       <c r="R31" t="n">
-        <v>6703768</v>
+        <v>6703709</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3693,21 +3688,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3724,10 +3704,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624404</v>
+        <v>129624299</v>
       </c>
       <c r="B32" t="n">
-        <v>87014</v>
+        <v>101876</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,21 +3715,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3759,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668299</v>
+        <v>668169</v>
       </c>
       <c r="R32" t="n">
-        <v>6703709</v>
+        <v>6703716</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3821,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624299</v>
+        <v>129624382</v>
       </c>
       <c r="B33" t="n">
-        <v>101876</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,34 +3812,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668169</v>
+        <v>668266</v>
       </c>
       <c r="R33" t="n">
-        <v>6703716</v>
+        <v>6703768</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3902,6 +3887,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624369</v>
+        <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>105846</v>
+        <v>96126</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,21 +4220,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668127</v>
+        <v>668318</v>
       </c>
       <c r="R37" t="n">
-        <v>6703878</v>
+        <v>6703714</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96126</v>
+        <v>96222</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,34 +4317,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R38" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4403,10 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129624372</v>
+        <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>96222</v>
+        <v>105846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4414,43 +4423,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668296</v>
+        <v>668127</v>
       </c>
       <c r="R39" t="n">
-        <v>6703695</v>
+        <v>6703878</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>100969</v>
+        <v>97026</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R62" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>97026</v>
+        <v>100969</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R63" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129624391</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>101876</v>
+        <v>101886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624343</v>
+        <v>129624395</v>
       </c>
       <c r="B8" t="n">
-        <v>98758</v>
+        <v>100979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668165</v>
+        <v>668288</v>
       </c>
       <c r="R8" t="n">
-        <v>6703856</v>
+        <v>6703696</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624395</v>
+        <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668288</v>
+        <v>668154</v>
       </c>
       <c r="R9" t="n">
-        <v>6703696</v>
+        <v>6703899</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624399</v>
+        <v>129624343</v>
       </c>
       <c r="B10" t="n">
-        <v>100969</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668154</v>
+        <v>668165</v>
       </c>
       <c r="R10" t="n">
-        <v>6703899</v>
+        <v>6703856</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,7 +1561,7 @@
         <v>129624370</v>
       </c>
       <c r="B11" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624308</v>
+        <v>129624394</v>
       </c>
       <c r="B12" t="n">
-        <v>97026</v>
+        <v>100979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668162</v>
+        <v>668270</v>
       </c>
       <c r="R12" t="n">
-        <v>6703712</v>
+        <v>6703699</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624313</v>
+        <v>129624374</v>
       </c>
       <c r="B13" t="n">
-        <v>97026</v>
+        <v>4779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668179</v>
+        <v>668256</v>
       </c>
       <c r="R13" t="n">
-        <v>6703790</v>
+        <v>6703754</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624374</v>
+        <v>129624308</v>
       </c>
       <c r="B15" t="n">
-        <v>4779</v>
+        <v>97036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668256</v>
+        <v>668162</v>
       </c>
       <c r="R15" t="n">
-        <v>6703754</v>
+        <v>6703712</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2057,21 +2057,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2088,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624394</v>
+        <v>129624313</v>
       </c>
       <c r="B16" t="n">
-        <v>100969</v>
+        <v>97036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668270</v>
+        <v>668179</v>
       </c>
       <c r="R16" t="n">
-        <v>6703699</v>
+        <v>6703790</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2169,6 +2154,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2188,7 +2188,7 @@
         <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>129624392</v>
       </c>
       <c r="B18" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,50 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624297</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>101886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668176</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703677</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2593,45 +2588,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624396</v>
+        <v>129624366</v>
       </c>
       <c r="B21" t="n">
-        <v>100969</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668305</v>
+        <v>668160</v>
       </c>
       <c r="R21" t="n">
-        <v>6703732</v>
+        <v>6703911</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2690,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624297</v>
+        <v>129624396</v>
       </c>
       <c r="B22" t="n">
-        <v>101876</v>
+        <v>100979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668176</v>
+        <v>668305</v>
       </c>
       <c r="R22" t="n">
-        <v>6703677</v>
+        <v>6703732</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2787,42 +2791,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624366</v>
+        <v>129624329</v>
       </c>
       <c r="B23" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668160</v>
+        <v>668230</v>
       </c>
       <c r="R23" t="n">
-        <v>6703911</v>
+        <v>6703725</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2893,45 +2893,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624401</v>
+        <v>129624328</v>
       </c>
       <c r="B24" t="n">
-        <v>100969</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668293</v>
+        <v>668312</v>
       </c>
       <c r="R24" t="n">
-        <v>6703720</v>
+        <v>6703726</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2990,50 +2995,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624328</v>
+        <v>129624401</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668312</v>
+        <v>668293</v>
       </c>
       <c r="R25" t="n">
-        <v>6703726</v>
+        <v>6703720</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3095,7 +3095,7 @@
         <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>129624368</v>
       </c>
       <c r="B27" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,32 +3286,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624388</v>
+        <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>100969</v>
+        <v>97036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668122</v>
+        <v>668262</v>
       </c>
       <c r="R28" t="n">
-        <v>6703878</v>
+        <v>6703727</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,6 +3367,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3383,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624316</v>
+        <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>97026</v>
+        <v>100979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3418,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668262</v>
+        <v>668122</v>
       </c>
       <c r="R29" t="n">
-        <v>6703727</v>
+        <v>6703878</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3464,21 +3479,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3498,7 +3498,7 @@
         <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624299</v>
+        <v>129624382</v>
       </c>
       <c r="B32" t="n">
-        <v>101876</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,34 +3715,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668169</v>
+        <v>668266</v>
       </c>
       <c r="R32" t="n">
-        <v>6703716</v>
+        <v>6703768</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3785,6 +3790,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3801,10 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624382</v>
+        <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>101886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,39 +3832,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668266</v>
+        <v>668169</v>
       </c>
       <c r="R33" t="n">
-        <v>6703768</v>
+        <v>6703716</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3887,21 +3902,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3921,7 +3921,7 @@
         <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129624320</v>
       </c>
       <c r="B35" t="n">
-        <v>104251</v>
+        <v>104261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>129624296</v>
       </c>
       <c r="B36" t="n">
-        <v>101876</v>
+        <v>101886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B37" t="n">
-        <v>96126</v>
+        <v>96232</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,34 +4220,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R37" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4315,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B38" t="n">
-        <v>96222</v>
+        <v>96136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,43 +4326,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R38" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4415,7 +4415,7 @@
         <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624371</v>
+        <v>129624373</v>
       </c>
       <c r="B40" t="n">
-        <v>105846</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668163</v>
+        <v>668112</v>
       </c>
       <c r="R40" t="n">
-        <v>6703870</v>
+        <v>6703887</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,6 +4590,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4606,32 +4621,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624345</v>
+        <v>129624307</v>
       </c>
       <c r="B41" t="n">
-        <v>98758</v>
+        <v>97036</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668302</v>
+        <v>668175</v>
       </c>
       <c r="R41" t="n">
-        <v>6703713</v>
+        <v>6703703</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4703,32 +4718,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624340</v>
+        <v>129624318</v>
       </c>
       <c r="B42" t="n">
-        <v>98758</v>
+        <v>97036</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4738,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668169</v>
+        <v>668185</v>
       </c>
       <c r="R42" t="n">
-        <v>6703716</v>
+        <v>6703684</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4784,6 +4799,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4803,7 +4833,7 @@
         <v>129624322</v>
       </c>
       <c r="B43" t="n">
-        <v>104251</v>
+        <v>104261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,32 +4927,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624307</v>
+        <v>129624371</v>
       </c>
       <c r="B44" t="n">
-        <v>97026</v>
+        <v>105856</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4932,10 +4962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668175</v>
+        <v>668163</v>
       </c>
       <c r="R44" t="n">
-        <v>6703703</v>
+        <v>6703870</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4994,32 +5024,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624318</v>
+        <v>129624345</v>
       </c>
       <c r="B45" t="n">
-        <v>97026</v>
+        <v>98768</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5029,10 +5059,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668185</v>
+        <v>668302</v>
       </c>
       <c r="R45" t="n">
-        <v>6703684</v>
+        <v>6703713</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5075,21 +5105,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5106,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624373</v>
+        <v>129624340</v>
       </c>
       <c r="B46" t="n">
-        <v>4779</v>
+        <v>98768</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5117,21 +5132,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5141,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668112</v>
+        <v>668169</v>
       </c>
       <c r="R46" t="n">
-        <v>6703887</v>
+        <v>6703716</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5187,21 +5202,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101876</v>
+        <v>101886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5315,45 +5315,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624397</v>
+        <v>129624327</v>
       </c>
       <c r="B48" t="n">
-        <v>100969</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668305</v>
+        <v>668173</v>
       </c>
       <c r="R48" t="n">
-        <v>6703751</v>
+        <v>6703787</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,50 +5529,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624327</v>
+        <v>129624397</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668173</v>
+        <v>668305</v>
       </c>
       <c r="R50" t="n">
-        <v>6703787</v>
+        <v>6703751</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5723,54 +5723,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624367</v>
+        <v>129624339</v>
       </c>
       <c r="B52" t="n">
-        <v>98780</v>
+        <v>98768</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668253</v>
+        <v>668166</v>
       </c>
       <c r="R52" t="n">
-        <v>6703781</v>
+        <v>6703694</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5829,10 +5820,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624339</v>
+        <v>129624393</v>
       </c>
       <c r="B53" t="n">
-        <v>98758</v>
+        <v>100979</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5840,21 +5831,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5864,10 +5855,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668166</v>
+        <v>668182</v>
       </c>
       <c r="R53" t="n">
-        <v>6703694</v>
+        <v>6703746</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624393</v>
+        <v>129624385</v>
       </c>
       <c r="B54" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5961,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668182</v>
+        <v>668149</v>
       </c>
       <c r="R54" t="n">
-        <v>6703746</v>
+        <v>6703811</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,10 +6014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624385</v>
+        <v>129624403</v>
       </c>
       <c r="B55" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,10 +6049,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668149</v>
+        <v>668258</v>
       </c>
       <c r="R55" t="n">
-        <v>6703811</v>
+        <v>6703763</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,10 +6111,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624403</v>
+        <v>129624400</v>
       </c>
       <c r="B56" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6155,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668258</v>
+        <v>668331</v>
       </c>
       <c r="R56" t="n">
-        <v>6703763</v>
+        <v>6703743</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,45 +6208,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624400</v>
+        <v>129624367</v>
       </c>
       <c r="B57" t="n">
-        <v>100969</v>
+        <v>98790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668331</v>
+        <v>668253</v>
       </c>
       <c r="R57" t="n">
-        <v>6703743</v>
+        <v>6703781</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6317,7 +6317,7 @@
         <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624301</v>
+        <v>129624389</v>
       </c>
       <c r="B64" t="n">
-        <v>101876</v>
+        <v>100979</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668194</v>
+        <v>668107</v>
       </c>
       <c r="R64" t="n">
-        <v>6703673</v>
+        <v>6703910</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7016,7 +7016,7 @@
         <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>110911</v>
+        <v>110946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624389</v>
+        <v>129624301</v>
       </c>
       <c r="B66" t="n">
-        <v>100969</v>
+        <v>101886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668107</v>
+        <v>668194</v>
       </c>
       <c r="R66" t="n">
-        <v>6703910</v>
+        <v>6703673</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -1165,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624331</v>
+        <v>129624395</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668257</v>
+        <v>668288</v>
       </c>
       <c r="R7" t="n">
-        <v>6703774</v>
+        <v>6703696</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624395</v>
+        <v>129624399</v>
       </c>
       <c r="B8" t="n">
         <v>100979</v>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668288</v>
+        <v>668154</v>
       </c>
       <c r="R8" t="n">
-        <v>6703696</v>
+        <v>6703899</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624399</v>
+        <v>129624370</v>
       </c>
       <c r="B9" t="n">
-        <v>100979</v>
+        <v>105856</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668154</v>
+        <v>668108</v>
       </c>
       <c r="R9" t="n">
-        <v>6703899</v>
+        <v>6703888</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,45 +1456,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624343</v>
+        <v>129624331</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668165</v>
+        <v>668257</v>
       </c>
       <c r="R10" t="n">
-        <v>6703856</v>
+        <v>6703774</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624370</v>
+        <v>129624343</v>
       </c>
       <c r="B11" t="n">
-        <v>105856</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668108</v>
+        <v>668165</v>
       </c>
       <c r="R11" t="n">
-        <v>6703888</v>
+        <v>6703856</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624310</v>
+        <v>129624392</v>
       </c>
       <c r="B17" t="n">
-        <v>97036</v>
+        <v>100979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668108</v>
+        <v>668190</v>
       </c>
       <c r="R17" t="n">
-        <v>6703891</v>
+        <v>6703813</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,21 +2266,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2297,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624392</v>
+        <v>129624390</v>
       </c>
       <c r="B18" t="n">
         <v>100979</v>
@@ -2332,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668190</v>
+        <v>668123</v>
       </c>
       <c r="R18" t="n">
-        <v>6703813</v>
+        <v>6703926</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2394,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624390</v>
+        <v>129624310</v>
       </c>
       <c r="B19" t="n">
-        <v>100979</v>
+        <v>97036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668123</v>
+        <v>668108</v>
       </c>
       <c r="R19" t="n">
-        <v>6703926</v>
+        <v>6703891</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2475,6 +2460,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2694,45 +2694,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B22" t="n">
-        <v>100979</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R22" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,50 +2796,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624329</v>
+        <v>129624396</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668230</v>
+        <v>668305</v>
       </c>
       <c r="R23" t="n">
-        <v>6703725</v>
+        <v>6703732</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3286,32 +3286,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624316</v>
+        <v>129624388</v>
       </c>
       <c r="B28" t="n">
-        <v>97036</v>
+        <v>100979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668262</v>
+        <v>668122</v>
       </c>
       <c r="R28" t="n">
-        <v>6703727</v>
+        <v>6703878</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,21 +3367,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3398,32 +3383,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624388</v>
+        <v>129624316</v>
       </c>
       <c r="B29" t="n">
-        <v>100979</v>
+        <v>97036</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668122</v>
+        <v>668262</v>
       </c>
       <c r="R29" t="n">
-        <v>6703878</v>
+        <v>6703727</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3479,6 +3464,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624311</v>
+        <v>129624296</v>
       </c>
       <c r="B34" t="n">
-        <v>97036</v>
+        <v>101886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668158</v>
+        <v>668152</v>
       </c>
       <c r="R34" t="n">
-        <v>6703911</v>
+        <v>6703756</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624320</v>
+        <v>129624311</v>
       </c>
       <c r="B35" t="n">
-        <v>104261</v>
+        <v>97036</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668289</v>
+        <v>668158</v>
       </c>
       <c r="R35" t="n">
-        <v>6703690</v>
+        <v>6703911</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624296</v>
+        <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>101886</v>
+        <v>104261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668152</v>
+        <v>668289</v>
       </c>
       <c r="R36" t="n">
-        <v>6703756</v>
+        <v>6703690</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624373</v>
+        <v>129624307</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>97036</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668112</v>
+        <v>668175</v>
       </c>
       <c r="R40" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,21 +4590,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4621,7 +4606,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624307</v>
+        <v>129624318</v>
       </c>
       <c r="B41" t="n">
         <v>97036</v>
@@ -4656,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668175</v>
+        <v>668185</v>
       </c>
       <c r="R41" t="n">
-        <v>6703703</v>
+        <v>6703684</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4702,6 +4687,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,32 +4718,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624318</v>
+        <v>129624373</v>
       </c>
       <c r="B42" t="n">
-        <v>97036</v>
+        <v>4779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668185</v>
+        <v>668112</v>
       </c>
       <c r="R42" t="n">
-        <v>6703684</v>
+        <v>6703887</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4802,17 +4802,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624339</v>
+        <v>129624393</v>
       </c>
       <c r="B52" t="n">
-        <v>98768</v>
+        <v>100979</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668166</v>
+        <v>668182</v>
       </c>
       <c r="R52" t="n">
-        <v>6703694</v>
+        <v>6703746</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624393</v>
+        <v>129624385</v>
       </c>
       <c r="B53" t="n">
         <v>100979</v>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668182</v>
+        <v>668149</v>
       </c>
       <c r="R53" t="n">
-        <v>6703746</v>
+        <v>6703811</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5917,7 +5917,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624385</v>
+        <v>129624403</v>
       </c>
       <c r="B54" t="n">
         <v>100979</v>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668149</v>
+        <v>668258</v>
       </c>
       <c r="R54" t="n">
-        <v>6703811</v>
+        <v>6703763</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6014,7 +6014,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624403</v>
+        <v>129624400</v>
       </c>
       <c r="B55" t="n">
         <v>100979</v>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668258</v>
+        <v>668331</v>
       </c>
       <c r="R55" t="n">
-        <v>6703763</v>
+        <v>6703743</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6111,45 +6111,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624400</v>
+        <v>129624367</v>
       </c>
       <c r="B56" t="n">
-        <v>100979</v>
+        <v>98790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668331</v>
+        <v>668253</v>
       </c>
       <c r="R56" t="n">
-        <v>6703743</v>
+        <v>6703781</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6208,54 +6217,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624367</v>
+        <v>129624339</v>
       </c>
       <c r="B57" t="n">
-        <v>98790</v>
+        <v>98768</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668253</v>
+        <v>668166</v>
       </c>
       <c r="R57" t="n">
-        <v>6703781</v>
+        <v>6703694</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624389</v>
+        <v>129624323</v>
       </c>
       <c r="B64" t="n">
-        <v>100979</v>
+        <v>110946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668107</v>
+        <v>668134</v>
       </c>
       <c r="R64" t="n">
-        <v>6703910</v>
+        <v>6703832</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6989,12 +6989,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7013,10 +7019,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624323</v>
+        <v>129624301</v>
       </c>
       <c r="B65" t="n">
-        <v>110946</v>
+        <v>101886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7030,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7054,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668134</v>
+        <v>668194</v>
       </c>
       <c r="R65" t="n">
-        <v>6703832</v>
+        <v>6703673</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7086,18 +7092,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624301</v>
+        <v>129624389</v>
       </c>
       <c r="B66" t="n">
-        <v>101886</v>
+        <v>100979</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668194</v>
+        <v>668107</v>
       </c>
       <c r="R66" t="n">
-        <v>6703673</v>
+        <v>6703910</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -1165,45 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624395</v>
+        <v>129624331</v>
       </c>
       <c r="B7" t="n">
-        <v>100979</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668288</v>
+        <v>668257</v>
       </c>
       <c r="R7" t="n">
-        <v>6703696</v>
+        <v>6703774</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624399</v>
+        <v>129624395</v>
       </c>
       <c r="B8" t="n">
         <v>100979</v>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668154</v>
+        <v>668288</v>
       </c>
       <c r="R8" t="n">
-        <v>6703899</v>
+        <v>6703696</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624370</v>
+        <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>105856</v>
+        <v>100979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668108</v>
+        <v>668154</v>
       </c>
       <c r="R9" t="n">
-        <v>6703888</v>
+        <v>6703899</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,50 +1461,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624331</v>
+        <v>129624343</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668257</v>
+        <v>668165</v>
       </c>
       <c r="R10" t="n">
-        <v>6703774</v>
+        <v>6703856</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624343</v>
+        <v>129624370</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>105856</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668165</v>
+        <v>668108</v>
       </c>
       <c r="R11" t="n">
-        <v>6703856</v>
+        <v>6703888</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624394</v>
+        <v>129624308</v>
       </c>
       <c r="B12" t="n">
-        <v>100979</v>
+        <v>97036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668270</v>
+        <v>668162</v>
       </c>
       <c r="R12" t="n">
-        <v>6703699</v>
+        <v>6703712</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624374</v>
+        <v>129624313</v>
       </c>
       <c r="B13" t="n">
-        <v>4779</v>
+        <v>97036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668256</v>
+        <v>668179</v>
       </c>
       <c r="R13" t="n">
-        <v>6703754</v>
+        <v>6703790</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624383</v>
+        <v>129624394</v>
       </c>
       <c r="B14" t="n">
-        <v>92249</v>
+        <v>100979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668279</v>
+        <v>668270</v>
       </c>
       <c r="R14" t="n">
-        <v>6703691</v>
+        <v>6703699</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,21 +1945,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1976,32 +1961,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624308</v>
+        <v>129624374</v>
       </c>
       <c r="B15" t="n">
-        <v>97036</v>
+        <v>4779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668162</v>
+        <v>668256</v>
       </c>
       <c r="R15" t="n">
-        <v>6703712</v>
+        <v>6703754</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2057,6 +2042,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2073,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624313</v>
+        <v>129624383</v>
       </c>
       <c r="B16" t="n">
-        <v>97036</v>
+        <v>92249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668179</v>
+        <v>668279</v>
       </c>
       <c r="R16" t="n">
-        <v>6703790</v>
+        <v>6703691</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3495,45 +3495,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624315</v>
+        <v>129624382</v>
       </c>
       <c r="B30" t="n">
-        <v>97036</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668277</v>
+        <v>668266</v>
       </c>
       <c r="R30" t="n">
-        <v>6703748</v>
+        <v>6703768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3579,17 +3584,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3607,32 +3612,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624404</v>
+        <v>129624315</v>
       </c>
       <c r="B31" t="n">
-        <v>87014</v>
+        <v>97036</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668299</v>
+        <v>668277</v>
       </c>
       <c r="R31" t="n">
-        <v>6703709</v>
+        <v>6703748</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3688,6 +3693,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3704,10 +3724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624382</v>
+        <v>129624404</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>87014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,39 +3735,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668266</v>
+        <v>668299</v>
       </c>
       <c r="R32" t="n">
-        <v>6703768</v>
+        <v>6703709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3790,21 +3805,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624296</v>
+        <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>101886</v>
+        <v>97036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668152</v>
+        <v>668158</v>
       </c>
       <c r="R34" t="n">
-        <v>6703756</v>
+        <v>6703911</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624311</v>
+        <v>129624320</v>
       </c>
       <c r="B35" t="n">
-        <v>97036</v>
+        <v>104261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668158</v>
+        <v>668289</v>
       </c>
       <c r="R35" t="n">
-        <v>6703911</v>
+        <v>6703690</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624320</v>
+        <v>129624296</v>
       </c>
       <c r="B36" t="n">
-        <v>104261</v>
+        <v>101886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668289</v>
+        <v>668152</v>
       </c>
       <c r="R36" t="n">
-        <v>6703690</v>
+        <v>6703756</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624372</v>
+        <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96232</v>
+        <v>96136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,43 +4220,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668296</v>
+        <v>668318</v>
       </c>
       <c r="R37" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4315,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624325</v>
+        <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96136</v>
+        <v>96232</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,34 +4317,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668318</v>
+        <v>668296</v>
       </c>
       <c r="R38" t="n">
-        <v>6703714</v>
+        <v>6703695</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5723,45 +5723,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624393</v>
+        <v>129624367</v>
       </c>
       <c r="B52" t="n">
-        <v>100979</v>
+        <v>98790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668182</v>
+        <v>668253</v>
       </c>
       <c r="R52" t="n">
-        <v>6703746</v>
+        <v>6703781</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,7 +5829,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624385</v>
+        <v>129624393</v>
       </c>
       <c r="B53" t="n">
         <v>100979</v>
@@ -5855,10 +5864,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668149</v>
+        <v>668182</v>
       </c>
       <c r="R53" t="n">
-        <v>6703811</v>
+        <v>6703746</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5917,7 +5926,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624403</v>
+        <v>129624385</v>
       </c>
       <c r="B54" t="n">
         <v>100979</v>
@@ -5952,10 +5961,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668258</v>
+        <v>668149</v>
       </c>
       <c r="R54" t="n">
-        <v>6703763</v>
+        <v>6703811</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6014,7 +6023,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624400</v>
+        <v>129624403</v>
       </c>
       <c r="B55" t="n">
         <v>100979</v>
@@ -6049,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668331</v>
+        <v>668258</v>
       </c>
       <c r="R55" t="n">
-        <v>6703743</v>
+        <v>6703763</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6111,54 +6120,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624367</v>
+        <v>129624400</v>
       </c>
       <c r="B56" t="n">
-        <v>98790</v>
+        <v>100979</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668253</v>
+        <v>668331</v>
       </c>
       <c r="R56" t="n">
-        <v>6703781</v>
+        <v>6703743</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624391</v>
+        <v>129624300</v>
       </c>
       <c r="B4" t="n">
-        <v>100979</v>
+        <v>101890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668163</v>
+        <v>668262</v>
       </c>
       <c r="R4" t="n">
-        <v>6703831</v>
+        <v>6703729</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624346</v>
+        <v>129624391</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>100983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668302</v>
+        <v>668163</v>
       </c>
       <c r="R5" t="n">
-        <v>6703689</v>
+        <v>6703831</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624300</v>
+        <v>129624346</v>
       </c>
       <c r="B6" t="n">
-        <v>101886</v>
+        <v>98772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668262</v>
+        <v>668302</v>
       </c>
       <c r="R6" t="n">
-        <v>6703729</v>
+        <v>6703689</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,7 +1168,7 @@
         <v>129624331</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129624395</v>
       </c>
       <c r="B8" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624343</v>
+        <v>129624370</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>105860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668165</v>
+        <v>668108</v>
       </c>
       <c r="R10" t="n">
-        <v>6703856</v>
+        <v>6703888</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624370</v>
+        <v>129624343</v>
       </c>
       <c r="B11" t="n">
-        <v>105856</v>
+        <v>98772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668108</v>
+        <v>668165</v>
       </c>
       <c r="R11" t="n">
-        <v>6703888</v>
+        <v>6703856</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624308</v>
+        <v>129624383</v>
       </c>
       <c r="B12" t="n">
-        <v>97036</v>
+        <v>92252</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668162</v>
+        <v>668279</v>
       </c>
       <c r="R12" t="n">
-        <v>6703712</v>
+        <v>6703691</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1752,32 +1767,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624313</v>
+        <v>129624394</v>
       </c>
       <c r="B13" t="n">
-        <v>97036</v>
+        <v>100983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668179</v>
+        <v>668270</v>
       </c>
       <c r="R13" t="n">
-        <v>6703790</v>
+        <v>6703699</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1833,21 +1848,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1864,32 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624394</v>
+        <v>129624308</v>
       </c>
       <c r="B14" t="n">
-        <v>100979</v>
+        <v>97040</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668270</v>
+        <v>668162</v>
       </c>
       <c r="R14" t="n">
-        <v>6703699</v>
+        <v>6703712</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1961,32 +1961,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624374</v>
+        <v>129624313</v>
       </c>
       <c r="B15" t="n">
-        <v>4779</v>
+        <v>97040</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668256</v>
+        <v>668179</v>
       </c>
       <c r="R15" t="n">
-        <v>6703754</v>
+        <v>6703790</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624383</v>
+        <v>129624374</v>
       </c>
       <c r="B16" t="n">
-        <v>92249</v>
+        <v>4779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668279</v>
+        <v>668256</v>
       </c>
       <c r="R16" t="n">
-        <v>6703691</v>
+        <v>6703754</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2188,7 +2188,7 @@
         <v>129624392</v>
       </c>
       <c r="B17" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>129624390</v>
       </c>
       <c r="B18" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129624310</v>
       </c>
       <c r="B19" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,45 +2491,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624297</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>101886</v>
+        <v>57734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668176</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703677</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2591,7 +2596,7 @@
         <v>129624366</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,50 +2699,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624329</v>
+        <v>129624297</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>101890</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668230</v>
+        <v>668176</v>
       </c>
       <c r="R22" t="n">
-        <v>6703725</v>
+        <v>6703677</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2799,7 +2799,7 @@
         <v>129624396</v>
       </c>
       <c r="B23" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,50 +2893,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624328</v>
+        <v>129624401</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>100983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668312</v>
+        <v>668293</v>
       </c>
       <c r="R24" t="n">
-        <v>6703726</v>
+        <v>6703720</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2995,45 +2990,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624401</v>
+        <v>129624328</v>
       </c>
       <c r="B25" t="n">
-        <v>100979</v>
+        <v>57734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668293</v>
+        <v>668312</v>
       </c>
       <c r="R25" t="n">
-        <v>6703720</v>
+        <v>6703726</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3092,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624344</v>
+        <v>129624368</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>105860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668257</v>
+        <v>668181</v>
       </c>
       <c r="R26" t="n">
-        <v>6703688</v>
+        <v>6703685</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624368</v>
+        <v>129624344</v>
       </c>
       <c r="B27" t="n">
-        <v>105856</v>
+        <v>98772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668181</v>
+        <v>668257</v>
       </c>
       <c r="R27" t="n">
-        <v>6703685</v>
+        <v>6703688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3286,32 +3286,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624388</v>
+        <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>100979</v>
+        <v>97040</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668122</v>
+        <v>668262</v>
       </c>
       <c r="R28" t="n">
-        <v>6703878</v>
+        <v>6703727</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,6 +3367,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3383,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624316</v>
+        <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>97036</v>
+        <v>100983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3418,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668262</v>
+        <v>668122</v>
       </c>
       <c r="R29" t="n">
-        <v>6703727</v>
+        <v>6703878</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3464,21 +3479,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3612,32 +3612,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624315</v>
+        <v>129624299</v>
       </c>
       <c r="B31" t="n">
-        <v>97036</v>
+        <v>101890</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668277</v>
+        <v>668169</v>
       </c>
       <c r="R31" t="n">
-        <v>6703748</v>
+        <v>6703716</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3693,21 +3693,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3724,32 +3709,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624404</v>
+        <v>129624315</v>
       </c>
       <c r="B32" t="n">
-        <v>87014</v>
+        <v>97040</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3759,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668299</v>
+        <v>668277</v>
       </c>
       <c r="R32" t="n">
-        <v>6703709</v>
+        <v>6703748</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3805,6 +3790,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3821,10 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B33" t="n">
-        <v>101886</v>
+        <v>87017</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,21 +3832,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R33" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3921,7 +3921,7 @@
         <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624320</v>
+        <v>129624296</v>
       </c>
       <c r="B35" t="n">
-        <v>104261</v>
+        <v>101890</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668289</v>
+        <v>668152</v>
       </c>
       <c r="R35" t="n">
-        <v>6703690</v>
+        <v>6703756</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624296</v>
+        <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>101886</v>
+        <v>104265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668152</v>
+        <v>668289</v>
       </c>
       <c r="R36" t="n">
-        <v>6703756</v>
+        <v>6703690</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4212,7 +4212,7 @@
         <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624307</v>
+        <v>129624373</v>
       </c>
       <c r="B40" t="n">
-        <v>97036</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668175</v>
+        <v>668112</v>
       </c>
       <c r="R40" t="n">
-        <v>6703703</v>
+        <v>6703887</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,6 +4590,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4606,32 +4621,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624318</v>
+        <v>129624322</v>
       </c>
       <c r="B41" t="n">
-        <v>97036</v>
+        <v>104265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668185</v>
+        <v>668300</v>
       </c>
       <c r="R41" t="n">
-        <v>6703684</v>
+        <v>6703703</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4687,21 +4702,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624373</v>
+        <v>129624345</v>
       </c>
       <c r="B42" t="n">
-        <v>4779</v>
+        <v>98772</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668112</v>
+        <v>668302</v>
       </c>
       <c r="R42" t="n">
-        <v>6703887</v>
+        <v>6703713</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,21 +4799,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4830,10 +4815,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624322</v>
+        <v>129624340</v>
       </c>
       <c r="B43" t="n">
-        <v>104261</v>
+        <v>98772</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4841,21 +4826,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4865,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668300</v>
+        <v>668169</v>
       </c>
       <c r="R43" t="n">
-        <v>6703703</v>
+        <v>6703716</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4927,32 +4912,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624371</v>
+        <v>129624307</v>
       </c>
       <c r="B44" t="n">
-        <v>105856</v>
+        <v>97040</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4962,10 +4947,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668163</v>
+        <v>668175</v>
       </c>
       <c r="R44" t="n">
-        <v>6703870</v>
+        <v>6703703</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5024,32 +5009,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624345</v>
+        <v>129624318</v>
       </c>
       <c r="B45" t="n">
-        <v>98768</v>
+        <v>97040</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5059,10 +5044,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668302</v>
+        <v>668185</v>
       </c>
       <c r="R45" t="n">
-        <v>6703713</v>
+        <v>6703684</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5105,6 +5090,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624340</v>
+        <v>129624371</v>
       </c>
       <c r="B46" t="n">
-        <v>98768</v>
+        <v>105860</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668169</v>
+        <v>668163</v>
       </c>
       <c r="R46" t="n">
-        <v>6703716</v>
+        <v>6703870</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101886</v>
+        <v>101890</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>129624327</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5417,32 +5417,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624349</v>
+        <v>129624397</v>
       </c>
       <c r="B49" t="n">
-        <v>92052</v>
+        <v>100983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668275</v>
+        <v>668305</v>
       </c>
       <c r="R49" t="n">
-        <v>6703756</v>
+        <v>6703751</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5498,21 +5498,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5529,32 +5514,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624397</v>
+        <v>129624349</v>
       </c>
       <c r="B50" t="n">
-        <v>100979</v>
+        <v>92055</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5564,10 +5549,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668305</v>
+        <v>668275</v>
       </c>
       <c r="R50" t="n">
-        <v>6703751</v>
+        <v>6703756</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5610,6 +5595,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5626,45 +5626,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624348</v>
+        <v>129624367</v>
       </c>
       <c r="B51" t="n">
-        <v>91372</v>
+        <v>98794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668185</v>
+        <v>668253</v>
       </c>
       <c r="R51" t="n">
-        <v>6703715</v>
+        <v>6703781</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5723,54 +5732,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624367</v>
+        <v>129624339</v>
       </c>
       <c r="B52" t="n">
-        <v>98790</v>
+        <v>98772</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668253</v>
+        <v>668166</v>
       </c>
       <c r="R52" t="n">
-        <v>6703781</v>
+        <v>6703694</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5829,10 +5829,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624393</v>
+        <v>129624348</v>
       </c>
       <c r="B53" t="n">
-        <v>100979</v>
+        <v>91375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668182</v>
+        <v>668185</v>
       </c>
       <c r="R53" t="n">
-        <v>6703746</v>
+        <v>6703715</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624385</v>
+        <v>129624393</v>
       </c>
       <c r="B54" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668149</v>
+        <v>668182</v>
       </c>
       <c r="R54" t="n">
-        <v>6703811</v>
+        <v>6703746</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624403</v>
+        <v>129624385</v>
       </c>
       <c r="B55" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668258</v>
+        <v>668149</v>
       </c>
       <c r="R55" t="n">
-        <v>6703763</v>
+        <v>6703811</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624400</v>
+        <v>129624403</v>
       </c>
       <c r="B56" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668331</v>
+        <v>668258</v>
       </c>
       <c r="R56" t="n">
-        <v>6703743</v>
+        <v>6703763</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624339</v>
+        <v>129624400</v>
       </c>
       <c r="B57" t="n">
-        <v>98768</v>
+        <v>100983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668166</v>
+        <v>668331</v>
       </c>
       <c r="R57" t="n">
-        <v>6703694</v>
+        <v>6703743</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6317,7 +6317,7 @@
         <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B62" t="n">
-        <v>97036</v>
+        <v>100983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R62" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B63" t="n">
-        <v>100979</v>
+        <v>97040</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R63" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624323</v>
+        <v>129624389</v>
       </c>
       <c r="B64" t="n">
-        <v>110946</v>
+        <v>100983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668134</v>
+        <v>668107</v>
       </c>
       <c r="R64" t="n">
-        <v>6703832</v>
+        <v>6703910</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6989,18 +6989,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7019,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624301</v>
+        <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>101886</v>
+        <v>110950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7030,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7054,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668194</v>
+        <v>668134</v>
       </c>
       <c r="R65" t="n">
-        <v>6703673</v>
+        <v>6703832</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7092,12 +7086,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624389</v>
+        <v>129624301</v>
       </c>
       <c r="B66" t="n">
-        <v>100979</v>
+        <v>101890</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668107</v>
+        <v>668194</v>
       </c>
       <c r="R66" t="n">
-        <v>6703910</v>
+        <v>6703673</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624383</v>
+        <v>129624394</v>
       </c>
       <c r="B12" t="n">
-        <v>92252</v>
+        <v>100983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668279</v>
+        <v>668270</v>
       </c>
       <c r="R12" t="n">
-        <v>6703691</v>
+        <v>6703699</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1736,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1767,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624394</v>
+        <v>129624308</v>
       </c>
       <c r="B13" t="n">
-        <v>100983</v>
+        <v>97040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668270</v>
+        <v>668162</v>
       </c>
       <c r="R13" t="n">
-        <v>6703699</v>
+        <v>6703712</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1864,7 +1849,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624308</v>
+        <v>129624313</v>
       </c>
       <c r="B14" t="n">
         <v>97040</v>
@@ -1899,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668162</v>
+        <v>668179</v>
       </c>
       <c r="R14" t="n">
-        <v>6703712</v>
+        <v>6703790</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,6 +1930,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,32 +1961,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624313</v>
+        <v>129624383</v>
       </c>
       <c r="B15" t="n">
-        <v>97040</v>
+        <v>92252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668179</v>
+        <v>668279</v>
       </c>
       <c r="R15" t="n">
-        <v>6703790</v>
+        <v>6703691</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2491,50 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624297</v>
       </c>
       <c r="B20" t="n">
-        <v>57734</v>
+        <v>101890</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668176</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703677</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2593,54 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624366</v>
+        <v>129624396</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>100983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668160</v>
+        <v>668305</v>
       </c>
       <c r="R21" t="n">
-        <v>6703911</v>
+        <v>6703732</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2699,45 +2685,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624297</v>
+        <v>129624366</v>
       </c>
       <c r="B22" t="n">
-        <v>101890</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668176</v>
+        <v>668160</v>
       </c>
       <c r="R22" t="n">
-        <v>6703677</v>
+        <v>6703911</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2796,45 +2791,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624396</v>
+        <v>129624329</v>
       </c>
       <c r="B23" t="n">
-        <v>100983</v>
+        <v>57734</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668305</v>
+        <v>668230</v>
       </c>
       <c r="R23" t="n">
-        <v>6703732</v>
+        <v>6703725</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3495,50 +3495,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624382</v>
+        <v>129624315</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>97040</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668266</v>
+        <v>668277</v>
       </c>
       <c r="R30" t="n">
-        <v>6703768</v>
+        <v>6703748</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3584,17 +3579,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3612,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624299</v>
+        <v>129624404</v>
       </c>
       <c r="B31" t="n">
-        <v>101890</v>
+        <v>87017</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668169</v>
+        <v>668299</v>
       </c>
       <c r="R31" t="n">
-        <v>6703716</v>
+        <v>6703709</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3709,45 +3704,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624315</v>
+        <v>129624382</v>
       </c>
       <c r="B32" t="n">
-        <v>97040</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668277</v>
+        <v>668266</v>
       </c>
       <c r="R32" t="n">
-        <v>6703748</v>
+        <v>6703768</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3793,17 +3793,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624404</v>
+        <v>129624299</v>
       </c>
       <c r="B33" t="n">
-        <v>87017</v>
+        <v>101890</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,21 +3832,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668299</v>
+        <v>668169</v>
       </c>
       <c r="R33" t="n">
-        <v>6703709</v>
+        <v>6703716</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4621,10 +4621,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624322</v>
+        <v>129624371</v>
       </c>
       <c r="B41" t="n">
-        <v>104265</v>
+        <v>105860</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4632,21 +4632,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668300</v>
+        <v>668163</v>
       </c>
       <c r="R41" t="n">
-        <v>6703703</v>
+        <v>6703870</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624371</v>
+        <v>129624322</v>
       </c>
       <c r="B46" t="n">
-        <v>105860</v>
+        <v>104265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>222412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668163</v>
+        <v>668300</v>
       </c>
       <c r="R46" t="n">
-        <v>6703870</v>
+        <v>6703703</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5315,50 +5315,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B48" t="n">
-        <v>57734</v>
+        <v>92055</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R48" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5401,6 +5396,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5514,45 +5524,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624349</v>
+        <v>129624327</v>
       </c>
       <c r="B50" t="n">
-        <v>92055</v>
+        <v>57734</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668275</v>
+        <v>668173</v>
       </c>
       <c r="R50" t="n">
-        <v>6703756</v>
+        <v>6703787</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5595,21 +5610,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5626,54 +5626,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624367</v>
+        <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>98794</v>
+        <v>91375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668253</v>
+        <v>668185</v>
       </c>
       <c r="R51" t="n">
-        <v>6703781</v>
+        <v>6703715</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5732,10 +5723,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624339</v>
+        <v>129624393</v>
       </c>
       <c r="B52" t="n">
-        <v>98772</v>
+        <v>100983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5743,21 +5734,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5767,10 +5758,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668166</v>
+        <v>668182</v>
       </c>
       <c r="R52" t="n">
-        <v>6703694</v>
+        <v>6703746</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5829,10 +5820,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624348</v>
+        <v>129624385</v>
       </c>
       <c r="B53" t="n">
-        <v>91375</v>
+        <v>100983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5840,21 +5831,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5864,10 +5855,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668185</v>
+        <v>668149</v>
       </c>
       <c r="R53" t="n">
-        <v>6703715</v>
+        <v>6703811</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,7 +5917,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624393</v>
+        <v>129624403</v>
       </c>
       <c r="B54" t="n">
         <v>100983</v>
@@ -5961,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668182</v>
+        <v>668258</v>
       </c>
       <c r="R54" t="n">
-        <v>6703746</v>
+        <v>6703763</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,7 +6014,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624385</v>
+        <v>129624400</v>
       </c>
       <c r="B55" t="n">
         <v>100983</v>
@@ -6058,10 +6049,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668149</v>
+        <v>668331</v>
       </c>
       <c r="R55" t="n">
-        <v>6703811</v>
+        <v>6703743</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,45 +6111,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624403</v>
+        <v>129624367</v>
       </c>
       <c r="B56" t="n">
-        <v>100983</v>
+        <v>98794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668258</v>
+        <v>668253</v>
       </c>
       <c r="R56" t="n">
-        <v>6703763</v>
+        <v>6703781</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624400</v>
+        <v>129624339</v>
       </c>
       <c r="B57" t="n">
-        <v>100983</v>
+        <v>98772</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668331</v>
+        <v>668166</v>
       </c>
       <c r="R57" t="n">
-        <v>6703743</v>
+        <v>6703694</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624341</v>
       </c>
       <c r="B2" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624300</v>
+        <v>129624346</v>
       </c>
       <c r="B4" t="n">
-        <v>101890</v>
+        <v>98775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668262</v>
+        <v>668302</v>
       </c>
       <c r="R4" t="n">
-        <v>6703729</v>
+        <v>6703689</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +974,7 @@
         <v>129624391</v>
       </c>
       <c r="B5" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624346</v>
+        <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>98772</v>
+        <v>101893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668302</v>
+        <v>668262</v>
       </c>
       <c r="R6" t="n">
-        <v>6703689</v>
+        <v>6703729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624331</v>
+        <v>129624343</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>98775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668257</v>
+        <v>668165</v>
       </c>
       <c r="R7" t="n">
-        <v>6703774</v>
+        <v>6703856</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1270,7 +1265,7 @@
         <v>129624395</v>
       </c>
       <c r="B8" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1362,7 @@
         <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,45 +1456,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624370</v>
+        <v>129624331</v>
       </c>
       <c r="B10" t="n">
-        <v>105860</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668108</v>
+        <v>668257</v>
       </c>
       <c r="R10" t="n">
-        <v>6703888</v>
+        <v>6703774</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624343</v>
+        <v>129624370</v>
       </c>
       <c r="B11" t="n">
-        <v>98772</v>
+        <v>105863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668165</v>
+        <v>668108</v>
       </c>
       <c r="R11" t="n">
-        <v>6703856</v>
+        <v>6703888</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624394</v>
+        <v>129624374</v>
       </c>
       <c r="B12" t="n">
-        <v>100983</v>
+        <v>4779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668270</v>
+        <v>668256</v>
       </c>
       <c r="R12" t="n">
-        <v>6703699</v>
+        <v>6703754</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1752,32 +1767,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624308</v>
+        <v>129624394</v>
       </c>
       <c r="B13" t="n">
-        <v>97040</v>
+        <v>100986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668162</v>
+        <v>668270</v>
       </c>
       <c r="R13" t="n">
-        <v>6703712</v>
+        <v>6703699</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624313</v>
+        <v>129624308</v>
       </c>
       <c r="B14" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668179</v>
+        <v>668162</v>
       </c>
       <c r="R14" t="n">
-        <v>6703790</v>
+        <v>6703712</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1930,21 +1945,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,32 +1961,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624383</v>
+        <v>129624313</v>
       </c>
       <c r="B15" t="n">
-        <v>92252</v>
+        <v>97043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668279</v>
+        <v>668179</v>
       </c>
       <c r="R15" t="n">
-        <v>6703691</v>
+        <v>6703790</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624374</v>
+        <v>129624383</v>
       </c>
       <c r="B16" t="n">
-        <v>4779</v>
+        <v>92255</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668256</v>
+        <v>668279</v>
       </c>
       <c r="R16" t="n">
-        <v>6703754</v>
+        <v>6703691</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624392</v>
+        <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>100983</v>
+        <v>97043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668190</v>
+        <v>668108</v>
       </c>
       <c r="R17" t="n">
-        <v>6703813</v>
+        <v>6703891</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,6 +2266,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2282,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624390</v>
+        <v>129624392</v>
       </c>
       <c r="B18" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668123</v>
+        <v>668190</v>
       </c>
       <c r="R18" t="n">
-        <v>6703926</v>
+        <v>6703813</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2379,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624310</v>
+        <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>97040</v>
+        <v>100986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668108</v>
+        <v>668123</v>
       </c>
       <c r="R19" t="n">
-        <v>6703891</v>
+        <v>6703926</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2460,21 +2475,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2491,45 +2491,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624297</v>
+        <v>129624329</v>
       </c>
       <c r="B20" t="n">
-        <v>101890</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668176</v>
+        <v>668230</v>
       </c>
       <c r="R20" t="n">
-        <v>6703677</v>
+        <v>6703725</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2591,7 +2596,7 @@
         <v>129624396</v>
       </c>
       <c r="B21" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,54 +2690,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624366</v>
+        <v>129624297</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>101893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668160</v>
+        <v>668176</v>
       </c>
       <c r="R22" t="n">
-        <v>6703911</v>
+        <v>6703677</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,38 +2787,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624329</v>
+        <v>129624366</v>
       </c>
       <c r="B23" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668230</v>
+        <v>668160</v>
       </c>
       <c r="R23" t="n">
-        <v>6703725</v>
+        <v>6703911</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2893,45 +2893,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624401</v>
+        <v>129624328</v>
       </c>
       <c r="B24" t="n">
-        <v>100983</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668293</v>
+        <v>668312</v>
       </c>
       <c r="R24" t="n">
-        <v>6703720</v>
+        <v>6703726</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2990,50 +2995,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624328</v>
+        <v>129624368</v>
       </c>
       <c r="B25" t="n">
-        <v>57734</v>
+        <v>105863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668312</v>
+        <v>668181</v>
       </c>
       <c r="R25" t="n">
-        <v>6703726</v>
+        <v>6703685</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3092,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624368</v>
+        <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>105860</v>
+        <v>98775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668181</v>
+        <v>668257</v>
       </c>
       <c r="R26" t="n">
-        <v>6703685</v>
+        <v>6703688</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B27" t="n">
-        <v>98772</v>
+        <v>100986</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R27" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3289,7 +3289,7 @@
         <v>129624316</v>
       </c>
       <c r="B28" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>129624388</v>
       </c>
       <c r="B29" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624315</v>
+        <v>129624404</v>
       </c>
       <c r="B30" t="n">
-        <v>97040</v>
+        <v>87020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668277</v>
+        <v>668299</v>
       </c>
       <c r="R30" t="n">
-        <v>6703748</v>
+        <v>6703709</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3576,21 +3576,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3607,10 +3592,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624404</v>
+        <v>129624382</v>
       </c>
       <c r="B31" t="n">
-        <v>87017</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,34 +3603,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668299</v>
+        <v>668266</v>
       </c>
       <c r="R31" t="n">
-        <v>6703709</v>
+        <v>6703768</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3688,6 +3678,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3704,10 +3709,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624382</v>
+        <v>129624299</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>101893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,39 +3720,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668266</v>
+        <v>668169</v>
       </c>
       <c r="R32" t="n">
-        <v>6703768</v>
+        <v>6703716</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3790,21 +3790,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3821,32 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624299</v>
+        <v>129624315</v>
       </c>
       <c r="B33" t="n">
-        <v>101890</v>
+        <v>97043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668169</v>
+        <v>668277</v>
       </c>
       <c r="R33" t="n">
-        <v>6703716</v>
+        <v>6703748</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3902,6 +3887,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3921,7 +3921,7 @@
         <v>129624311</v>
       </c>
       <c r="B34" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129624296</v>
       </c>
       <c r="B35" t="n">
-        <v>101890</v>
+        <v>101893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>129624320</v>
       </c>
       <c r="B36" t="n">
-        <v>104265</v>
+        <v>104268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>129624325</v>
       </c>
       <c r="B37" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>129624372</v>
       </c>
       <c r="B38" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>129624369</v>
       </c>
       <c r="B39" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,32 +4509,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624373</v>
+        <v>129624307</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>97043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668112</v>
+        <v>668175</v>
       </c>
       <c r="R40" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4590,21 +4590,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4621,32 +4606,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624371</v>
+        <v>129624318</v>
       </c>
       <c r="B41" t="n">
-        <v>105860</v>
+        <v>97043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4656,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668163</v>
+        <v>668185</v>
       </c>
       <c r="R41" t="n">
-        <v>6703870</v>
+        <v>6703684</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4702,6 +4687,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624345</v>
+        <v>129624373</v>
       </c>
       <c r="B42" t="n">
-        <v>98772</v>
+        <v>4779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668302</v>
+        <v>668112</v>
       </c>
       <c r="R42" t="n">
-        <v>6703713</v>
+        <v>6703887</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,6 +4799,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4815,10 +4830,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624340</v>
+        <v>129624345</v>
       </c>
       <c r="B43" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4850,10 +4865,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668169</v>
+        <v>668302</v>
       </c>
       <c r="R43" t="n">
-        <v>6703716</v>
+        <v>6703713</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4912,32 +4927,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624307</v>
+        <v>129624340</v>
       </c>
       <c r="B44" t="n">
-        <v>97040</v>
+        <v>98775</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4947,10 +4962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668175</v>
+        <v>668169</v>
       </c>
       <c r="R44" t="n">
-        <v>6703703</v>
+        <v>6703716</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5009,32 +5024,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624318</v>
+        <v>129624371</v>
       </c>
       <c r="B45" t="n">
-        <v>97040</v>
+        <v>105863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5044,10 +5059,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668185</v>
+        <v>668163</v>
       </c>
       <c r="R45" t="n">
-        <v>6703684</v>
+        <v>6703870</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5090,21 +5105,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5124,7 +5124,7 @@
         <v>129624322</v>
       </c>
       <c r="B46" t="n">
-        <v>104265</v>
+        <v>104268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>129624298</v>
       </c>
       <c r="B47" t="n">
-        <v>101890</v>
+        <v>101893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5315,32 +5315,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624349</v>
+        <v>129624397</v>
       </c>
       <c r="B48" t="n">
-        <v>92055</v>
+        <v>100986</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668275</v>
+        <v>668305</v>
       </c>
       <c r="R48" t="n">
-        <v>6703756</v>
+        <v>6703751</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5396,21 +5396,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5427,32 +5412,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624397</v>
+        <v>129624349</v>
       </c>
       <c r="B49" t="n">
-        <v>100983</v>
+        <v>92058</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5462,10 +5447,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668305</v>
+        <v>668275</v>
       </c>
       <c r="R49" t="n">
-        <v>6703751</v>
+        <v>6703756</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5508,6 +5493,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5527,7 +5527,7 @@
         <v>129624327</v>
       </c>
       <c r="B50" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>129624348</v>
       </c>
       <c r="B51" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624393</v>
+        <v>129624339</v>
       </c>
       <c r="B52" t="n">
-        <v>100983</v>
+        <v>98775</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668182</v>
+        <v>668166</v>
       </c>
       <c r="R52" t="n">
-        <v>6703746</v>
+        <v>6703694</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,45 +5820,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624385</v>
+        <v>129624367</v>
       </c>
       <c r="B53" t="n">
-        <v>100983</v>
+        <v>98797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668149</v>
+        <v>668253</v>
       </c>
       <c r="R53" t="n">
-        <v>6703811</v>
+        <v>6703781</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5917,10 +5926,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624403</v>
+        <v>129624393</v>
       </c>
       <c r="B54" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5952,10 +5961,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668258</v>
+        <v>668182</v>
       </c>
       <c r="R54" t="n">
-        <v>6703763</v>
+        <v>6703746</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6014,10 +6023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624400</v>
+        <v>129624385</v>
       </c>
       <c r="B55" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6049,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668331</v>
+        <v>668149</v>
       </c>
       <c r="R55" t="n">
-        <v>6703743</v>
+        <v>6703811</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6111,54 +6120,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624367</v>
+        <v>129624403</v>
       </c>
       <c r="B56" t="n">
-        <v>98794</v>
+        <v>100986</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668253</v>
+        <v>668258</v>
       </c>
       <c r="R56" t="n">
-        <v>6703781</v>
+        <v>6703763</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624339</v>
+        <v>129624400</v>
       </c>
       <c r="B57" t="n">
-        <v>98772</v>
+        <v>100986</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,21 +6228,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668166</v>
+        <v>668331</v>
       </c>
       <c r="R57" t="n">
-        <v>6703694</v>
+        <v>6703743</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6317,7 +6317,7 @@
         <v>129624309</v>
       </c>
       <c r="B58" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>129624317</v>
       </c>
       <c r="B59" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129624347</v>
       </c>
       <c r="B60" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>129624387</v>
       </c>
       <c r="B62" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>129624314</v>
       </c>
       <c r="B63" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>129624389</v>
       </c>
       <c r="B64" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>129624323</v>
       </c>
       <c r="B65" t="n">
-        <v>110950</v>
+        <v>110953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>129624301</v>
       </c>
       <c r="B66" t="n">
-        <v>101890</v>
+        <v>101893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624330</v>
+        <v>129624300</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>101893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668289</v>
+        <v>668262</v>
       </c>
       <c r="R3" t="n">
-        <v>6703714</v>
+        <v>6703729</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624346</v>
+        <v>129624330</v>
       </c>
       <c r="B4" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668302</v>
+        <v>668289</v>
       </c>
       <c r="R4" t="n">
-        <v>6703689</v>
+        <v>6703714</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624391</v>
+        <v>129624346</v>
       </c>
       <c r="B5" t="n">
-        <v>100986</v>
+        <v>98775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668163</v>
+        <v>668302</v>
       </c>
       <c r="R5" t="n">
-        <v>6703831</v>
+        <v>6703689</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624300</v>
+        <v>129624391</v>
       </c>
       <c r="B6" t="n">
-        <v>101893</v>
+        <v>100986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668262</v>
+        <v>668163</v>
       </c>
       <c r="R6" t="n">
-        <v>6703729</v>
+        <v>6703831</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624343</v>
+        <v>129624395</v>
       </c>
       <c r="B7" t="n">
-        <v>98775</v>
+        <v>100986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668165</v>
+        <v>668288</v>
       </c>
       <c r="R7" t="n">
-        <v>6703856</v>
+        <v>6703696</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624395</v>
+        <v>129624399</v>
       </c>
       <c r="B8" t="n">
         <v>100986</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668288</v>
+        <v>668154</v>
       </c>
       <c r="R8" t="n">
-        <v>6703696</v>
+        <v>6703899</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,45 +1359,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624399</v>
+        <v>129624331</v>
       </c>
       <c r="B9" t="n">
-        <v>100986</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668154</v>
+        <v>668257</v>
       </c>
       <c r="R9" t="n">
-        <v>6703899</v>
+        <v>6703774</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,50 +1461,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624331</v>
+        <v>129624343</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>98775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668257</v>
+        <v>668165</v>
       </c>
       <c r="R10" t="n">
-        <v>6703774</v>
+        <v>6703856</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624310</v>
+        <v>129624392</v>
       </c>
       <c r="B17" t="n">
-        <v>97043</v>
+        <v>100986</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668108</v>
+        <v>668190</v>
       </c>
       <c r="R17" t="n">
-        <v>6703891</v>
+        <v>6703813</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,21 +2266,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2297,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624392</v>
+        <v>129624390</v>
       </c>
       <c r="B18" t="n">
         <v>100986</v>
@@ -2332,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668190</v>
+        <v>668123</v>
       </c>
       <c r="R18" t="n">
-        <v>6703813</v>
+        <v>6703926</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2394,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624390</v>
+        <v>129624310</v>
       </c>
       <c r="B19" t="n">
-        <v>100986</v>
+        <v>97043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668123</v>
+        <v>668108</v>
       </c>
       <c r="R19" t="n">
-        <v>6703926</v>
+        <v>6703891</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2475,6 +2460,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B26" t="n">
-        <v>98775</v>
+        <v>100986</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R26" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624401</v>
+        <v>129624344</v>
       </c>
       <c r="B27" t="n">
-        <v>100986</v>
+        <v>98775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668293</v>
+        <v>668257</v>
       </c>
       <c r="R27" t="n">
-        <v>6703720</v>
+        <v>6703688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3918,32 +3918,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624311</v>
+        <v>129624296</v>
       </c>
       <c r="B34" t="n">
-        <v>97043</v>
+        <v>101893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668158</v>
+        <v>668152</v>
       </c>
       <c r="R34" t="n">
-        <v>6703911</v>
+        <v>6703756</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4015,32 +4015,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624296</v>
+        <v>129624311</v>
       </c>
       <c r="B35" t="n">
-        <v>101893</v>
+        <v>97043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668152</v>
+        <v>668158</v>
       </c>
       <c r="R35" t="n">
-        <v>6703756</v>
+        <v>6703911</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4718,10 +4718,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624373</v>
+        <v>129624345</v>
       </c>
       <c r="B42" t="n">
-        <v>4779</v>
+        <v>98775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668112</v>
+        <v>668302</v>
       </c>
       <c r="R42" t="n">
-        <v>6703887</v>
+        <v>6703713</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,21 +4799,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4830,7 +4815,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624345</v>
+        <v>129624340</v>
       </c>
       <c r="B43" t="n">
         <v>98775</v>
@@ -4865,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668302</v>
+        <v>668169</v>
       </c>
       <c r="R43" t="n">
-        <v>6703713</v>
+        <v>6703716</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4927,10 +4912,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624340</v>
+        <v>129624322</v>
       </c>
       <c r="B44" t="n">
-        <v>98775</v>
+        <v>104268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4938,21 +4923,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4962,10 +4947,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668169</v>
+        <v>668300</v>
       </c>
       <c r="R44" t="n">
-        <v>6703716</v>
+        <v>6703703</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5024,10 +5009,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624371</v>
+        <v>129624373</v>
       </c>
       <c r="B45" t="n">
-        <v>105863</v>
+        <v>4779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5035,21 +5020,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5059,10 +5044,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668163</v>
+        <v>668112</v>
       </c>
       <c r="R45" t="n">
-        <v>6703870</v>
+        <v>6703887</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5105,6 +5090,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624322</v>
+        <v>129624371</v>
       </c>
       <c r="B46" t="n">
-        <v>104268</v>
+        <v>105863</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668300</v>
+        <v>668163</v>
       </c>
       <c r="R46" t="n">
-        <v>6703703</v>
+        <v>6703870</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B62" t="n">
-        <v>100986</v>
+        <v>97043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R62" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>97043</v>
+        <v>100986</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R63" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624300</v>
+        <v>129624330</v>
       </c>
       <c r="B3" t="n">
-        <v>101893</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668262</v>
+        <v>668289</v>
       </c>
       <c r="R3" t="n">
-        <v>6703729</v>
+        <v>6703714</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624330</v>
+        <v>129624346</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>98775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668289</v>
+        <v>668302</v>
       </c>
       <c r="R4" t="n">
-        <v>6703714</v>
+        <v>6703689</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624346</v>
+        <v>129624391</v>
       </c>
       <c r="B5" t="n">
-        <v>98775</v>
+        <v>100986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668302</v>
+        <v>668163</v>
       </c>
       <c r="R5" t="n">
-        <v>6703689</v>
+        <v>6703831</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624391</v>
+        <v>129624300</v>
       </c>
       <c r="B6" t="n">
-        <v>100986</v>
+        <v>101893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668163</v>
+        <v>668262</v>
       </c>
       <c r="R6" t="n">
-        <v>6703831</v>
+        <v>6703729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624395</v>
+        <v>129624343</v>
       </c>
       <c r="B7" t="n">
-        <v>100986</v>
+        <v>98775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668288</v>
+        <v>668165</v>
       </c>
       <c r="R7" t="n">
-        <v>6703696</v>
+        <v>6703856</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624399</v>
+        <v>129624395</v>
       </c>
       <c r="B8" t="n">
         <v>100986</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668154</v>
+        <v>668288</v>
       </c>
       <c r="R8" t="n">
-        <v>6703899</v>
+        <v>6703696</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,50 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624331</v>
+        <v>129624399</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>100986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668257</v>
+        <v>668154</v>
       </c>
       <c r="R9" t="n">
-        <v>6703774</v>
+        <v>6703899</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,45 +1456,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624343</v>
+        <v>129624331</v>
       </c>
       <c r="B10" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668165</v>
+        <v>668257</v>
       </c>
       <c r="R10" t="n">
-        <v>6703856</v>
+        <v>6703774</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624392</v>
+        <v>129624310</v>
       </c>
       <c r="B17" t="n">
-        <v>100986</v>
+        <v>97043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668190</v>
+        <v>668108</v>
       </c>
       <c r="R17" t="n">
-        <v>6703813</v>
+        <v>6703891</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,6 +2266,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2282,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624390</v>
+        <v>129624392</v>
       </c>
       <c r="B18" t="n">
         <v>100986</v>
@@ -2317,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668123</v>
+        <v>668190</v>
       </c>
       <c r="R18" t="n">
-        <v>6703926</v>
+        <v>6703813</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2379,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624310</v>
+        <v>129624390</v>
       </c>
       <c r="B19" t="n">
-        <v>97043</v>
+        <v>100986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668108</v>
+        <v>668123</v>
       </c>
       <c r="R19" t="n">
-        <v>6703891</v>
+        <v>6703926</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2460,21 +2475,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624401</v>
+        <v>129624344</v>
       </c>
       <c r="B26" t="n">
-        <v>100986</v>
+        <v>98775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3103,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668293</v>
+        <v>668257</v>
       </c>
       <c r="R26" t="n">
-        <v>6703720</v>
+        <v>6703688</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624344</v>
+        <v>129624401</v>
       </c>
       <c r="B27" t="n">
-        <v>98775</v>
+        <v>100986</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668257</v>
+        <v>668293</v>
       </c>
       <c r="R27" t="n">
-        <v>6703688</v>
+        <v>6703720</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -6722,32 +6722,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B62" t="n">
-        <v>97043</v>
+        <v>100986</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R62" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6819,32 +6819,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624387</v>
+        <v>129624314</v>
       </c>
       <c r="B63" t="n">
-        <v>100986</v>
+        <v>97043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668132</v>
+        <v>668262</v>
       </c>
       <c r="R63" t="n">
-        <v>6703833</v>
+        <v>6703759</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624389</v>
+        <v>129624301</v>
       </c>
       <c r="B64" t="n">
-        <v>100986</v>
+        <v>101893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668107</v>
+        <v>668194</v>
       </c>
       <c r="R64" t="n">
-        <v>6703910</v>
+        <v>6703673</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624323</v>
+        <v>129624389</v>
       </c>
       <c r="B65" t="n">
-        <v>110953</v>
+        <v>100986</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7024,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668134</v>
+        <v>668107</v>
       </c>
       <c r="R65" t="n">
-        <v>6703832</v>
+        <v>6703910</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7086,18 +7086,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7110,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624301</v>
+        <v>129624323</v>
       </c>
       <c r="B66" t="n">
-        <v>101893</v>
+        <v>110953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,21 +7121,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7151,10 +7145,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668194</v>
+        <v>668134</v>
       </c>
       <c r="R66" t="n">
-        <v>6703673</v>
+        <v>6703832</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7189,12 +7183,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4912,10 +4912,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624322</v>
+        <v>129624357</v>
       </c>
       <c r="B44" t="n">
-        <v>104268</v>
+        <v>97662</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4923,23 +4923,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>221944</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4947,10 +4943,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668300</v>
+        <v>668270</v>
       </c>
       <c r="R44" t="n">
-        <v>6703703</v>
+        <v>6703694</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4991,6 +4987,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5009,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624373</v>
+        <v>129624322</v>
       </c>
       <c r="B45" t="n">
-        <v>4779</v>
+        <v>104268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5020,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>222412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5044,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668112</v>
+        <v>668300</v>
       </c>
       <c r="R45" t="n">
-        <v>6703887</v>
+        <v>6703703</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5090,21 +5087,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5121,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624371</v>
+        <v>129624373</v>
       </c>
       <c r="B46" t="n">
-        <v>105863</v>
+        <v>4779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5156,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668163</v>
+        <v>668112</v>
       </c>
       <c r="R46" t="n">
-        <v>6703870</v>
+        <v>6703887</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5202,6 +5184,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5218,10 +5215,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129624298</v>
+        <v>129624371</v>
       </c>
       <c r="B47" t="n">
-        <v>101893</v>
+        <v>105863</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5229,21 +5226,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5253,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668171</v>
+        <v>668163</v>
       </c>
       <c r="R47" t="n">
-        <v>6703708</v>
+        <v>6703870</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5315,10 +5312,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624397</v>
+        <v>129624298</v>
       </c>
       <c r="B48" t="n">
-        <v>100986</v>
+        <v>101893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5326,21 +5323,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5350,10 +5347,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668305</v>
+        <v>668171</v>
       </c>
       <c r="R48" t="n">
-        <v>6703751</v>
+        <v>6703708</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5412,32 +5409,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624349</v>
+        <v>129624397</v>
       </c>
       <c r="B49" t="n">
-        <v>92058</v>
+        <v>100986</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5447,10 +5444,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668275</v>
+        <v>668305</v>
       </c>
       <c r="R49" t="n">
-        <v>6703756</v>
+        <v>6703751</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5493,21 +5490,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5524,50 +5506,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624327</v>
+        <v>129624349</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>92058</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668173</v>
+        <v>668275</v>
       </c>
       <c r="R50" t="n">
-        <v>6703787</v>
+        <v>6703756</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5610,6 +5587,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5626,45 +5618,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624348</v>
+        <v>129624327</v>
       </c>
       <c r="B51" t="n">
-        <v>91378</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668185</v>
+        <v>668173</v>
       </c>
       <c r="R51" t="n">
-        <v>6703715</v>
+        <v>6703787</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5723,10 +5720,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624339</v>
+        <v>129624348</v>
       </c>
       <c r="B52" t="n">
-        <v>98775</v>
+        <v>91378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5734,21 +5731,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5758,10 +5755,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668166</v>
+        <v>668185</v>
       </c>
       <c r="R52" t="n">
-        <v>6703694</v>
+        <v>6703715</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5820,54 +5817,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624367</v>
+        <v>129624339</v>
       </c>
       <c r="B53" t="n">
-        <v>98797</v>
+        <v>98775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668253</v>
+        <v>668166</v>
       </c>
       <c r="R53" t="n">
-        <v>6703781</v>
+        <v>6703694</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5926,45 +5914,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624393</v>
+        <v>129624367</v>
       </c>
       <c r="B54" t="n">
-        <v>100986</v>
+        <v>98797</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668182</v>
+        <v>668253</v>
       </c>
       <c r="R54" t="n">
-        <v>6703746</v>
+        <v>6703781</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6023,7 +6020,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624385</v>
+        <v>129624393</v>
       </c>
       <c r="B55" t="n">
         <v>100986</v>
@@ -6058,10 +6055,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668149</v>
+        <v>668182</v>
       </c>
       <c r="R55" t="n">
-        <v>6703811</v>
+        <v>6703746</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,7 +6117,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624403</v>
+        <v>129624385</v>
       </c>
       <c r="B56" t="n">
         <v>100986</v>
@@ -6155,10 +6152,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668258</v>
+        <v>668149</v>
       </c>
       <c r="R56" t="n">
-        <v>6703763</v>
+        <v>6703811</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6217,7 +6214,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624400</v>
+        <v>129624403</v>
       </c>
       <c r="B57" t="n">
         <v>100986</v>
@@ -6252,10 +6249,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668331</v>
+        <v>668258</v>
       </c>
       <c r="R57" t="n">
-        <v>6703743</v>
+        <v>6703763</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6314,32 +6311,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624309</v>
+        <v>129624400</v>
       </c>
       <c r="B58" t="n">
-        <v>97043</v>
+        <v>100986</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6346,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668130</v>
+        <v>668331</v>
       </c>
       <c r="R58" t="n">
-        <v>6703878</v>
+        <v>6703743</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6411,7 +6408,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624317</v>
+        <v>129624309</v>
       </c>
       <c r="B59" t="n">
         <v>97043</v>
@@ -6446,10 +6443,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668229</v>
+        <v>668130</v>
       </c>
       <c r="R59" t="n">
-        <v>6703722</v>
+        <v>6703878</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6508,32 +6505,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624347</v>
+        <v>129624317</v>
       </c>
       <c r="B60" t="n">
-        <v>98775</v>
+        <v>97043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6540,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668269</v>
+        <v>668229</v>
       </c>
       <c r="R60" t="n">
-        <v>6703736</v>
+        <v>6703722</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6605,10 +6602,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129624381</v>
+        <v>129624347</v>
       </c>
       <c r="B61" t="n">
-        <v>5177</v>
+        <v>98775</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6616,39 +6613,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668298</v>
+        <v>668269</v>
       </c>
       <c r="R61" t="n">
-        <v>6703728</v>
+        <v>6703736</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6691,21 +6683,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6722,10 +6699,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624387</v>
+        <v>129624381</v>
       </c>
       <c r="B62" t="n">
-        <v>100986</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6733,34 +6710,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668132</v>
+        <v>668298</v>
       </c>
       <c r="R62" t="n">
-        <v>6703833</v>
+        <v>6703728</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6803,6 +6785,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6819,32 +6816,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624314</v>
+        <v>129624387</v>
       </c>
       <c r="B63" t="n">
-        <v>97043</v>
+        <v>100986</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6854,10 +6851,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668262</v>
+        <v>668132</v>
       </c>
       <c r="R63" t="n">
-        <v>6703759</v>
+        <v>6703833</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6916,32 +6913,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624301</v>
+        <v>129624314</v>
       </c>
       <c r="B64" t="n">
-        <v>101893</v>
+        <v>97043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6948,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668194</v>
+        <v>668262</v>
       </c>
       <c r="R64" t="n">
-        <v>6703673</v>
+        <v>6703759</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7013,10 +7010,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624389</v>
+        <v>129624301</v>
       </c>
       <c r="B65" t="n">
-        <v>100986</v>
+        <v>101893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,21 +7021,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7048,10 +7045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668107</v>
+        <v>668194</v>
       </c>
       <c r="R65" t="n">
-        <v>6703910</v>
+        <v>6703673</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7110,10 +7107,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624323</v>
+        <v>129624389</v>
       </c>
       <c r="B66" t="n">
-        <v>110953</v>
+        <v>100986</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7121,21 +7118,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7145,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668134</v>
+        <v>668107</v>
       </c>
       <c r="R66" t="n">
-        <v>6703832</v>
+        <v>6703910</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7183,18 +7180,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +7201,109 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129624323</v>
+      </c>
+      <c r="B67" t="n">
+        <v>110953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>668134</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6703832</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9346,10 +9346,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134392452</v>
+        <v>134392443</v>
       </c>
       <c r="B88" t="n">
-        <v>104693</v>
+        <v>102304</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9357,21 +9357,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>667981</v>
+        <v>667882</v>
       </c>
       <c r="R88" t="n">
-        <v>6703672</v>
+        <v>6703730</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9443,10 +9443,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134392443</v>
+        <v>134392452</v>
       </c>
       <c r="B89" t="n">
-        <v>102304</v>
+        <v>104693</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9454,21 +9454,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>667882</v>
+        <v>667981</v>
       </c>
       <c r="R89" t="n">
-        <v>6703730</v>
+        <v>6703672</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9537,6 +9537,1461 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134416563</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>667808</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6703766</v>
+      </c>
+      <c r="S90" t="n">
+        <v>8</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134416579</v>
+      </c>
+      <c r="B91" t="n">
+        <v>75454</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>667925</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6703706</v>
+      </c>
+      <c r="S91" t="n">
+        <v>14</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134416556</v>
+      </c>
+      <c r="B92" t="n">
+        <v>102304</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>667771</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6703557</v>
+      </c>
+      <c r="S92" t="n">
+        <v>12</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134416558</v>
+      </c>
+      <c r="B93" t="n">
+        <v>106310</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>667771</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6703573</v>
+      </c>
+      <c r="S93" t="n">
+        <v>12</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134416580</v>
+      </c>
+      <c r="B94" t="n">
+        <v>75454</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>667928</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6703706</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134416560</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101389</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>667777</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6703601</v>
+      </c>
+      <c r="S95" t="n">
+        <v>16</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134416566</v>
+      </c>
+      <c r="B96" t="n">
+        <v>102304</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>667829</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6703833</v>
+      </c>
+      <c r="S96" t="n">
+        <v>13</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>134416572</v>
+      </c>
+      <c r="B97" t="n">
+        <v>97421</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>53</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>667863</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6703823</v>
+      </c>
+      <c r="S97" t="n">
+        <v>13</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134416567</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101389</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>667829</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6703833</v>
+      </c>
+      <c r="S98" t="n">
+        <v>9</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134416565</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97421</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>53</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>667827</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6703851</v>
+      </c>
+      <c r="S99" t="n">
+        <v>13</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>134416576</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>667875</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6703750</v>
+      </c>
+      <c r="S100" t="n">
+        <v>12</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>134416577</v>
+      </c>
+      <c r="B101" t="n">
+        <v>75454</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>667921</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6703707</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>134416562</v>
+      </c>
+      <c r="B102" t="n">
+        <v>97421</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>53</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>667778</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6703686</v>
+      </c>
+      <c r="S102" t="n">
+        <v>19</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>134416574</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>667872</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6703790</v>
+      </c>
+      <c r="S103" t="n">
+        <v>11</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>134416581</v>
+      </c>
+      <c r="B104" t="n">
+        <v>75454</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>667937</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6703678</v>
+      </c>
+      <c r="S104" t="n">
+        <v>12</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -7310,7 +7310,7 @@
         <v>134392487</v>
       </c>
       <c r="B68" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>134392488</v>
       </c>
       <c r="B69" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>134392490</v>
       </c>
       <c r="B70" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>134392453</v>
       </c>
       <c r="B71" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>134392441</v>
       </c>
       <c r="B72" t="n">
-        <v>102304</v>
+        <v>102311</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>134392442</v>
       </c>
       <c r="B73" t="n">
-        <v>102304</v>
+        <v>102311</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>134392447</v>
       </c>
       <c r="B74" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>134392446</v>
       </c>
       <c r="B75" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>134392499</v>
       </c>
       <c r="B76" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>134392500</v>
       </c>
       <c r="B77" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>134392472</v>
       </c>
       <c r="B78" t="n">
-        <v>99159</v>
+        <v>99166</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>134392496</v>
       </c>
       <c r="B79" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>134392448</v>
       </c>
       <c r="B80" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>134392497</v>
       </c>
       <c r="B81" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134392459</v>
+        <v>134392498</v>
       </c>
       <c r="B82" t="n">
-        <v>96519</v>
+        <v>101396</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8736,21 +8736,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>667846</v>
+        <v>667852</v>
       </c>
       <c r="R82" t="n">
-        <v>6703798</v>
+        <v>6703807</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8806,21 +8806,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -8837,10 +8822,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134392498</v>
+        <v>134392451</v>
       </c>
       <c r="B83" t="n">
-        <v>101389</v>
+        <v>99212</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8848,21 +8833,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8872,10 +8857,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>667852</v>
+        <v>667994</v>
       </c>
       <c r="R83" t="n">
-        <v>6703807</v>
+        <v>6703722</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8934,10 +8919,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134392451</v>
+        <v>134392459</v>
       </c>
       <c r="B84" t="n">
-        <v>99205</v>
+        <v>96526</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8945,21 +8930,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219847</v>
+        <v>2818</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8969,10 +8954,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>667994</v>
+        <v>667846</v>
       </c>
       <c r="R84" t="n">
-        <v>6703722</v>
+        <v>6703798</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9015,6 +9000,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9146,7 +9146,7 @@
         <v>134392502</v>
       </c>
       <c r="B86" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>134392456</v>
       </c>
       <c r="B87" t="n">
-        <v>111457</v>
+        <v>111464</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9346,10 +9346,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134392443</v>
+        <v>134392452</v>
       </c>
       <c r="B88" t="n">
-        <v>102304</v>
+        <v>104700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9357,21 +9357,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>667882</v>
+        <v>667981</v>
       </c>
       <c r="R88" t="n">
-        <v>6703730</v>
+        <v>6703672</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9443,10 +9443,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134392452</v>
+        <v>134392443</v>
       </c>
       <c r="B89" t="n">
-        <v>104693</v>
+        <v>102311</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9454,21 +9454,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>667981</v>
+        <v>667882</v>
       </c>
       <c r="R89" t="n">
-        <v>6703672</v>
+        <v>6703730</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9640,7 +9640,7 @@
         <v>134416579</v>
       </c>
       <c r="B91" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>134416556</v>
       </c>
       <c r="B92" t="n">
-        <v>102304</v>
+        <v>102311</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>134416558</v>
       </c>
       <c r="B93" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>134416580</v>
       </c>
       <c r="B94" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>134416560</v>
       </c>
       <c r="B95" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>134416566</v>
       </c>
       <c r="B96" t="n">
-        <v>102304</v>
+        <v>102311</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>134416572</v>
       </c>
       <c r="B97" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>134416567</v>
       </c>
       <c r="B98" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>134416565</v>
       </c>
       <c r="B99" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>134416576</v>
       </c>
       <c r="B100" t="n">
-        <v>99159</v>
+        <v>99166</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>134416577</v>
       </c>
       <c r="B101" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10704,32 +10704,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134416562</v>
+        <v>134416574</v>
       </c>
       <c r="B102" t="n">
-        <v>97421</v>
+        <v>99105</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>667778</v>
+        <v>667872</v>
       </c>
       <c r="R102" t="n">
-        <v>6703686</v>
+        <v>6703790</v>
       </c>
       <c r="S102" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10801,32 +10801,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134416574</v>
+        <v>134416562</v>
       </c>
       <c r="B103" t="n">
-        <v>99098</v>
+        <v>97428</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10836,13 +10836,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>667872</v>
+        <v>667778</v>
       </c>
       <c r="R103" t="n">
-        <v>6703790</v>
+        <v>6703686</v>
       </c>
       <c r="S103" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>134416581</v>
       </c>
       <c r="B104" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624341</v>
+        <v>129624307</v>
       </c>
       <c r="B2" t="n">
-        <v>98775</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668131</v>
+        <v>668175</v>
       </c>
       <c r="R2" t="n">
-        <v>6703835</v>
+        <v>6703703</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624330</v>
+        <v>129624308</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668289</v>
+        <v>668162</v>
       </c>
       <c r="R3" t="n">
-        <v>6703714</v>
+        <v>6703712</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624346</v>
+        <v>129624309</v>
       </c>
       <c r="B4" t="n">
-        <v>98775</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668302</v>
+        <v>668130</v>
       </c>
       <c r="R4" t="n">
-        <v>6703689</v>
+        <v>6703878</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624391</v>
+        <v>129624310</v>
       </c>
       <c r="B5" t="n">
-        <v>100986</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668163</v>
+        <v>668108</v>
       </c>
       <c r="R5" t="n">
-        <v>6703831</v>
+        <v>6703891</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1052,6 +1047,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1068,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624300</v>
+        <v>129624311</v>
       </c>
       <c r="B6" t="n">
-        <v>101893</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668262</v>
+        <v>668158</v>
       </c>
       <c r="R6" t="n">
-        <v>6703729</v>
+        <v>6703911</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624343</v>
+        <v>129624313</v>
       </c>
       <c r="B7" t="n">
-        <v>98775</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668165</v>
+        <v>668179</v>
       </c>
       <c r="R7" t="n">
-        <v>6703856</v>
+        <v>6703790</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1246,6 +1256,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1262,32 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624395</v>
+        <v>129624314</v>
       </c>
       <c r="B8" t="n">
-        <v>100986</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668288</v>
+        <v>668262</v>
       </c>
       <c r="R8" t="n">
-        <v>6703696</v>
+        <v>6703759</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,32 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624399</v>
+        <v>129624315</v>
       </c>
       <c r="B9" t="n">
-        <v>100986</v>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668154</v>
+        <v>668277</v>
       </c>
       <c r="R9" t="n">
-        <v>6703899</v>
+        <v>6703748</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1440,6 +1465,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1456,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624331</v>
+        <v>129624316</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668257</v>
+        <v>668262</v>
       </c>
       <c r="R10" t="n">
-        <v>6703774</v>
+        <v>6703727</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1542,6 +1577,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1558,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624370</v>
+        <v>129624317</v>
       </c>
       <c r="B11" t="n">
-        <v>105863</v>
+        <v>97358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668108</v>
+        <v>668229</v>
       </c>
       <c r="R11" t="n">
-        <v>6703888</v>
+        <v>6703722</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624374</v>
+        <v>129624318</v>
       </c>
       <c r="B12" t="n">
-        <v>4779</v>
+        <v>97358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668256</v>
+        <v>668185</v>
       </c>
       <c r="R12" t="n">
-        <v>6703754</v>
+        <v>6703684</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1739,17 +1789,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1767,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624394</v>
+        <v>134392446</v>
       </c>
       <c r="B13" t="n">
-        <v>100986</v>
+        <v>97435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668270</v>
+        <v>667878</v>
       </c>
       <c r="R13" t="n">
-        <v>6703699</v>
+        <v>6703790</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1832,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624308</v>
+        <v>134392447</v>
       </c>
       <c r="B14" t="n">
-        <v>97043</v>
+        <v>97435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,13 +1949,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668162</v>
+        <v>667871</v>
       </c>
       <c r="R14" t="n">
-        <v>6703712</v>
+        <v>6703758</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1929,12 +1979,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1945,6 +1995,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624313</v>
+        <v>134392448</v>
       </c>
       <c r="B15" t="n">
-        <v>97043</v>
+        <v>97435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668179</v>
+        <v>668010</v>
       </c>
       <c r="R15" t="n">
-        <v>6703790</v>
+        <v>6703823</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2026,12 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2045,17 +2110,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2073,48 +2138,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624383</v>
+        <v>134416562</v>
       </c>
       <c r="B16" t="n">
-        <v>92255</v>
+        <v>97435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668279</v>
+        <v>667778</v>
       </c>
       <c r="R16" t="n">
-        <v>6703691</v>
+        <v>6703686</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2138,12 +2203,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2154,41 +2219,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624310</v>
+        <v>134416565</v>
       </c>
       <c r="B17" t="n">
-        <v>97043</v>
+        <v>97435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,17 +2266,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668108</v>
+        <v>667827</v>
       </c>
       <c r="R17" t="n">
-        <v>6703891</v>
+        <v>6703851</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2250,12 +2300,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,79 +2316,64 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624392</v>
+        <v>134416572</v>
       </c>
       <c r="B18" t="n">
-        <v>100986</v>
+        <v>97435</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668190</v>
+        <v>667863</v>
       </c>
       <c r="R18" t="n">
-        <v>6703813</v>
+        <v>6703823</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2362,12 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624390</v>
+        <v>129624372</v>
       </c>
       <c r="B19" t="n">
-        <v>100986</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,34 +2440,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668123</v>
+        <v>668296</v>
       </c>
       <c r="R19" t="n">
-        <v>6703926</v>
+        <v>6703695</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2491,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624329</v>
+        <v>129624349</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>92369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,39 +2546,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668230</v>
+        <v>668275</v>
       </c>
       <c r="R20" t="n">
-        <v>6703725</v>
+        <v>6703756</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2577,6 +2616,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2593,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624396</v>
+        <v>129624383</v>
       </c>
       <c r="B21" t="n">
-        <v>100986</v>
+        <v>92564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2604,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668305</v>
+        <v>668279</v>
       </c>
       <c r="R21" t="n">
-        <v>6703732</v>
+        <v>6703691</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2674,6 +2728,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2690,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624297</v>
+        <v>134392484</v>
       </c>
       <c r="B22" t="n">
-        <v>101893</v>
+        <v>96410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2770,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>2812</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,13 +2794,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668176</v>
+        <v>667795</v>
       </c>
       <c r="R22" t="n">
-        <v>6703677</v>
+        <v>6703380</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2824,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,57 +2856,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624366</v>
+        <v>134392485</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>96410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668160</v>
+        <v>667771</v>
       </c>
       <c r="R23" t="n">
-        <v>6703911</v>
+        <v>6703593</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2861,12 +2921,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2893,53 +2953,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624328</v>
+        <v>134392486</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>96410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668312</v>
+        <v>667800</v>
       </c>
       <c r="R24" t="n">
-        <v>6703726</v>
+        <v>6703778</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2963,12 +3018,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2995,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624368</v>
+        <v>129624325</v>
       </c>
       <c r="B25" t="n">
-        <v>105863</v>
+        <v>96458</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3030,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668181</v>
+        <v>668318</v>
       </c>
       <c r="R25" t="n">
-        <v>6703685</v>
+        <v>6703714</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3092,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624344</v>
+        <v>134392459</v>
       </c>
       <c r="B26" t="n">
-        <v>98775</v>
+        <v>96533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,21 +3158,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3127,13 +3182,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668257</v>
+        <v>667846</v>
       </c>
       <c r="R26" t="n">
-        <v>6703688</v>
+        <v>6703798</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3157,12 +3212,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3173,6 +3228,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3189,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624401</v>
+        <v>129624348</v>
       </c>
       <c r="B27" t="n">
-        <v>100986</v>
+        <v>91680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,21 +3270,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3224,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668293</v>
+        <v>668185</v>
       </c>
       <c r="R27" t="n">
-        <v>6703720</v>
+        <v>6703715</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3286,32 +3356,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624316</v>
+        <v>129624404</v>
       </c>
       <c r="B28" t="n">
-        <v>97043</v>
+        <v>87309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668262</v>
+        <v>668299</v>
       </c>
       <c r="R28" t="n">
-        <v>6703727</v>
+        <v>6703709</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,21 +3437,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3398,32 +3453,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624388</v>
+        <v>134392487</v>
       </c>
       <c r="B29" t="n">
-        <v>100986</v>
+        <v>75468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,13 +3488,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668122</v>
+        <v>667926</v>
       </c>
       <c r="R29" t="n">
-        <v>6703878</v>
+        <v>6703698</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3463,12 +3518,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,6 +3534,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3495,32 +3565,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624404</v>
+        <v>134392488</v>
       </c>
       <c r="B30" t="n">
-        <v>87020</v>
+        <v>75468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,13 +3600,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668299</v>
+        <v>667914</v>
       </c>
       <c r="R30" t="n">
-        <v>6703709</v>
+        <v>6703674</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3560,12 +3630,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3576,6 +3646,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3592,50 +3677,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624382</v>
+        <v>134416577</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>75468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668266</v>
+        <v>667921</v>
       </c>
       <c r="R31" t="n">
-        <v>6703768</v>
+        <v>6703707</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3662,12 +3742,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3678,79 +3758,64 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624299</v>
+        <v>134416579</v>
       </c>
       <c r="B32" t="n">
-        <v>101893</v>
+        <v>75468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668169</v>
+        <v>667925</v>
       </c>
       <c r="R32" t="n">
-        <v>6703716</v>
+        <v>6703706</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3774,12 +3839,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,22 +3859,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624315</v>
+        <v>134416580</v>
       </c>
       <c r="B33" t="n">
-        <v>97043</v>
+        <v>75468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,37 +3882,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668277</v>
+        <v>667928</v>
       </c>
       <c r="R33" t="n">
-        <v>6703748</v>
+        <v>6703706</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3871,12 +3936,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,79 +3952,64 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624296</v>
+        <v>134416581</v>
       </c>
       <c r="B34" t="n">
-        <v>101893</v>
+        <v>75468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221235</v>
+        <v>6426</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668152</v>
+        <v>667937</v>
       </c>
       <c r="R34" t="n">
-        <v>6703756</v>
+        <v>6703678</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3983,12 +4033,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,57 +4053,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129624311</v>
+        <v>129624327</v>
       </c>
       <c r="B35" t="n">
-        <v>97043</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668158</v>
+        <v>668173</v>
       </c>
       <c r="R35" t="n">
-        <v>6703911</v>
+        <v>6703787</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4112,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624320</v>
+        <v>129624328</v>
       </c>
       <c r="B36" t="n">
-        <v>104268</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,34 +4178,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668289</v>
+        <v>668312</v>
       </c>
       <c r="R36" t="n">
-        <v>6703690</v>
+        <v>6703726</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4209,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129624325</v>
+        <v>129624329</v>
       </c>
       <c r="B37" t="n">
-        <v>96143</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,34 +4280,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668318</v>
+        <v>668230</v>
       </c>
       <c r="R37" t="n">
-        <v>6703714</v>
+        <v>6703725</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4306,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129624372</v>
+        <v>129624330</v>
       </c>
       <c r="B38" t="n">
-        <v>96239</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,31 +4382,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4350,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668296</v>
+        <v>668289</v>
       </c>
       <c r="R38" t="n">
-        <v>6703695</v>
+        <v>6703714</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4412,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129624369</v>
+        <v>129624331</v>
       </c>
       <c r="B39" t="n">
-        <v>105863</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,34 +4484,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668127</v>
+        <v>668257</v>
       </c>
       <c r="R39" t="n">
-        <v>6703878</v>
+        <v>6703774</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4509,48 +4575,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129624307</v>
+        <v>134416563</v>
       </c>
       <c r="B40" t="n">
-        <v>97043</v>
+        <v>4776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668175</v>
+        <v>667808</v>
       </c>
       <c r="R40" t="n">
-        <v>6703703</v>
+        <v>6703766</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4574,12 +4640,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,57 +4660,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129624318</v>
+        <v>129624381</v>
       </c>
       <c r="B41" t="n">
-        <v>97043</v>
+        <v>5179</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668185</v>
+        <v>668298</v>
       </c>
       <c r="R41" t="n">
-        <v>6703684</v>
+        <v>6703728</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4690,17 +4761,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -4718,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129624345</v>
+        <v>129624382</v>
       </c>
       <c r="B42" t="n">
-        <v>98775</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,34 +4800,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668302</v>
+        <v>668266</v>
       </c>
       <c r="R42" t="n">
-        <v>6703713</v>
+        <v>6703768</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4799,6 +4875,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4815,10 +4906,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129624340</v>
+        <v>129624373</v>
       </c>
       <c r="B43" t="n">
-        <v>98775</v>
+        <v>4781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,21 +4917,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668169</v>
+        <v>668112</v>
       </c>
       <c r="R43" t="n">
-        <v>6703716</v>
+        <v>6703887</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4896,6 +4987,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4912,10 +5018,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129624357</v>
+        <v>129624374</v>
       </c>
       <c r="B44" t="n">
-        <v>97662</v>
+        <v>4781</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4923,19 +5029,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221944</v>
+        <v>102306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4943,10 +5053,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668270</v>
+        <v>668256</v>
       </c>
       <c r="R44" t="n">
-        <v>6703694</v>
+        <v>6703754</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4987,9 +5097,23 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5006,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129624322</v>
+        <v>134392491</v>
       </c>
       <c r="B45" t="n">
-        <v>104268</v>
+        <v>4782</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,13 +5165,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668300</v>
+        <v>667917</v>
       </c>
       <c r="R45" t="n">
-        <v>6703703</v>
+        <v>6703686</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5071,12 +5195,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5087,6 +5211,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5103,32 +5242,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129624373</v>
+        <v>129624323</v>
       </c>
       <c r="B46" t="n">
-        <v>4779</v>
+        <v>111389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5277,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668112</v>
+        <v>668134</v>
       </c>
       <c r="R46" t="n">
-        <v>6703887</v>
+        <v>6703832</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5176,29 +5315,20 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Vid kolbotten</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5215,48 +5345,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129624371</v>
+        <v>134392456</v>
       </c>
       <c r="B47" t="n">
-        <v>105863</v>
+        <v>111471</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668163</v>
+        <v>667811</v>
       </c>
       <c r="R47" t="n">
-        <v>6703870</v>
+        <v>6703819</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5280,12 +5419,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5312,10 +5451,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624298</v>
+        <v>134392496</v>
       </c>
       <c r="B48" t="n">
-        <v>101893</v>
+        <v>99112</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5323,21 +5462,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5347,13 +5486,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668171</v>
+        <v>667994</v>
       </c>
       <c r="R48" t="n">
-        <v>6703708</v>
+        <v>6703671</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5377,12 +5516,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5409,10 +5548,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624397</v>
+        <v>134416574</v>
       </c>
       <c r="B49" t="n">
-        <v>100986</v>
+        <v>99112</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5420,37 +5559,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668305</v>
+        <v>667872</v>
       </c>
       <c r="R49" t="n">
-        <v>6703751</v>
+        <v>6703790</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5474,12 +5613,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,44 +5633,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624349</v>
+        <v>129624339</v>
       </c>
       <c r="B50" t="n">
-        <v>92058</v>
+        <v>99096</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5680,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668275</v>
+        <v>668166</v>
       </c>
       <c r="R50" t="n">
-        <v>6703756</v>
+        <v>6703694</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,21 +5726,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5618,50 +5742,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624327</v>
+        <v>129624340</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>99096</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668173</v>
+        <v>668169</v>
       </c>
       <c r="R51" t="n">
-        <v>6703787</v>
+        <v>6703716</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5720,10 +5839,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624348</v>
+        <v>129624341</v>
       </c>
       <c r="B52" t="n">
-        <v>91378</v>
+        <v>99096</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5731,21 +5850,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5755,10 +5874,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668185</v>
+        <v>668131</v>
       </c>
       <c r="R52" t="n">
-        <v>6703715</v>
+        <v>6703835</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5817,10 +5936,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624339</v>
+        <v>129624343</v>
       </c>
       <c r="B53" t="n">
-        <v>98775</v>
+        <v>99096</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,10 +5971,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668166</v>
+        <v>668165</v>
       </c>
       <c r="R53" t="n">
-        <v>6703694</v>
+        <v>6703856</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5914,54 +6033,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624367</v>
+        <v>129624344</v>
       </c>
       <c r="B54" t="n">
-        <v>98797</v>
+        <v>99096</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668253</v>
+        <v>668257</v>
       </c>
       <c r="R54" t="n">
-        <v>6703781</v>
+        <v>6703688</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6020,10 +6130,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129624393</v>
+        <v>129624345</v>
       </c>
       <c r="B55" t="n">
-        <v>100986</v>
+        <v>99096</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6031,21 +6141,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6055,10 +6165,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668182</v>
+        <v>668302</v>
       </c>
       <c r="R55" t="n">
-        <v>6703746</v>
+        <v>6703713</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6117,10 +6227,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129624385</v>
+        <v>129624346</v>
       </c>
       <c r="B56" t="n">
-        <v>100986</v>
+        <v>99096</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6128,21 +6238,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6152,10 +6262,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668149</v>
+        <v>668302</v>
       </c>
       <c r="R56" t="n">
-        <v>6703811</v>
+        <v>6703689</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6214,10 +6324,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129624403</v>
+        <v>129624347</v>
       </c>
       <c r="B57" t="n">
-        <v>100986</v>
+        <v>99096</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6225,21 +6335,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6249,10 +6359,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668258</v>
+        <v>668269</v>
       </c>
       <c r="R57" t="n">
-        <v>6703763</v>
+        <v>6703736</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6311,10 +6421,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129624400</v>
+        <v>134392471</v>
       </c>
       <c r="B58" t="n">
-        <v>100986</v>
+        <v>99173</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,21 +6432,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6346,13 +6456,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668331</v>
+        <v>667798</v>
       </c>
       <c r="R58" t="n">
-        <v>6703743</v>
+        <v>6703380</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6376,12 +6486,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6408,32 +6518,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129624309</v>
+        <v>134392472</v>
       </c>
       <c r="B59" t="n">
-        <v>97043</v>
+        <v>99173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6443,13 +6553,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668130</v>
+        <v>667810</v>
       </c>
       <c r="R59" t="n">
-        <v>6703878</v>
+        <v>6703816</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6473,12 +6583,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6505,48 +6615,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129624317</v>
+        <v>134416576</v>
       </c>
       <c r="B60" t="n">
-        <v>97043</v>
+        <v>99173</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668229</v>
+        <v>667875</v>
       </c>
       <c r="R60" t="n">
-        <v>6703722</v>
+        <v>6703750</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6570,12 +6680,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6590,22 +6700,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129624347</v>
+        <v>134392450</v>
       </c>
       <c r="B61" t="n">
-        <v>98775</v>
+        <v>99219</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6613,21 +6723,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6637,13 +6747,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668269</v>
+        <v>667798</v>
       </c>
       <c r="R61" t="n">
-        <v>6703736</v>
+        <v>6703380</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6667,12 +6777,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6699,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624381</v>
+        <v>134392451</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>99219</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6710,42 +6820,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>219847</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668298</v>
+        <v>667994</v>
       </c>
       <c r="R62" t="n">
-        <v>6703728</v>
+        <v>6703722</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6769,12 +6874,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6785,21 +6890,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6816,10 +6906,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129624387</v>
+        <v>134392483</v>
       </c>
       <c r="B63" t="n">
-        <v>100986</v>
+        <v>108274</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6827,21 +6917,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6851,13 +6941,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668132</v>
+        <v>667994</v>
       </c>
       <c r="R63" t="n">
-        <v>6703833</v>
+        <v>6703671</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6881,12 +6971,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6913,48 +7003,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129624314</v>
+        <v>134416582</v>
       </c>
       <c r="B64" t="n">
-        <v>97043</v>
+        <v>108274</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>220102</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668262</v>
+        <v>668145</v>
       </c>
       <c r="R64" t="n">
-        <v>6703759</v>
+        <v>6703816</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6978,12 +7068,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6992,28 +7082,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129624301</v>
+        <v>134392454</v>
       </c>
       <c r="B65" t="n">
-        <v>101893</v>
+        <v>104880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7021,21 +7112,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>220460</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cardamine bulbifera</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7045,13 +7136,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668194</v>
+        <v>667989</v>
       </c>
       <c r="R65" t="n">
-        <v>6703673</v>
+        <v>6703734</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7075,12 +7166,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7107,45 +7198,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129624389</v>
+        <v>129624366</v>
       </c>
       <c r="B66" t="n">
-        <v>100986</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668107</v>
+        <v>668160</v>
       </c>
       <c r="R66" t="n">
-        <v>6703910</v>
+        <v>6703911</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7204,45 +7304,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129624323</v>
+        <v>129624367</v>
       </c>
       <c r="B67" t="n">
-        <v>110953</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668134</v>
+        <v>668253</v>
       </c>
       <c r="R67" t="n">
-        <v>6703832</v>
+        <v>6703781</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7277,18 +7386,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Vid kolbotten</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7307,10 +7410,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134392487</v>
+        <v>129624368</v>
       </c>
       <c r="B68" t="n">
-        <v>75461</v>
+        <v>106243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7318,21 +7421,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7342,13 +7445,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>667926</v>
+        <v>668181</v>
       </c>
       <c r="R68" t="n">
-        <v>6703698</v>
+        <v>6703685</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7372,12 +7475,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7388,21 +7491,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7419,10 +7507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134392488</v>
+        <v>129624369</v>
       </c>
       <c r="B69" t="n">
-        <v>75461</v>
+        <v>106243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7430,21 +7518,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7454,13 +7542,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>667914</v>
+        <v>668127</v>
       </c>
       <c r="R69" t="n">
-        <v>6703674</v>
+        <v>6703878</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7484,12 +7572,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7500,21 +7588,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7531,10 +7604,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134392490</v>
+        <v>129624370</v>
       </c>
       <c r="B70" t="n">
-        <v>106317</v>
+        <v>106243</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7566,13 +7639,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668025</v>
+        <v>668108</v>
       </c>
       <c r="R70" t="n">
-        <v>6703816</v>
+        <v>6703888</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7596,12 +7669,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7628,10 +7701,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134392453</v>
+        <v>129624371</v>
       </c>
       <c r="B71" t="n">
-        <v>104700</v>
+        <v>106243</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7639,21 +7712,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222412</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7663,13 +7736,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>667989</v>
+        <v>668163</v>
       </c>
       <c r="R71" t="n">
-        <v>6703734</v>
+        <v>6703870</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7693,12 +7766,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7725,10 +7798,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134392441</v>
+        <v>134392489</v>
       </c>
       <c r="B72" t="n">
-        <v>102311</v>
+        <v>106324</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7736,21 +7809,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7760,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>667813</v>
+        <v>667765</v>
       </c>
       <c r="R72" t="n">
-        <v>6703824</v>
+        <v>6703549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7822,10 +7895,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134392442</v>
+        <v>134392490</v>
       </c>
       <c r="B73" t="n">
-        <v>102311</v>
+        <v>106324</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7833,21 +7906,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7857,10 +7930,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>667852</v>
+        <v>668025</v>
       </c>
       <c r="R73" t="n">
-        <v>6703807</v>
+        <v>6703816</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,48 +7992,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134392447</v>
+        <v>134416558</v>
       </c>
       <c r="B74" t="n">
-        <v>97428</v>
+        <v>106324</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>667871</v>
+        <v>667771</v>
       </c>
       <c r="R74" t="n">
-        <v>6703758</v>
+        <v>6703573</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8000,41 +8073,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134392446</v>
+        <v>129624296</v>
       </c>
       <c r="B75" t="n">
-        <v>97428</v>
+        <v>102240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8042,21 +8100,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8066,13 +8124,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>667878</v>
+        <v>668152</v>
       </c>
       <c r="R75" t="n">
-        <v>6703790</v>
+        <v>6703756</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8096,12 +8154,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8128,32 +8186,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134392499</v>
+        <v>129624297</v>
       </c>
       <c r="B76" t="n">
-        <v>101396</v>
+        <v>102240</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8163,13 +8221,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>667871</v>
+        <v>668176</v>
       </c>
       <c r="R76" t="n">
-        <v>6703785</v>
+        <v>6703677</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8193,12 +8251,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8225,32 +8283,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134392500</v>
+        <v>129624298</v>
       </c>
       <c r="B77" t="n">
-        <v>101396</v>
+        <v>102240</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8260,13 +8318,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>667878</v>
+        <v>668171</v>
       </c>
       <c r="R77" t="n">
-        <v>6703749</v>
+        <v>6703708</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8290,12 +8348,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8322,32 +8380,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134392472</v>
+        <v>129624299</v>
       </c>
       <c r="B78" t="n">
-        <v>99166</v>
+        <v>102240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8357,13 +8415,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>667810</v>
+        <v>668169</v>
       </c>
       <c r="R78" t="n">
-        <v>6703816</v>
+        <v>6703716</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8387,12 +8445,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8419,32 +8477,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134392496</v>
+        <v>129624300</v>
       </c>
       <c r="B79" t="n">
-        <v>99105</v>
+        <v>102240</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219790</v>
+        <v>221235</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8454,13 +8512,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>667994</v>
+        <v>668262</v>
       </c>
       <c r="R79" t="n">
-        <v>6703671</v>
+        <v>6703729</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8484,12 +8542,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8516,10 +8574,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134392448</v>
+        <v>129624301</v>
       </c>
       <c r="B80" t="n">
-        <v>97428</v>
+        <v>102240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8527,21 +8585,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8551,13 +8609,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668010</v>
+        <v>668194</v>
       </c>
       <c r="R80" t="n">
-        <v>6703823</v>
+        <v>6703673</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8581,12 +8639,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8597,21 +8655,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -8628,32 +8671,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134392497</v>
+        <v>134392441</v>
       </c>
       <c r="B81" t="n">
-        <v>101396</v>
+        <v>102318</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8663,10 +8706,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>667819</v>
+        <v>667813</v>
       </c>
       <c r="R81" t="n">
-        <v>6703799</v>
+        <v>6703824</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8725,32 +8768,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134392498</v>
+        <v>134392442</v>
       </c>
       <c r="B82" t="n">
-        <v>101396</v>
+        <v>102318</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8822,32 +8865,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134392451</v>
+        <v>134392443</v>
       </c>
       <c r="B83" t="n">
-        <v>99212</v>
+        <v>102318</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8857,10 +8900,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>667994</v>
+        <v>667882</v>
       </c>
       <c r="R83" t="n">
-        <v>6703722</v>
+        <v>6703730</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8919,48 +8962,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134392459</v>
+        <v>134416555</v>
       </c>
       <c r="B84" t="n">
-        <v>96526</v>
+        <v>102318</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2818</v>
+        <v>221235</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>667846</v>
+        <v>667761</v>
       </c>
       <c r="R84" t="n">
-        <v>6703798</v>
+        <v>6703513</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9000,79 +9043,64 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134392491</v>
+        <v>134416556</v>
       </c>
       <c r="B85" t="n">
-        <v>4782</v>
+        <v>102318</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>667917</v>
+        <v>667771</v>
       </c>
       <c r="R85" t="n">
-        <v>6703686</v>
+        <v>6703557</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9112,79 +9140,64 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134392502</v>
+        <v>134416566</v>
       </c>
       <c r="B86" t="n">
-        <v>101396</v>
+        <v>102318</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>667917</v>
+        <v>667829</v>
       </c>
       <c r="R86" t="n">
-        <v>6703675</v>
+        <v>6703833</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9228,22 +9241,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134392456</v>
+        <v>129624357</v>
       </c>
       <c r="B87" t="n">
-        <v>111464</v>
+        <v>97977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9251,46 +9264,33 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219711</v>
+        <v>221944</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>667811</v>
+        <v>668270</v>
       </c>
       <c r="R87" t="n">
-        <v>6703819</v>
+        <v>6703694</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9328,6 +9328,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9346,10 +9347,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134392452</v>
+        <v>129624320</v>
       </c>
       <c r="B88" t="n">
-        <v>104700</v>
+        <v>104627</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,13 +9382,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>667981</v>
+        <v>668289</v>
       </c>
       <c r="R88" t="n">
-        <v>6703672</v>
+        <v>6703690</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9411,12 +9412,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9443,10 +9444,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134392443</v>
+        <v>129624322</v>
       </c>
       <c r="B89" t="n">
-        <v>102311</v>
+        <v>104627</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9454,21 +9455,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9478,13 +9479,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>667882</v>
+        <v>668300</v>
       </c>
       <c r="R89" t="n">
-        <v>6703730</v>
+        <v>6703703</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9508,12 +9509,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9540,10 +9541,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134416563</v>
+        <v>134392452</v>
       </c>
       <c r="B90" t="n">
-        <v>4776</v>
+        <v>104707</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9551,37 +9552,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100299</v>
+        <v>222412</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>667808</v>
+        <v>667981</v>
       </c>
       <c r="R90" t="n">
-        <v>6703766</v>
+        <v>6703672</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9625,22 +9626,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134416579</v>
+        <v>134392453</v>
       </c>
       <c r="B91" t="n">
-        <v>75461</v>
+        <v>104707</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9648,37 +9649,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>667925</v>
+        <v>667989</v>
       </c>
       <c r="R91" t="n">
-        <v>6703706</v>
+        <v>6703734</v>
       </c>
       <c r="S91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9722,22 +9723,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134416556</v>
+        <v>129624385</v>
       </c>
       <c r="B92" t="n">
-        <v>102311</v>
+        <v>101325</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9745,37 +9746,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>667771</v>
+        <v>668149</v>
       </c>
       <c r="R92" t="n">
-        <v>6703557</v>
+        <v>6703811</v>
       </c>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9799,12 +9800,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9819,22 +9820,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134416558</v>
+        <v>129624387</v>
       </c>
       <c r="B93" t="n">
-        <v>106317</v>
+        <v>101325</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9842,37 +9843,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>667771</v>
+        <v>668132</v>
       </c>
       <c r="R93" t="n">
-        <v>6703573</v>
+        <v>6703833</v>
       </c>
       <c r="S93" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9896,12 +9897,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9916,22 +9917,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134416580</v>
+        <v>129624388</v>
       </c>
       <c r="B94" t="n">
-        <v>75461</v>
+        <v>101325</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,37 +9940,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>667928</v>
+        <v>668122</v>
       </c>
       <c r="R94" t="n">
-        <v>6703706</v>
+        <v>6703878</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9993,12 +9994,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10013,22 +10014,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134416560</v>
+        <v>129624389</v>
       </c>
       <c r="B95" t="n">
-        <v>101396</v>
+        <v>101325</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10056,17 +10057,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>667777</v>
+        <v>668107</v>
       </c>
       <c r="R95" t="n">
-        <v>6703601</v>
+        <v>6703910</v>
       </c>
       <c r="S95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10090,12 +10091,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10110,22 +10111,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134416566</v>
+        <v>129624390</v>
       </c>
       <c r="B96" t="n">
-        <v>102311</v>
+        <v>101325</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10133,37 +10134,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>667829</v>
+        <v>668123</v>
       </c>
       <c r="R96" t="n">
-        <v>6703833</v>
+        <v>6703926</v>
       </c>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10187,12 +10188,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10207,60 +10208,60 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134416572</v>
+        <v>129624391</v>
       </c>
       <c r="B97" t="n">
-        <v>97428</v>
+        <v>101325</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>667863</v>
+        <v>668163</v>
       </c>
       <c r="R97" t="n">
-        <v>6703823</v>
+        <v>6703831</v>
       </c>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10284,12 +10285,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10304,22 +10305,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134416567</v>
+        <v>129624392</v>
       </c>
       <c r="B98" t="n">
-        <v>101396</v>
+        <v>101325</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10347,17 +10348,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>667829</v>
+        <v>668190</v>
       </c>
       <c r="R98" t="n">
-        <v>6703833</v>
+        <v>6703813</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10381,12 +10382,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10401,60 +10402,60 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134416565</v>
+        <v>129624393</v>
       </c>
       <c r="B99" t="n">
-        <v>97428</v>
+        <v>101325</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>667827</v>
+        <v>668182</v>
       </c>
       <c r="R99" t="n">
-        <v>6703851</v>
+        <v>6703746</v>
       </c>
       <c r="S99" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10478,12 +10479,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10498,22 +10499,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134416576</v>
+        <v>129624394</v>
       </c>
       <c r="B100" t="n">
-        <v>99166</v>
+        <v>101325</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10521,37 +10522,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>667875</v>
+        <v>668270</v>
       </c>
       <c r="R100" t="n">
-        <v>6703750</v>
+        <v>6703699</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10575,12 +10576,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10595,22 +10596,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134416577</v>
+        <v>129624395</v>
       </c>
       <c r="B101" t="n">
-        <v>75461</v>
+        <v>101325</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10618,34 +10619,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>667921</v>
+        <v>668288</v>
       </c>
       <c r="R101" t="n">
-        <v>6703707</v>
+        <v>6703696</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10672,12 +10673,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10692,22 +10693,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134416574</v>
+        <v>129624396</v>
       </c>
       <c r="B102" t="n">
-        <v>99105</v>
+        <v>101325</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10715,37 +10716,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219790</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>667872</v>
+        <v>668305</v>
       </c>
       <c r="R102" t="n">
-        <v>6703790</v>
+        <v>6703732</v>
       </c>
       <c r="S102" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10769,12 +10770,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10789,60 +10790,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134416562</v>
+        <v>129624397</v>
       </c>
       <c r="B103" t="n">
-        <v>97428</v>
+        <v>101325</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>667778</v>
+        <v>668305</v>
       </c>
       <c r="R103" t="n">
-        <v>6703686</v>
+        <v>6703751</v>
       </c>
       <c r="S103" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10866,12 +10867,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10886,22 +10887,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134416581</v>
+        <v>129624398</v>
       </c>
       <c r="B104" t="n">
-        <v>75461</v>
+        <v>101325</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10909,37 +10910,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kuggböle, Upl</t>
+          <t>Kuggböle, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>667937</v>
+        <v>668194</v>
       </c>
       <c r="R104" t="n">
-        <v>6703678</v>
+        <v>6703666</v>
       </c>
       <c r="S104" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10963,12 +10964,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10983,15 +10984,1567 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129624399</v>
+      </c>
+      <c r="B105" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>668154</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6703899</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129624400</v>
+      </c>
+      <c r="B106" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>668331</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6703743</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129624401</v>
+      </c>
+      <c r="B107" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>668293</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6703720</v>
+      </c>
+      <c r="S107" t="n">
+        <v>15</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129624402</v>
+      </c>
+      <c r="B108" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>668264</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6703785</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129624403</v>
+      </c>
+      <c r="B109" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>668258</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6703763</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>134392497</v>
+      </c>
+      <c r="B110" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>667819</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6703799</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>134392498</v>
+      </c>
+      <c r="B111" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>667852</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6703807</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>134392499</v>
+      </c>
+      <c r="B112" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>667871</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6703785</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>134392500</v>
+      </c>
+      <c r="B113" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>667878</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6703749</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>134392502</v>
+      </c>
+      <c r="B114" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>667917</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6703675</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>134416560</v>
+      </c>
+      <c r="B115" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>667777</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6703601</v>
+      </c>
+      <c r="S115" t="n">
+        <v>16</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
           <t>Vilhelm Kroon</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
+      <c r="AX115" t="inlineStr">
         <is>
           <t>Vilhelm Kroon</t>
         </is>
       </c>
-      <c r="AY104" t="inlineStr"/>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>134416567</v>
+      </c>
+      <c r="B116" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>667829</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6703833</v>
+      </c>
+      <c r="S116" t="n">
+        <v>9</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>134392473</v>
+      </c>
+      <c r="B117" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>667797</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6703379</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>134392474</v>
+      </c>
+      <c r="B118" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>667814</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6703797</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>134392475</v>
+      </c>
+      <c r="B119" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>667852</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6703807</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>134416571</v>
+      </c>
+      <c r="B120" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kuggböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>667835</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6703827</v>
+      </c>
+      <c r="S120" t="n">
+        <v>7</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51096-2025 artfynd.xlsx
+++ b/artfynd/A 51096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624308</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624309</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624311</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624313</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624314</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624315</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624316</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624317</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624318</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392446</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392447</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392448</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416562</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416565</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2426,6 +2511,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416572</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2532,6 +2622,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624372</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2644,6 +2739,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624349</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2756,6 +2856,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624383</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2853,6 +2958,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392484</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2950,6 +3060,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392485</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392486</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3144,6 +3264,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624325</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3256,6 +3381,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392459</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3353,6 +3483,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624348</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3450,6 +3585,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624404</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392487</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3674,6 +3819,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392488</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3771,6 +3921,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416577</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3868,6 +4023,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416579</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3965,6 +4125,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416580</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4062,6 +4227,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416581</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4164,6 +4334,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624327</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4266,6 +4441,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624328</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4368,6 +4548,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624329</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4470,6 +4655,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624330</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4572,6 +4762,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624331</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4669,6 +4864,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416563</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4786,6 +4986,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624381</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4903,6 +5108,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624382</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5015,6 +5225,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624373</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5127,6 +5342,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624374</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5239,6 +5459,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392491</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5342,6 +5567,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624323</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5448,6 +5678,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392456</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5545,6 +5780,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392496</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5642,6 +5882,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416574</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5739,6 +5984,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624339</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5836,6 +6086,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624340</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5933,6 +6188,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624341</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6030,6 +6290,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624343</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6127,6 +6392,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624344</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6224,6 +6494,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624345</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6321,6 +6596,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624346</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6418,6 +6698,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624347</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6515,6 +6800,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392471</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6612,6 +6902,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392472</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6709,6 +7004,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416576</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6806,6 +7106,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392450</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6903,6 +7208,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392451</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7000,6 +7310,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392483</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7098,6 +7413,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416582</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7195,6 +7515,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392454</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7301,6 +7626,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624366</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7407,6 +7737,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624367</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7504,6 +7839,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624368</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7601,6 +7941,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624369</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7698,6 +8043,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624370</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7795,6 +8145,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624371</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7892,6 +8247,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392489</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7989,6 +8349,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392490</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8086,6 +8451,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416558</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8183,6 +8553,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624296</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8280,6 +8655,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624297</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8377,6 +8757,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624298</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8474,6 +8859,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624299</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8571,6 +8961,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624300</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8668,6 +9063,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624301</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8765,6 +9165,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392441</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8862,6 +9267,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392442</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8959,6 +9369,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392443</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9056,6 +9471,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416555</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9153,6 +9573,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416556</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9250,6 +9675,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416566</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9344,6 +9774,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624357</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9441,6 +9876,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624320</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9538,6 +9978,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624322</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9635,6 +10080,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392452</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9732,6 +10182,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392453</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9829,6 +10284,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624385</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9926,6 +10386,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624387</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10023,6 +10488,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624388</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10120,6 +10590,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624389</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10217,6 +10692,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624390</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10314,6 +10794,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624391</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10411,6 +10896,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624392</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10508,6 +10998,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624393</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10605,6 +11100,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624394</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10702,6 +11202,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624395</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10799,6 +11304,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624396</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10896,6 +11406,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624397</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10993,6 +11508,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624398</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11090,6 +11610,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624399</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11187,6 +11712,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624400</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11284,6 +11814,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624401</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11381,6 +11916,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624402</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11478,6 +12018,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624403</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11575,6 +12120,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392497</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11672,6 +12222,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392498</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11769,6 +12324,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392499</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11866,6 +12426,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392500</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11963,6 +12528,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392502</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12060,6 +12630,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416560</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12157,6 +12732,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416567</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12254,6 +12834,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392473</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12351,6 +12936,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392474</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12448,6 +13038,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134392475</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12545,8 +13140,134 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416571</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>